--- a/Method_Operating_Model_2027_28.xlsx
+++ b/Method_Operating_Model_2027_28.xlsx
@@ -2416,7 +2416,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="15">
+  <numFmts count="16">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\)"/>
     <numFmt numFmtId="166" formatCode="0.0%;\-0.0%"/>
@@ -2425,13 +2425,14 @@
     <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
     <numFmt numFmtId="171" formatCode="0"/>
-    <numFmt numFmtId="172" formatCode="\$#,##0"/>
-    <numFmt numFmtId="173" formatCode="0.00%"/>
-    <numFmt numFmtId="174" formatCode="0.0"/>
-    <numFmt numFmtId="175" formatCode="0%"/>
-    <numFmt numFmtId="176" formatCode="@"/>
-    <numFmt numFmtId="177" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="178" formatCode="\$#,##0;;\–"/>
+    <numFmt numFmtId="172" formatCode="General"/>
+    <numFmt numFmtId="173" formatCode="\$#,##0"/>
+    <numFmt numFmtId="174" formatCode="0.00%"/>
+    <numFmt numFmtId="175" formatCode="0.0"/>
+    <numFmt numFmtId="176" formatCode="0%"/>
+    <numFmt numFmtId="177" formatCode="@"/>
+    <numFmt numFmtId="178" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="179" formatCode="\$#,##0;;\–"/>
   </numFmts>
   <fonts count="44">
     <font>
@@ -2870,760 +2871,764 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="190">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="22" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="21" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="21" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="25" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="25" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="25" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="25" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="25" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="25" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="25" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="25" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="28" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="28" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="179" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="179" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="40" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="40" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="41" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="41" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4639,15 +4644,15 @@
       <c r="D1" s="40"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="61" t="s">
         <v>357</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="86" t="s">
         <v>358</v>
       </c>
       <c r="C4" s="43" t="s">
@@ -4766,14 +4771,14 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="64" t="s">
         <v>370</v>
       </c>
-      <c r="C18" s="86" t="n">
+      <c r="C18" s="87" t="n">
         <f aca="false">'Vessel 2026 P&amp;L'!$AB$44</f>
         <v>80624</v>
       </c>
-      <c r="D18" s="87" t="n">
+      <c r="D18" s="88" t="n">
         <f aca="false">C18/12</f>
         <v>6718.66666666667</v>
       </c>
@@ -13974,7 +13979,7 @@
       <c r="A4" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="C4" s="88" t="n">
+      <c r="C4" s="89" t="n">
         <v>46235</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -19287,7 +19292,7 @@
       <c r="A4" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="C4" s="88" t="n">
+      <c r="C4" s="89" t="n">
         <v>46266</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -24541,25 +24546,25 @@
       <c r="D1" s="40"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="61" t="s">
         <v>404</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="62" t="s">
         <v>405</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="47" t="s">
         <v>406</v>
       </c>
-      <c r="C5" s="62" t="n">
+      <c r="C5" s="63" t="n">
         <v>106838.2</v>
       </c>
     </row>
@@ -24567,10 +24572,10 @@
       <c r="B6" s="47" t="s">
         <v>407</v>
       </c>
-      <c r="C6" s="62" t="n">
+      <c r="C6" s="63" t="n">
         <v>131727.36</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>408</v>
       </c>
     </row>
@@ -24578,7 +24583,7 @@
       <c r="B7" s="47" t="s">
         <v>409</v>
       </c>
-      <c r="C7" s="62" t="n">
+      <c r="C7" s="63" t="n">
         <v>13996.3</v>
       </c>
     </row>
@@ -24586,7 +24591,7 @@
       <c r="B8" s="47" t="s">
         <v>410</v>
       </c>
-      <c r="C8" s="62" t="n">
+      <c r="C8" s="63" t="n">
         <v>5847.56</v>
       </c>
     </row>
@@ -24594,7 +24599,7 @@
       <c r="B9" s="47" t="s">
         <v>411</v>
       </c>
-      <c r="C9" s="62" t="n">
+      <c r="C9" s="63" t="n">
         <v>7792.6</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -24602,26 +24607,26 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="66" t="s">
+      <c r="B10" s="67" t="s">
         <v>413</v>
       </c>
-      <c r="C10" s="67" t="n">
+      <c r="C10" s="68" t="n">
         <f aca="false">SUM(C5:C9)</f>
         <v>266202.02</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="62" t="s">
         <v>414</v>
       </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="47" t="s">
         <v>415</v>
       </c>
-      <c r="C13" s="64" t="n">
+      <c r="C13" s="65" t="n">
         <v>0.4407</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -24632,7 +24637,7 @@
       <c r="B14" s="47" t="s">
         <v>417</v>
       </c>
-      <c r="C14" s="64" t="n">
+      <c r="C14" s="65" t="n">
         <v>0.2216</v>
       </c>
     </row>
@@ -24640,7 +24645,7 @@
       <c r="B15" s="47" t="s">
         <v>418</v>
       </c>
-      <c r="C15" s="64" t="n">
+      <c r="C15" s="65" t="n">
         <v>0.3328</v>
       </c>
     </row>
@@ -24648,7 +24653,7 @@
       <c r="B16" s="47" t="s">
         <v>419</v>
       </c>
-      <c r="C16" s="64" t="n">
+      <c r="C16" s="65" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -24659,7 +24664,7 @@
       <c r="B17" s="47" t="s">
         <v>421</v>
       </c>
-      <c r="C17" s="64" t="n">
+      <c r="C17" s="65" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -24667,20 +24672,20 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="62" t="s">
         <v>423</v>
       </c>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="47" t="s">
         <v>424</v>
       </c>
-      <c r="C20" s="65" t="n">
+      <c r="C20" s="66" t="n">
         <v>10</v>
       </c>
-      <c r="D20" s="63" t="s">
+      <c r="D20" s="64" t="s">
         <v>425</v>
       </c>
     </row>
@@ -24688,11 +24693,11 @@
       <c r="B21" s="47" t="s">
         <v>426</v>
       </c>
-      <c r="C21" s="65" t="n">
+      <c r="C21" s="66" t="n">
         <f aca="false">2*4/7</f>
         <v>1.14285714285714</v>
       </c>
-      <c r="D21" s="63" t="s">
+      <c r="D21" s="64" t="s">
         <v>427</v>
       </c>
     </row>
@@ -24700,7 +24705,7 @@
       <c r="B22" s="47" t="s">
         <v>428</v>
       </c>
-      <c r="C22" s="65" t="n">
+      <c r="C22" s="66" t="n">
         <v>7</v>
       </c>
     </row>
@@ -24708,10 +24713,10 @@
       <c r="B23" s="47" t="s">
         <v>429</v>
       </c>
-      <c r="C23" s="62" t="n">
+      <c r="C23" s="63" t="n">
         <v>20</v>
       </c>
-      <c r="D23" s="63" t="s">
+      <c r="D23" s="64" t="s">
         <v>430</v>
       </c>
     </row>
@@ -24719,19 +24724,19 @@
       <c r="B24" s="47" t="s">
         <v>298</v>
       </c>
-      <c r="C24" s="64" t="n">
+      <c r="C24" s="65" t="n">
         <v>0.16</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="66" t="s">
+      <c r="B25" s="67" t="s">
         <v>431</v>
       </c>
-      <c r="C25" s="67" t="n">
+      <c r="C25" s="68" t="n">
         <f aca="false">(C20+C21)*C22*52*C23*(1+C24)+C26*52*(1+C24)</f>
         <v>111953.92</v>
       </c>
-      <c r="D25" s="63" t="s">
+      <c r="D25" s="64" t="s">
         <v>432</v>
       </c>
     </row>
@@ -24739,7 +24744,7 @@
       <c r="B26" s="47" t="s">
         <v>433</v>
       </c>
-      <c r="C26" s="62" t="n">
+      <c r="C26" s="63" t="n">
         <v>296</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -24747,38 +24752,38 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="61" t="s">
+      <c r="B27" s="62" t="s">
         <v>435</v>
       </c>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="47" t="s">
         <v>436</v>
       </c>
-      <c r="C28" s="62" t="n">
+      <c r="C28" s="63" t="n">
         <v>164857</v>
       </c>
-      <c r="D28" s="63" t="s">
+      <c r="D28" s="64" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="62" t="s">
         <v>438</v>
       </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="62"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="C31" s="64" t="n">
+      <c r="C31" s="65" t="n">
         <v>0.025</v>
       </c>
-      <c r="D31" s="63" t="s">
+      <c r="D31" s="64" t="s">
         <v>439</v>
       </c>
     </row>
@@ -24786,10 +24791,10 @@
       <c r="B32" s="47" t="s">
         <v>440</v>
       </c>
-      <c r="C32" s="62" t="n">
+      <c r="C32" s="63" t="n">
         <v>89675</v>
       </c>
-      <c r="D32" s="63" t="s">
+      <c r="D32" s="64" t="s">
         <v>441</v>
       </c>
     </row>
@@ -24797,25 +24802,25 @@
       <c r="B33" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="C33" s="62" t="n">
+      <c r="C33" s="63" t="n">
         <v>5657</v>
       </c>
-      <c r="D33" s="63" t="s">
+      <c r="D33" s="64" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="61" t="s">
+      <c r="B35" s="62" t="s">
         <v>443</v>
       </c>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="47" t="s">
         <v>444</v>
       </c>
-      <c r="C36" s="62" t="n">
+      <c r="C36" s="63" t="n">
         <f aca="false">'LW Retail Plan'!$C$19</f>
         <v>42000.22</v>
       </c>
@@ -24827,7 +24832,7 @@
       <c r="B37" s="47" t="s">
         <v>446</v>
       </c>
-      <c r="C37" s="89" t="n">
+      <c r="C37" s="90" t="n">
         <f aca="false">'LW Retail Plan'!$C$20</f>
         <v>0.42</v>
       </c>
@@ -24836,20 +24841,20 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="90" t="s">
+      <c r="B39" s="91" t="s">
         <v>448</v>
       </c>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90"/>
+      <c r="C39" s="91"/>
+      <c r="D39" s="91"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="47" t="s">
         <v>449</v>
       </c>
-      <c r="C40" s="91" t="n">
+      <c r="C40" s="92" t="n">
         <v>0.04</v>
       </c>
-      <c r="D40" s="63" t="s">
+      <c r="D40" s="64" t="s">
         <v>450</v>
       </c>
     </row>
@@ -24857,10 +24862,10 @@
       <c r="B41" s="47" t="s">
         <v>451</v>
       </c>
-      <c r="C41" s="91" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="63" t="s">
+      <c r="C41" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="64" t="s">
         <v>452</v>
       </c>
     </row>
@@ -24871,7 +24876,7 @@
       <c r="C42" s="45" t="n">
         <v>10012</v>
       </c>
-      <c r="D42" s="63" t="s">
+      <c r="D42" s="64" t="s">
         <v>454</v>
       </c>
     </row>
@@ -24883,7 +24888,7 @@
         <f aca="false">'LW Menu Pricing'!$C$53</f>
         <v>9160.92</v>
       </c>
-      <c r="D43" s="63" t="s">
+      <c r="D43" s="64" t="s">
         <v>456</v>
       </c>
     </row>
@@ -24891,10 +24896,10 @@
       <c r="B44" s="47" t="s">
         <v>457</v>
       </c>
-      <c r="C44" s="92" t="n">
+      <c r="C44" s="93" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="63" t="s">
+      <c r="D44" s="64" t="s">
         <v>458</v>
       </c>
     </row>
@@ -24905,7 +24910,7 @@
       <c r="C45" s="45" t="n">
         <v>12880</v>
       </c>
-      <c r="D45" s="63" t="s">
+      <c r="D45" s="64" t="s">
         <v>460</v>
       </c>
     </row>
@@ -24913,7 +24918,7 @@
       <c r="B46" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C46" s="93" t="n">
+      <c r="C46" s="94" t="n">
         <v>0.5</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -24924,7 +24929,7 @@
       <c r="B47" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C47" s="86" t="n">
+      <c r="C47" s="87" t="n">
         <f aca="false">'LW Assumptions'!$C$8*'LW Assumptions'!$C$46</f>
         <v>2923.78</v>
       </c>
@@ -24933,10 +24938,10 @@
       <c r="B48" s="47" t="s">
         <v>312</v>
       </c>
-      <c r="C48" s="91" t="n">
+      <c r="C48" s="92" t="n">
         <v>0.125</v>
       </c>
-      <c r="D48" s="63" t="s">
+      <c r="D48" s="64" t="s">
         <v>464</v>
       </c>
     </row>
@@ -24944,28 +24949,28 @@
       <c r="B49" s="47" t="s">
         <v>465</v>
       </c>
-      <c r="C49" s="91" t="n">
+      <c r="C49" s="92" t="n">
         <v>0.035</v>
       </c>
-      <c r="D49" s="63"/>
+      <c r="D49" s="64"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="47" t="s">
         <v>314</v>
       </c>
-      <c r="C50" s="91" t="n">
+      <c r="C50" s="92" t="n">
         <v>0.085</v>
       </c>
-      <c r="D50" s="63"/>
+      <c r="D50" s="64"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="47" t="s">
         <v>466</v>
       </c>
-      <c r="C51" s="91" t="n">
+      <c r="C51" s="92" t="n">
         <v>0.4</v>
       </c>
-      <c r="D51" s="63" t="s">
+      <c r="D51" s="64" t="s">
         <v>467</v>
       </c>
     </row>
@@ -24973,10 +24978,10 @@
       <c r="B52" s="47" t="s">
         <v>468</v>
       </c>
-      <c r="C52" s="91" t="n">
+      <c r="C52" s="92" t="n">
         <v>0.045</v>
       </c>
-      <c r="D52" s="63" t="s">
+      <c r="D52" s="64" t="s">
         <v>469</v>
       </c>
     </row>
@@ -24984,10 +24989,10 @@
       <c r="B53" s="47" t="s">
         <v>470</v>
       </c>
-      <c r="C53" s="91" t="n">
+      <c r="C53" s="92" t="n">
         <v>0.025</v>
       </c>
-      <c r="D53" s="63" t="s">
+      <c r="D53" s="64" t="s">
         <v>471</v>
       </c>
     </row>
@@ -31719,7 +31724,7 @@
       <c r="A76" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="C76" s="74" t="n">
+      <c r="C76" s="75" t="n">
         <f aca="false">'LW Assumptions'!$C$20+'LW Assumptions'!$C$21</f>
         <v>11.1428571428571</v>
       </c>
@@ -31732,7 +31737,7 @@
       <c r="A77" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="C77" s="74" t="n">
+      <c r="C77" s="75" t="n">
         <v>8</v>
       </c>
       <c r="E77" s="24" t="n">
@@ -31744,7 +31749,7 @@
       <c r="A78" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="C78" s="74" t="n">
+      <c r="C78" s="75" t="n">
         <v>13.5</v>
       </c>
       <c r="E78" s="24" t="n">
@@ -31756,7 +31761,7 @@
       <c r="A79" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="C79" s="74" t="n">
+      <c r="C79" s="75" t="n">
         <v>16</v>
       </c>
       <c r="E79" s="24" t="n">
@@ -31834,16 +31839,16 @@
       <c r="H1" s="40"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="61" t="s">
         <v>493</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="42" t="s">
@@ -31854,7 +31859,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="86" t="s">
         <v>496</v>
       </c>
       <c r="C5" s="43" t="s">
@@ -31863,7 +31868,7 @@
       <c r="D5" s="43" t="s">
         <v>497</v>
       </c>
-      <c r="F5" s="85" t="s">
+      <c r="F5" s="86" t="s">
         <v>498</v>
       </c>
       <c r="G5" s="43" t="s">
@@ -31928,7 +31933,7 @@
         <f aca="false">C8/'LW Assumptions'!C10</f>
         <v>0.115427373541343</v>
       </c>
-      <c r="F8" s="94" t="s">
+      <c r="F8" s="95" t="s">
         <v>506</v>
       </c>
       <c r="G8" s="45" t="n">
@@ -31963,7 +31968,7 @@
         <f aca="false">C10/'LW Assumptions'!C10</f>
         <v>0.00332829931192859</v>
       </c>
-      <c r="F10" s="63" t="s">
+      <c r="F10" s="64" t="s">
         <v>509</v>
       </c>
     </row>
@@ -31978,12 +31983,12 @@
         <f aca="false">C11/'LW Assumptions'!C10</f>
         <v>0.0853975488240097</v>
       </c>
-      <c r="F11" s="63" t="s">
+      <c r="F11" s="64" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="95" t="s">
         <v>512</v>
       </c>
       <c r="C12" s="45" t="n">
@@ -31994,7 +31999,7 @@
         <f aca="false">C12/'LW Assumptions'!C10</f>
         <v>0.619296577839642</v>
       </c>
-      <c r="F12" s="63" t="s">
+      <c r="F12" s="64" t="s">
         <v>513</v>
       </c>
     </row>
@@ -32007,7 +32012,7 @@
       <c r="B15" s="47" t="s">
         <v>515</v>
       </c>
-      <c r="C15" s="95" t="n">
+      <c r="C15" s="96" t="n">
         <f aca="false">'LW Assumptions'!C20+'LW Assumptions'!C21</f>
         <v>11.1428571428571</v>
       </c>
@@ -32058,10 +32063,10 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="96" t="s">
+      <c r="B21" s="97" t="s">
         <v>521</v>
       </c>
-      <c r="C21" s="97" t="n">
+      <c r="C21" s="98" t="n">
         <f aca="false">C12-C20</f>
         <v>52904.08</v>
       </c>
@@ -32116,7 +32121,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="99" t="s">
         <v>523</v>
       </c>
       <c r="B1" s="38"/>
@@ -32124,15 +32129,15 @@
       <c r="D1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="100" t="s">
         <v>524</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="85"/>
+      <c r="A4" s="86"/>
       <c r="B4" s="43" t="s">
         <v>525</v>
       </c>
@@ -32144,321 +32149,321 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="95" t="s">
         <v>528</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="101" t="s">
+      <c r="A6" s="102" t="s">
         <v>529</v>
       </c>
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="103" t="s">
         <v>530</v>
       </c>
-      <c r="C6" s="102" t="n">
+      <c r="C6" s="103" t="n">
         <f aca="false">'LW Assumptions'!$C$20+'LW Assumptions'!$C$21</f>
         <v>11.1428571428571</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="101" t="s">
+      <c r="A7" s="102" t="s">
         <v>531</v>
       </c>
-      <c r="B7" s="103" t="n">
+      <c r="B7" s="104" t="n">
         <v>7</v>
       </c>
-      <c r="C7" s="103" t="n">
+      <c r="C7" s="104" t="n">
         <f aca="false">'LW Assumptions'!$C$22</f>
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="94" t="s">
+      <c r="A9" s="95" t="s">
         <v>532</v>
       </c>
-      <c r="B9" s="100"/>
-      <c r="C9" s="100"/>
-      <c r="D9" s="100"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="101"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="102" t="s">
         <v>533</v>
       </c>
-      <c r="B10" s="104" t="n">
+      <c r="B10" s="105" t="n">
         <v>111.8</v>
       </c>
-      <c r="C10" s="104" t="n">
+      <c r="C10" s="105" t="n">
         <f aca="false">('LW Assumptions'!$C$20+'LW Assumptions'!$C$21)*'LW Assumptions'!$C$22</f>
         <v>78</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="101" t="s">
+      <c r="A11" s="102" t="s">
         <v>534</v>
       </c>
-      <c r="B11" s="104" t="n">
+      <c r="B11" s="105" t="n">
         <v>13.3</v>
       </c>
-      <c r="C11" s="104" t="n">
+      <c r="C11" s="105" t="n">
         <f aca="false">B11</f>
         <v>13.3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="105" t="s">
+      <c r="A12" s="106" t="s">
         <v>535</v>
       </c>
-      <c r="B12" s="106" t="n">
+      <c r="B12" s="107" t="n">
         <v>125.1</v>
       </c>
-      <c r="C12" s="106" t="n">
+      <c r="C12" s="107" t="n">
         <f aca="false">('LW Assumptions'!$C$20+'LW Assumptions'!$C$21)*'LW Assumptions'!$C$22+C11</f>
         <v>91.3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="107"/>
-      <c r="B13" s="108"/>
-      <c r="C13" s="108"/>
+      <c r="A13" s="108"/>
+      <c r="B13" s="109"/>
+      <c r="C13" s="109"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="94" t="s">
+      <c r="A14" s="95" t="s">
         <v>536</v>
       </c>
-      <c r="B14" s="100"/>
-      <c r="C14" s="100"/>
-      <c r="D14" s="100"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="101"/>
+      <c r="D14" s="101"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="101" t="s">
+      <c r="A15" s="102" t="s">
         <v>537</v>
       </c>
-      <c r="B15" s="109" t="n">
+      <c r="B15" s="110" t="n">
         <v>2207</v>
       </c>
-      <c r="C15" s="109" t="n">
+      <c r="C15" s="110" t="n">
         <f aca="false">('LW Assumptions'!$C$20+'LW Assumptions'!$C$21)*'LW Assumptions'!$C$22*'LW Assumptions'!$C$23</f>
         <v>1560</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="101" t="s">
+      <c r="A16" s="102" t="s">
         <v>538</v>
       </c>
-      <c r="B16" s="109" t="n">
+      <c r="B16" s="110" t="n">
         <v>296</v>
       </c>
-      <c r="C16" s="109" t="n">
+      <c r="C16" s="110" t="n">
         <f aca="false">'LW Assumptions'!$C$26</f>
         <v>296</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="107" t="s">
+      <c r="A17" s="108" t="s">
         <v>539</v>
       </c>
-      <c r="B17" s="87" t="n">
+      <c r="B17" s="88" t="n">
         <v>2503</v>
       </c>
-      <c r="C17" s="87" t="n">
+      <c r="C17" s="88" t="n">
         <f aca="false">C15+C16</f>
         <v>1856</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="101" t="s">
+      <c r="A18" s="102" t="s">
         <v>540</v>
       </c>
-      <c r="B18" s="109" t="n">
+      <c r="B18" s="110" t="n">
         <f aca="false">'LW Assumptions'!$C$45/52</f>
         <v>247.692307692308</v>
       </c>
-      <c r="C18" s="109" t="n">
+      <c r="C18" s="110" t="n">
         <f aca="false">'LW Assumptions'!$C$45/52</f>
         <v>247.692307692308</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="101" t="s">
+      <c r="A19" s="102" t="s">
         <v>541</v>
       </c>
-      <c r="B19" s="109" t="n">
+      <c r="B19" s="110" t="n">
         <f aca="false">(B17+B18)*'LW Assumptions'!$C$24</f>
         <v>440.110769230769</v>
       </c>
-      <c r="C19" s="109" t="n">
+      <c r="C19" s="110" t="n">
         <f aca="false">(C17+C18)*'LW Assumptions'!$C$24</f>
         <v>336.590769230769</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="111" t="s">
         <v>542</v>
       </c>
-      <c r="B20" s="111" t="n">
+      <c r="B20" s="112" t="n">
         <f aca="false">B17+B18+B19</f>
         <v>3190.80307692308</v>
       </c>
-      <c r="C20" s="111" t="n">
+      <c r="C20" s="112" t="n">
         <f aca="false">C17+C18+C19</f>
         <v>2440.28307692308</v>
       </c>
-      <c r="D20" s="111" t="n">
+      <c r="D20" s="112" t="n">
         <f aca="false">C20-B20</f>
         <v>-750.52</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="112"/>
-      <c r="B21" s="113"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
+      <c r="A21" s="113"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="107" t="s">
+      <c r="A22" s="108" t="s">
         <v>543</v>
       </c>
-      <c r="B22" s="87" t="n">
+      <c r="B22" s="88" t="n">
         <f aca="false">B20*52</f>
         <v>165921.76</v>
       </c>
-      <c r="C22" s="87" t="n">
+      <c r="C22" s="88" t="n">
         <f aca="false">C20*52</f>
         <v>126894.72</v>
       </c>
-      <c r="D22" s="87" t="n">
+      <c r="D22" s="88" t="n">
         <f aca="false">C22-B22</f>
         <v>-39027.04</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="107"/>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
-      <c r="D23" s="87"/>
+      <c r="A23" s="108"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="94" t="s">
+      <c r="A24" s="95" t="s">
         <v>544</v>
       </c>
-      <c r="B24" s="100"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="100"/>
+      <c r="B24" s="101"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="101"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="101" t="s">
+      <c r="A25" s="102" t="s">
         <v>545</v>
       </c>
-      <c r="B25" s="109" t="n">
+      <c r="B25" s="110" t="n">
         <v>5888.94</v>
       </c>
-      <c r="C25" s="109" t="n">
+      <c r="C25" s="110" t="n">
         <v>5888.94</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="107" t="s">
+      <c r="A26" s="108" t="s">
         <v>546</v>
       </c>
-      <c r="B26" s="114" t="n">
+      <c r="B26" s="115" t="n">
         <f aca="false">B20/B25</f>
         <v>0.541829782086942</v>
       </c>
-      <c r="C26" s="114" t="n">
+      <c r="C26" s="115" t="n">
         <f aca="false">C20/C25</f>
         <v>0.414384095766484</v>
       </c>
-      <c r="D26" s="114" t="n">
+      <c r="D26" s="115" t="n">
         <f aca="false">C26-B26</f>
         <v>-0.127445686320458</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="107"/>
-      <c r="B27" s="114"/>
-      <c r="C27" s="114"/>
-      <c r="D27" s="114"/>
+      <c r="A27" s="108"/>
+      <c r="B27" s="115"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="115"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="115" t="s">
+      <c r="A28" s="116" t="s">
         <v>547</v>
       </c>
-      <c r="B28" s="115"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="115"/>
+      <c r="B28" s="116"/>
+      <c r="C28" s="116"/>
+      <c r="D28" s="116"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="107" t="s">
+      <c r="A29" s="108" t="s">
         <v>548</v>
       </c>
-      <c r="C29" s="87" t="n">
+      <c r="C29" s="88" t="n">
         <f aca="false">B20-C20</f>
         <v>750.52</v>
       </c>
-      <c r="D29" s="87" t="n">
+      <c r="D29" s="88" t="n">
         <f aca="false">C22-B22</f>
         <v>-39027.04</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="116" t="s">
+      <c r="A31" s="117" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="117" t="s">
+      <c r="A32" s="118" t="s">
         <v>550</v>
       </c>
-      <c r="B32" s="117"/>
-      <c r="C32" s="117"/>
-      <c r="D32" s="117"/>
+      <c r="B32" s="118"/>
+      <c r="C32" s="118"/>
+      <c r="D32" s="118"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="117"/>
-      <c r="B33" s="117"/>
-      <c r="C33" s="117"/>
-      <c r="D33" s="117"/>
+      <c r="A33" s="118"/>
+      <c r="B33" s="118"/>
+      <c r="C33" s="118"/>
+      <c r="D33" s="118"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="116" t="s">
+      <c r="A35" s="117" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="117" t="s">
+      <c r="A36" s="118" t="s">
         <v>552</v>
       </c>
-      <c r="B36" s="117"/>
-      <c r="C36" s="117"/>
-      <c r="D36" s="117"/>
+      <c r="B36" s="118"/>
+      <c r="C36" s="118"/>
+      <c r="D36" s="118"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="117"/>
-      <c r="B37" s="117"/>
-      <c r="C37" s="117"/>
-      <c r="D37" s="117"/>
+      <c r="A37" s="118"/>
+      <c r="B37" s="118"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="118"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="118" t="s">
+      <c r="A39" s="119" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="117" t="s">
+      <c r="A40" s="118" t="s">
         <v>554</v>
       </c>
-      <c r="B40" s="117"/>
-      <c r="C40" s="117"/>
-      <c r="D40" s="117"/>
+      <c r="B40" s="118"/>
+      <c r="C40" s="118"/>
+      <c r="D40" s="118"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="117"/>
-      <c r="B41" s="117"/>
-      <c r="C41" s="117"/>
-      <c r="D41" s="117"/>
+      <c r="A41" s="118"/>
+      <c r="B41" s="118"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="118"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -33749,7 +33754,7 @@
       <c r="A46" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="C46" s="119" t="n">
+      <c r="C46" s="120" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -33775,16 +33780,16 @@
       <c r="A49" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="C49" s="120" t="n">
+      <c r="C49" s="121" t="n">
         <v>0.25</v>
       </c>
-      <c r="D49" s="120" t="n">
+      <c r="D49" s="121" t="n">
         <v>0.5</v>
       </c>
-      <c r="E49" s="120" t="n">
+      <c r="E49" s="121" t="n">
         <v>0.75</v>
       </c>
-      <c r="F49" s="120" t="n">
+      <c r="F49" s="121" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33988,7 +33993,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="122" t="s">
         <v>621</v>
       </c>
       <c r="B1" s="38"/>
@@ -34003,35 +34008,35 @@
       <c r="K1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="100" t="s">
         <v>622</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="117" t="s">
         <v>623</v>
       </c>
-      <c r="B4" s="122" t="s">
+      <c r="B4" s="123" t="s">
         <v>624</v>
       </c>
-      <c r="C4" s="123" t="n">
+      <c r="C4" s="124" t="n">
         <f aca="false">'LW Assumptions'!$C$23</f>
         <v>20</v>
       </c>
-      <c r="D4" s="122" t="s">
+      <c r="D4" s="123" t="s">
         <v>625</v>
       </c>
-      <c r="E4" s="123" t="n">
+      <c r="E4" s="124" t="n">
         <v>25</v>
       </c>
     </row>
@@ -34041,341 +34046,341 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="124" t="s">
+      <c r="A7" s="125" t="s">
         <v>627</v>
       </c>
-      <c r="B7" s="124" t="s">
+      <c r="B7" s="125" t="s">
         <v>496</v>
       </c>
-      <c r="C7" s="125" t="s">
+      <c r="C7" s="126" t="s">
         <v>628</v>
       </c>
-      <c r="D7" s="125" t="s">
+      <c r="D7" s="126" t="s">
         <v>629</v>
       </c>
-      <c r="E7" s="125" t="s">
+      <c r="E7" s="126" t="s">
         <v>630</v>
       </c>
-      <c r="F7" s="125" t="s">
+      <c r="F7" s="126" t="s">
         <v>631</v>
       </c>
-      <c r="G7" s="125" t="s">
+      <c r="G7" s="126" t="s">
         <v>632</v>
       </c>
-      <c r="H7" s="125" t="s">
+      <c r="H7" s="126" t="s">
         <v>633</v>
       </c>
-      <c r="I7" s="125" t="s">
+      <c r="I7" s="126" t="s">
         <v>634</v>
       </c>
-      <c r="J7" s="125" t="s">
+      <c r="J7" s="126" t="s">
         <v>635</v>
       </c>
-      <c r="K7" s="125" t="s">
+      <c r="K7" s="126" t="s">
         <v>636</v>
       </c>
-      <c r="L7" s="125" t="s">
+      <c r="L7" s="126" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="127" t="s">
         <v>638</v>
       </c>
-      <c r="B8" s="127" t="s">
+      <c r="B8" s="128" t="s">
         <v>639</v>
       </c>
-      <c r="C8" s="128" t="n">
+      <c r="C8" s="129" t="n">
         <v>18.29</v>
       </c>
-      <c r="D8" s="129" t="n">
+      <c r="D8" s="130" t="n">
         <f aca="false">6*$C8</f>
         <v>109.74</v>
       </c>
-      <c r="E8" s="129" t="n">
+      <c r="E8" s="130" t="n">
         <f aca="false">7.75*$C8</f>
         <v>141.7475</v>
       </c>
-      <c r="F8" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="131" t="n">
+      <c r="F8" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="132" t="n">
         <v>13.75</v>
       </c>
-      <c r="L8" s="132" t="n">
+      <c r="L8" s="133" t="n">
         <f aca="false">SUM(D8:J8)</f>
         <v>251.4875</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="126" t="s">
+      <c r="A9" s="127" t="s">
         <v>638</v>
       </c>
-      <c r="B9" s="127" t="s">
+      <c r="B9" s="128" t="s">
         <v>640</v>
       </c>
-      <c r="C9" s="128" t="n">
+      <c r="C9" s="129" t="n">
         <v>21.03</v>
       </c>
-      <c r="D9" s="129" t="n">
+      <c r="D9" s="130" t="n">
         <f aca="false">1.75*$C9</f>
         <v>36.8025</v>
       </c>
-      <c r="E9" s="129" t="n">
+      <c r="E9" s="130" t="n">
         <f aca="false">1.75*$C9</f>
         <v>36.8025</v>
       </c>
-      <c r="F9" s="129" t="n">
+      <c r="F9" s="130" t="n">
         <f aca="false">7.75*$C9</f>
         <v>162.9825</v>
       </c>
-      <c r="G9" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="131" t="n">
+      <c r="G9" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="132" t="n">
         <v>11.25</v>
       </c>
-      <c r="L9" s="132" t="n">
+      <c r="L9" s="133" t="n">
         <f aca="false">SUM(D9:J9)</f>
         <v>236.5875</v>
       </c>
-      <c r="M9" s="133" t="s">
+      <c r="M9" s="134" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="126" t="s">
+      <c r="A10" s="127" t="s">
         <v>642</v>
       </c>
-      <c r="B10" s="127" t="s">
+      <c r="B10" s="128" t="s">
         <v>639</v>
       </c>
-      <c r="C10" s="128" t="n">
+      <c r="C10" s="129" t="n">
         <v>17.79</v>
       </c>
-      <c r="D10" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="129" t="n">
+      <c r="D10" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="130" t="n">
         <f aca="false">8*$C10</f>
         <v>142.32</v>
       </c>
-      <c r="I10" s="129" t="n">
+      <c r="I10" s="130" t="n">
         <f aca="false">8*$C10</f>
         <v>142.32</v>
       </c>
-      <c r="J10" s="129" t="n">
+      <c r="J10" s="130" t="n">
         <f aca="false">8*$C10</f>
         <v>142.32</v>
       </c>
-      <c r="K10" s="131" t="n">
+      <c r="K10" s="132" t="n">
         <v>24</v>
       </c>
-      <c r="L10" s="132" t="n">
+      <c r="L10" s="133" t="n">
         <f aca="false">SUM(D10:J10)</f>
         <v>426.96</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="126" t="s">
+      <c r="A11" s="127" t="s">
         <v>643</v>
       </c>
-      <c r="B11" s="127" t="s">
+      <c r="B11" s="128" t="s">
         <v>644</v>
       </c>
-      <c r="C11" s="128" t="n">
+      <c r="C11" s="129" t="n">
         <v>19.79</v>
       </c>
-      <c r="D11" s="129" t="n">
+      <c r="D11" s="130" t="n">
         <f aca="false">8*$C11</f>
         <v>158.32</v>
       </c>
-      <c r="E11" s="129" t="n">
+      <c r="E11" s="130" t="n">
         <f aca="false">8*$C11</f>
         <v>158.32</v>
       </c>
-      <c r="F11" s="129" t="n">
+      <c r="F11" s="130" t="n">
         <f aca="false">8*$C11</f>
         <v>158.32</v>
       </c>
-      <c r="G11" s="129" t="n">
+      <c r="G11" s="130" t="n">
         <f aca="false">8*$C11</f>
         <v>158.32</v>
       </c>
-      <c r="H11" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="129" t="n">
+      <c r="H11" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="130" t="n">
         <f aca="false">3*$C11</f>
         <v>59.37</v>
       </c>
-      <c r="K11" s="131" t="n">
+      <c r="K11" s="132" t="n">
         <v>35</v>
       </c>
-      <c r="L11" s="132" t="n">
+      <c r="L11" s="133" t="n">
         <f aca="false">SUM(D11:J11)</f>
         <v>692.65</v>
       </c>
-      <c r="M11" s="133" t="s">
+      <c r="M11" s="134" t="s">
         <v>645</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="126" t="s">
+      <c r="A12" s="127" t="s">
         <v>646</v>
       </c>
-      <c r="B12" s="127" t="s">
+      <c r="B12" s="128" t="s">
         <v>644</v>
       </c>
-      <c r="C12" s="128" t="n">
+      <c r="C12" s="129" t="n">
         <v>21.21</v>
       </c>
-      <c r="D12" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="129" t="n">
+      <c r="D12" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="130" t="n">
         <f aca="false">8*$C12</f>
         <v>169.68</v>
       </c>
-      <c r="G12" s="129" t="n">
+      <c r="G12" s="130" t="n">
         <f aca="false">8*$C12</f>
         <v>169.68</v>
       </c>
-      <c r="H12" s="129" t="n">
+      <c r="H12" s="130" t="n">
         <f aca="false">8*$C12</f>
         <v>169.68</v>
       </c>
-      <c r="I12" s="129" t="n">
+      <c r="I12" s="130" t="n">
         <f aca="false">8*$C12</f>
         <v>169.68</v>
       </c>
-      <c r="J12" s="129" t="n">
+      <c r="J12" s="130" t="n">
         <f aca="false">8*$C12</f>
         <v>169.68</v>
       </c>
-      <c r="K12" s="131" t="n">
+      <c r="K12" s="132" t="n">
         <v>40</v>
       </c>
-      <c r="L12" s="132" t="n">
+      <c r="L12" s="133" t="n">
         <f aca="false">SUM(D12:J12)</f>
         <v>848.4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="126" t="s">
+      <c r="A13" s="127" t="s">
         <v>647</v>
       </c>
-      <c r="B13" s="127" t="s">
+      <c r="B13" s="128" t="s">
         <v>648</v>
       </c>
-      <c r="C13" s="128" t="n">
+      <c r="C13" s="129" t="n">
         <v>25</v>
       </c>
-      <c r="D13" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="129" t="n">
+      <c r="D13" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="130" t="n">
         <f aca="false">8*$C13</f>
         <v>200</v>
       </c>
-      <c r="H13" s="129" t="n">
+      <c r="H13" s="130" t="n">
         <f aca="false">8*$C13</f>
         <v>200</v>
       </c>
-      <c r="I13" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="131" t="n">
+      <c r="I13" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="132" t="n">
         <v>16</v>
       </c>
-      <c r="L13" s="132" t="n">
+      <c r="L13" s="133" t="n">
         <f aca="false">SUM(D13:J13)</f>
         <v>400</v>
       </c>
-      <c r="M13" s="133" t="s">
+      <c r="M13" s="134" t="s">
         <v>649</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="94" t="s">
+      <c r="A14" s="95" t="s">
         <v>650</v>
       </c>
-      <c r="B14" s="100"/>
-      <c r="C14" s="134"/>
-      <c r="D14" s="134" t="n">
+      <c r="B14" s="101"/>
+      <c r="C14" s="135"/>
+      <c r="D14" s="135" t="n">
         <f aca="false">SUM(D8:D13)</f>
         <v>304.8625</v>
       </c>
-      <c r="E14" s="134" t="n">
+      <c r="E14" s="135" t="n">
         <f aca="false">SUM(E8:E13)</f>
         <v>336.87</v>
       </c>
-      <c r="F14" s="134" t="n">
+      <c r="F14" s="135" t="n">
         <f aca="false">SUM(F8:F13)</f>
         <v>490.9825</v>
       </c>
-      <c r="G14" s="134" t="n">
+      <c r="G14" s="135" t="n">
         <f aca="false">SUM(G8:G13)</f>
         <v>528</v>
       </c>
-      <c r="H14" s="134" t="n">
+      <c r="H14" s="135" t="n">
         <f aca="false">SUM(H8:H13)</f>
         <v>512</v>
       </c>
-      <c r="I14" s="134" t="n">
+      <c r="I14" s="135" t="n">
         <f aca="false">SUM(I8:I13)</f>
         <v>312</v>
       </c>
-      <c r="J14" s="134" t="n">
+      <c r="J14" s="135" t="n">
         <f aca="false">SUM(J8:J13)</f>
         <v>371.37</v>
       </c>
-      <c r="K14" s="135" t="n">
+      <c r="K14" s="136" t="n">
         <f aca="false">SUM(K8:K13)</f>
         <v>140</v>
       </c>
@@ -34383,236 +34388,236 @@
         <f aca="false">SUM(L8:L13)</f>
         <v>2856.085</v>
       </c>
-      <c r="M14" s="127" t="s">
+      <c r="M14" s="128" t="s">
         <v>651</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="136" t="s">
+      <c r="A17" s="137" t="s">
         <v>652</v>
       </c>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="136"/>
+      <c r="B17" s="137"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
+      <c r="H17" s="137"/>
+      <c r="I17" s="137"/>
+      <c r="J17" s="137"/>
+      <c r="K17" s="137"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="124"/>
-      <c r="B18" s="124" t="s">
+      <c r="A18" s="125"/>
+      <c r="B18" s="125" t="s">
         <v>653</v>
       </c>
-      <c r="D18" s="125" t="s">
+      <c r="D18" s="126" t="s">
         <v>654</v>
       </c>
-      <c r="F18" s="125" t="s">
+      <c r="F18" s="126" t="s">
         <v>655</v>
       </c>
-      <c r="G18" s="125" t="s">
+      <c r="G18" s="126" t="s">
         <v>656</v>
       </c>
-      <c r="H18" s="125" t="s">
+      <c r="H18" s="126" t="s">
         <v>657</v>
       </c>
-      <c r="J18" s="125" t="s">
+      <c r="J18" s="126" t="s">
         <v>658</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="116" t="s">
+      <c r="A19" s="117" t="s">
         <v>659</v>
       </c>
-      <c r="B19" s="126" t="s">
+      <c r="B19" s="127" t="s">
         <v>660</v>
       </c>
-      <c r="D19" s="137" t="s">
+      <c r="D19" s="138" t="s">
         <v>661</v>
       </c>
-      <c r="F19" s="138" t="s">
+      <c r="F19" s="139" t="s">
         <v>662</v>
       </c>
-      <c r="G19" s="139" t="n">
+      <c r="G19" s="140" t="n">
         <v>8</v>
       </c>
-      <c r="H19" s="129" t="n">
+      <c r="H19" s="130" t="n">
         <f aca="false">8*$C$4</f>
         <v>160</v>
       </c>
-      <c r="J19" s="132" t="n">
+      <c r="J19" s="133" t="n">
         <f aca="false">H19*7</f>
         <v>1120</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="116"/>
-      <c r="B20" s="126" t="s">
+      <c r="A20" s="117"/>
+      <c r="B20" s="127" t="s">
         <v>663</v>
       </c>
-      <c r="D20" s="137" t="s">
+      <c r="D20" s="138" t="s">
         <v>664</v>
       </c>
-      <c r="F20" s="138" t="s">
+      <c r="F20" s="139" t="s">
         <v>662</v>
       </c>
-      <c r="G20" s="139" t="n">
+      <c r="G20" s="140" t="n">
         <v>8</v>
       </c>
-      <c r="H20" s="129" t="n">
+      <c r="H20" s="130" t="n">
         <f aca="false">8*$C$4</f>
         <v>160</v>
       </c>
-      <c r="J20" s="132" t="n">
+      <c r="J20" s="133" t="n">
         <f aca="false">H20*7</f>
         <v>1120</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="116"/>
-      <c r="B21" s="126" t="s">
+      <c r="A21" s="117"/>
+      <c r="B21" s="127" t="s">
         <v>665</v>
       </c>
-      <c r="D21" s="137" t="s">
+      <c r="D21" s="138" t="s">
         <v>666</v>
       </c>
-      <c r="F21" s="138" t="s">
+      <c r="F21" s="139" t="s">
         <v>667</v>
       </c>
-      <c r="G21" s="139" t="n">
+      <c r="G21" s="140" t="n">
         <v>4</v>
       </c>
-      <c r="H21" s="129" t="n">
+      <c r="H21" s="130" t="n">
         <f aca="false">4*$E$4</f>
         <v>100</v>
       </c>
-      <c r="J21" s="132" t="n">
+      <c r="J21" s="133" t="n">
         <f aca="false">H21*7</f>
         <v>700</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="140" t="s">
+      <c r="A22" s="141" t="s">
         <v>668</v>
       </c>
-      <c r="B22" s="100"/>
-      <c r="D22" s="100"/>
-      <c r="F22" s="100"/>
-      <c r="G22" s="135" t="n">
+      <c r="B22" s="101"/>
+      <c r="D22" s="101"/>
+      <c r="F22" s="101"/>
+      <c r="G22" s="136" t="n">
         <f aca="false">G19+G20+G21</f>
         <v>20</v>
       </c>
-      <c r="H22" s="134" t="n">
+      <c r="H22" s="135" t="n">
         <f aca="false">H19+H20+H21</f>
         <v>420</v>
       </c>
-      <c r="J22" s="134" t="n">
+      <c r="J22" s="135" t="n">
         <f aca="false">H22*7</f>
         <v>2940</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="140" t="s">
+      <c r="A24" s="141" t="s">
         <v>669</v>
       </c>
-      <c r="B24" s="141" t="s">
+      <c r="B24" s="142" t="s">
         <v>670</v>
       </c>
-      <c r="C24" s="100"/>
-      <c r="D24" s="142" t="s">
+      <c r="C24" s="101"/>
+      <c r="D24" s="143" t="s">
         <v>671</v>
       </c>
-      <c r="E24" s="100"/>
-      <c r="F24" s="143" t="s">
+      <c r="E24" s="101"/>
+      <c r="F24" s="144" t="s">
         <v>672</v>
       </c>
-      <c r="G24" s="144" t="n">
+      <c r="G24" s="145" t="n">
         <v>10</v>
       </c>
-      <c r="H24" s="145" t="n">
+      <c r="H24" s="146" t="n">
         <f aca="false">10*$C$4</f>
         <v>200</v>
       </c>
-      <c r="I24" s="100"/>
-      <c r="J24" s="134" t="n">
+      <c r="I24" s="101"/>
+      <c r="J24" s="135" t="n">
         <f aca="false">H24*7</f>
         <v>1400</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="146"/>
-      <c r="B25" s="147" t="s">
+      <c r="A25" s="147"/>
+      <c r="B25" s="148" t="s">
         <v>673</v>
       </c>
-      <c r="C25" s="148"/>
-      <c r="D25" s="149" t="s">
+      <c r="C25" s="149"/>
+      <c r="D25" s="150" t="s">
         <v>674</v>
       </c>
-      <c r="E25" s="148"/>
-      <c r="F25" s="150" t="s">
+      <c r="E25" s="149"/>
+      <c r="F25" s="151" t="s">
         <v>675</v>
       </c>
-      <c r="G25" s="151" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="148"/>
-      <c r="J25" s="153" t="n">
+      <c r="G25" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="149"/>
+      <c r="J25" s="154" t="n">
         <f aca="false">H25*7</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="140" t="s">
+      <c r="A26" s="141" t="s">
         <v>676</v>
       </c>
-      <c r="B26" s="100"/>
-      <c r="D26" s="100"/>
-      <c r="F26" s="100"/>
-      <c r="G26" s="135" t="n">
+      <c r="B26" s="101"/>
+      <c r="D26" s="101"/>
+      <c r="F26" s="101"/>
+      <c r="G26" s="136" t="n">
         <v>10</v>
       </c>
-      <c r="H26" s="134" t="n">
+      <c r="H26" s="135" t="n">
         <f aca="false">10*$C$4</f>
         <v>200</v>
       </c>
-      <c r="J26" s="134" t="n">
+      <c r="J26" s="135" t="n">
         <f aca="false">H26*7</f>
         <v>1400</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="154" t="s">
+      <c r="A28" s="155" t="s">
         <v>677</v>
       </c>
-      <c r="B28" s="154"/>
-      <c r="C28" s="154"/>
-      <c r="D28" s="154"/>
-      <c r="E28" s="154"/>
-      <c r="F28" s="154"/>
-      <c r="G28" s="154"/>
-      <c r="H28" s="154"/>
-      <c r="I28" s="154"/>
-      <c r="J28" s="154"/>
-      <c r="K28" s="154"/>
+      <c r="B28" s="155"/>
+      <c r="C28" s="155"/>
+      <c r="D28" s="155"/>
+      <c r="E28" s="155"/>
+      <c r="F28" s="155"/>
+      <c r="G28" s="155"/>
+      <c r="H28" s="155"/>
+      <c r="I28" s="155"/>
+      <c r="J28" s="155"/>
+      <c r="K28" s="155"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="154"/>
-      <c r="B29" s="154"/>
-      <c r="C29" s="154"/>
-      <c r="D29" s="154"/>
-      <c r="E29" s="154"/>
-      <c r="F29" s="154"/>
-      <c r="G29" s="154"/>
-      <c r="H29" s="154"/>
-      <c r="I29" s="154"/>
-      <c r="J29" s="154"/>
-      <c r="K29" s="154"/>
+      <c r="A29" s="155"/>
+      <c r="B29" s="155"/>
+      <c r="C29" s="155"/>
+      <c r="D29" s="155"/>
+      <c r="E29" s="155"/>
+      <c r="F29" s="155"/>
+      <c r="G29" s="155"/>
+      <c r="H29" s="155"/>
+      <c r="I29" s="155"/>
+      <c r="J29" s="155"/>
+      <c r="K29" s="155"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -34644,7 +34649,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="156" t="s">
         <v>678</v>
       </c>
       <c r="B1" s="38"/>
@@ -34652,15 +34657,15 @@
       <c r="D1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="156" t="s">
+      <c r="A2" s="157" t="s">
         <v>679</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="86" t="s">
         <v>680</v>
       </c>
       <c r="B4" s="43" t="s">
@@ -34677,102 +34682,102 @@
       <c r="A5" s="44" t="s">
         <v>682</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="101" t="s">
+      <c r="A6" s="102" t="s">
         <v>683</v>
       </c>
-      <c r="B6" s="109" t="n">
+      <c r="B6" s="110" t="n">
         <v>119121</v>
       </c>
-      <c r="C6" s="109" t="n">
+      <c r="C6" s="110" t="n">
         <f aca="false">B6/12</f>
         <v>9926.75</v>
       </c>
-      <c r="D6" s="157" t="n">
+      <c r="D6" s="158" t="n">
         <f aca="false">B6/258287</f>
         <v>0.461196266169029</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="101" t="s">
+      <c r="A7" s="102" t="s">
         <v>684</v>
       </c>
-      <c r="B7" s="109" t="n">
+      <c r="B7" s="110" t="n">
         <v>133545</v>
       </c>
-      <c r="C7" s="109" t="n">
+      <c r="C7" s="110" t="n">
         <f aca="false">B7/12</f>
         <v>11128.75</v>
       </c>
-      <c r="D7" s="157" t="n">
+      <c r="D7" s="158" t="n">
         <f aca="false">B7/258287</f>
         <v>0.517041120923624</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="102" t="s">
         <v>685</v>
       </c>
-      <c r="B8" s="109" t="n">
+      <c r="B8" s="110" t="n">
         <v>17887</v>
       </c>
-      <c r="C8" s="109" t="n">
+      <c r="C8" s="110" t="n">
         <f aca="false">B8/12</f>
         <v>1490.58333333333</v>
       </c>
-      <c r="D8" s="157" t="n">
+      <c r="D8" s="158" t="n">
         <f aca="false">B8/258287</f>
         <v>0.0692524207567551</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="101" t="s">
+      <c r="A9" s="102" t="s">
         <v>686</v>
       </c>
-      <c r="B9" s="109" t="n">
+      <c r="B9" s="110" t="n">
         <v>6836</v>
       </c>
-      <c r="C9" s="109" t="n">
+      <c r="C9" s="110" t="n">
         <f aca="false">B9/12</f>
         <v>569.666666666667</v>
       </c>
-      <c r="D9" s="157" t="n">
+      <c r="D9" s="158" t="n">
         <f aca="false">B9/258287</f>
         <v>0.026466682411426</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="102" t="s">
         <v>687</v>
       </c>
-      <c r="B10" s="109" t="n">
+      <c r="B10" s="110" t="n">
         <v>-20307</v>
       </c>
-      <c r="C10" s="109" t="n">
+      <c r="C10" s="110" t="n">
         <f aca="false">B10/12</f>
         <v>-1692.25</v>
       </c>
-      <c r="D10" s="157" t="n">
+      <c r="D10" s="158" t="n">
         <f aca="false">B10/258287</f>
         <v>-0.0786218431434799</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="101" t="s">
+      <c r="A11" s="102" t="s">
         <v>688</v>
       </c>
-      <c r="B11" s="109" t="n">
+      <c r="B11" s="110" t="n">
         <v>1204</v>
       </c>
-      <c r="C11" s="109" t="n">
+      <c r="C11" s="110" t="n">
         <f aca="false">B11/12</f>
         <v>100.333333333333</v>
       </c>
-      <c r="D11" s="157" t="n">
+      <c r="D11" s="158" t="n">
         <f aca="false">B11/258287</f>
         <v>0.00466148122050277</v>
       </c>
@@ -34784,11 +34789,11 @@
       <c r="B12" s="45" t="n">
         <v>258287</v>
       </c>
-      <c r="C12" s="158" t="n">
+      <c r="C12" s="159" t="n">
         <f aca="false">B12/12</f>
         <v>21523.9166666667</v>
       </c>
-      <c r="D12" s="159" t="n">
+      <c r="D12" s="160" t="n">
         <f aca="false">B12/258287</f>
         <v>1</v>
       </c>
@@ -34802,70 +34807,70 @@
       <c r="A14" s="44" t="s">
         <v>690</v>
       </c>
-      <c r="B14" s="160"/>
-      <c r="C14" s="161"/>
-      <c r="D14" s="161"/>
+      <c r="B14" s="161"/>
+      <c r="C14" s="162"/>
+      <c r="D14" s="162"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="101" t="s">
+      <c r="A15" s="102" t="s">
         <v>691</v>
       </c>
-      <c r="B15" s="109" t="n">
+      <c r="B15" s="110" t="n">
         <v>48655</v>
       </c>
-      <c r="C15" s="109" t="n">
+      <c r="C15" s="110" t="n">
         <f aca="false">B15/12</f>
         <v>4054.58333333333</v>
       </c>
-      <c r="D15" s="157" t="n">
+      <c r="D15" s="158" t="n">
         <f aca="false">B15/258287</f>
         <v>0.188375721581032</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="101" t="s">
+      <c r="A16" s="102" t="s">
         <v>692</v>
       </c>
-      <c r="B16" s="109" t="n">
+      <c r="B16" s="110" t="n">
         <v>27428</v>
       </c>
-      <c r="C16" s="109" t="n">
+      <c r="C16" s="110" t="n">
         <f aca="false">B16/12</f>
         <v>2285.66666666667</v>
       </c>
-      <c r="D16" s="157" t="n">
+      <c r="D16" s="158" t="n">
         <f aca="false">B16/258287</f>
         <v>0.106191949265739</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="101" t="s">
+      <c r="A17" s="102" t="s">
         <v>693</v>
       </c>
-      <c r="B17" s="109" t="n">
+      <c r="B17" s="110" t="n">
         <v>5516</v>
       </c>
-      <c r="C17" s="109" t="n">
+      <c r="C17" s="110" t="n">
         <f aca="false">B17/12</f>
         <v>459.666666666667</v>
       </c>
-      <c r="D17" s="157" t="n">
+      <c r="D17" s="158" t="n">
         <f aca="false">B17/258287</f>
         <v>0.0213560883823034</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="101" t="s">
+      <c r="A18" s="102" t="s">
         <v>694</v>
       </c>
-      <c r="B18" s="109" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="109" t="n">
+      <c r="B18" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="110" t="n">
         <f aca="false">B18/12</f>
         <v>0</v>
       </c>
-      <c r="D18" s="157" t="n">
+      <c r="D18" s="158" t="n">
         <f aca="false">B18/258287</f>
         <v>0</v>
       </c>
@@ -34877,11 +34882,11 @@
       <c r="B19" s="45" t="n">
         <v>81599</v>
       </c>
-      <c r="C19" s="158" t="n">
+      <c r="C19" s="159" t="n">
         <f aca="false">B19/12</f>
         <v>6799.91666666667</v>
       </c>
-      <c r="D19" s="159" t="n">
+      <c r="D19" s="160" t="n">
         <f aca="false">B19/258287</f>
         <v>0.315923759229075</v>
       </c>
@@ -34893,11 +34898,11 @@
       <c r="B20" s="45" t="n">
         <v>176688</v>
       </c>
-      <c r="C20" s="158" t="n">
+      <c r="C20" s="159" t="n">
         <f aca="false">B20/12</f>
         <v>14724</v>
       </c>
-      <c r="D20" s="159" t="n">
+      <c r="D20" s="160" t="n">
         <f aca="false">B20/258287</f>
         <v>0.684076240770925</v>
       </c>
@@ -34911,54 +34916,54 @@
       <c r="A22" s="44" t="s">
         <v>290</v>
       </c>
-      <c r="B22" s="160"/>
-      <c r="C22" s="161"/>
-      <c r="D22" s="161"/>
+      <c r="B22" s="161"/>
+      <c r="C22" s="162"/>
+      <c r="D22" s="162"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="101" t="s">
+      <c r="A23" s="102" t="s">
         <v>697</v>
       </c>
-      <c r="B23" s="109" t="n">
+      <c r="B23" s="110" t="n">
         <v>142124</v>
       </c>
-      <c r="C23" s="109" t="n">
+      <c r="C23" s="110" t="n">
         <f aca="false">B23/12</f>
         <v>11843.6666666667</v>
       </c>
-      <c r="D23" s="157" t="n">
+      <c r="D23" s="158" t="n">
         <f aca="false">B23/258287</f>
         <v>0.550256110450778</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="101" t="s">
+      <c r="A24" s="102" t="s">
         <v>698</v>
       </c>
-      <c r="B24" s="109" t="n">
+      <c r="B24" s="110" t="n">
         <v>16219</v>
       </c>
-      <c r="C24" s="109" t="n">
+      <c r="C24" s="110" t="n">
         <f aca="false">B24/12</f>
         <v>1351.58333333333</v>
       </c>
-      <c r="D24" s="157" t="n">
+      <c r="D24" s="158" t="n">
         <f aca="false">B24/258287</f>
         <v>0.0627944883017728</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="101" t="s">
+      <c r="A25" s="102" t="s">
         <v>699</v>
       </c>
-      <c r="B25" s="109" t="n">
+      <c r="B25" s="110" t="n">
         <v>6514</v>
       </c>
-      <c r="C25" s="109" t="n">
+      <c r="C25" s="110" t="n">
         <f aca="false">B25/12</f>
         <v>542.833333333333</v>
       </c>
-      <c r="D25" s="157" t="n">
+      <c r="D25" s="158" t="n">
         <f aca="false">B25/258287</f>
         <v>0.0252200072012916</v>
       </c>
@@ -34970,11 +34975,11 @@
       <c r="B26" s="45" t="n">
         <v>164857</v>
       </c>
-      <c r="C26" s="158" t="n">
+      <c r="C26" s="159" t="n">
         <f aca="false">B26/12</f>
         <v>13738.0833333333</v>
       </c>
-      <c r="D26" s="159" t="n">
+      <c r="D26" s="160" t="n">
         <f aca="false">B26/258287</f>
         <v>0.638270605953842</v>
       </c>
@@ -34988,70 +34993,70 @@
       <c r="A28" s="44" t="s">
         <v>701</v>
       </c>
-      <c r="B28" s="160"/>
-      <c r="C28" s="161"/>
-      <c r="D28" s="161"/>
+      <c r="B28" s="161"/>
+      <c r="C28" s="162"/>
+      <c r="D28" s="162"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="101" t="s">
+      <c r="A29" s="102" t="s">
         <v>702</v>
       </c>
-      <c r="B29" s="109" t="n">
+      <c r="B29" s="110" t="n">
         <v>44540</v>
       </c>
-      <c r="C29" s="109" t="n">
+      <c r="C29" s="110" t="n">
         <f aca="false">B29/12</f>
         <v>3711.66666666667</v>
       </c>
-      <c r="D29" s="157" t="n">
+      <c r="D29" s="158" t="n">
         <f aca="false">B29/258287</f>
         <v>0.172443831861456</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="101" t="s">
+      <c r="A30" s="102" t="s">
         <v>703</v>
       </c>
-      <c r="B30" s="109" t="n">
+      <c r="B30" s="110" t="n">
         <v>11918</v>
       </c>
-      <c r="C30" s="109" t="n">
+      <c r="C30" s="110" t="n">
         <f aca="false">B30/12</f>
         <v>993.166666666667</v>
       </c>
-      <c r="D30" s="157" t="n">
+      <c r="D30" s="158" t="n">
         <f aca="false">B30/258287</f>
         <v>0.0461424694235482</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="101" t="s">
+      <c r="A31" s="102" t="s">
         <v>704</v>
       </c>
-      <c r="B31" s="109" t="n">
+      <c r="B31" s="110" t="n">
         <v>2912</v>
       </c>
-      <c r="C31" s="109" t="n">
+      <c r="C31" s="110" t="n">
         <f aca="false">B31/12</f>
         <v>242.666666666667</v>
       </c>
-      <c r="D31" s="157" t="n">
+      <c r="D31" s="158" t="n">
         <f aca="false">B31/258287</f>
         <v>0.011274280161216</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="101" t="s">
+      <c r="A32" s="102" t="s">
         <v>705</v>
       </c>
-      <c r="B32" s="109" t="n">
+      <c r="B32" s="110" t="n">
         <v>30305</v>
       </c>
-      <c r="C32" s="109" t="n">
+      <c r="C32" s="110" t="n">
         <f aca="false">B32/12</f>
         <v>2525.41666666667</v>
       </c>
-      <c r="D32" s="157" t="n">
+      <c r="D32" s="158" t="n">
         <f aca="false">B32/258287</f>
         <v>0.117330721251941</v>
       </c>
@@ -35063,116 +35068,116 @@
       <c r="B33" s="45" t="n">
         <v>89675</v>
       </c>
-      <c r="C33" s="158" t="n">
+      <c r="C33" s="159" t="n">
         <f aca="false">B33/12</f>
         <v>7472.91666666667</v>
       </c>
-      <c r="D33" s="159" t="n">
+      <c r="D33" s="160" t="n">
         <f aca="false">B33/258287</f>
         <v>0.347191302698161</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="162" t="s">
+      <c r="A34" s="163" t="s">
         <v>707</v>
       </c>
-      <c r="B34" s="109" t="n">
+      <c r="B34" s="110" t="n">
         <v>10012</v>
       </c>
-      <c r="C34" s="109" t="n">
+      <c r="C34" s="110" t="n">
         <f aca="false">B34/12</f>
         <v>834.333333333333</v>
       </c>
-      <c r="D34" s="157" t="n">
+      <c r="D34" s="158" t="n">
         <f aca="false">B34/258287</f>
         <v>0.0387630813784666</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="163" t="s">
+      <c r="A35" s="164" t="s">
         <v>708</v>
       </c>
-      <c r="B35" s="87" t="n">
+      <c r="B35" s="88" t="n">
         <v>5657</v>
       </c>
-      <c r="C35" s="109" t="n">
+      <c r="C35" s="110" t="n">
         <f aca="false">B35/12</f>
         <v>471.416666666667</v>
       </c>
-      <c r="D35" s="157" t="n">
+      <c r="D35" s="158" t="n">
         <f aca="false">B35/258287</f>
         <v>0.0219019927445051</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="164" t="s">
+      <c r="A37" s="165" t="s">
         <v>709</v>
       </c>
-      <c r="B37" s="111" t="n">
+      <c r="B37" s="112" t="n">
         <v>-93513</v>
       </c>
-      <c r="C37" s="165" t="n">
+      <c r="C37" s="166" t="n">
         <f aca="false">B37/12</f>
         <v>-7792.75</v>
       </c>
-      <c r="D37" s="159" t="n">
+      <c r="D37" s="160" t="n">
         <f aca="false">B37/258287</f>
         <v>-0.36205074200405</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="101" t="s">
+      <c r="A38" s="102" t="s">
         <v>710</v>
       </c>
-      <c r="B38" s="109" t="n">
+      <c r="B38" s="110" t="n">
         <v>-48000</v>
       </c>
-      <c r="C38" s="109" t="n">
+      <c r="C38" s="110" t="n">
         <f aca="false">B38/12</f>
         <v>-4000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="101" t="s">
+      <c r="A39" s="102" t="s">
         <v>711</v>
       </c>
-      <c r="B39" s="109" t="n">
+      <c r="B39" s="110" t="n">
         <v>-15642</v>
       </c>
-      <c r="C39" s="109" t="n">
+      <c r="C39" s="110" t="n">
         <f aca="false">B39/12</f>
         <v>-1303.5</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="164" t="s">
+      <c r="A40" s="165" t="s">
         <v>712</v>
       </c>
-      <c r="B40" s="111" t="n">
+      <c r="B40" s="112" t="n">
         <v>-157155</v>
       </c>
-      <c r="C40" s="165" t="n">
+      <c r="C40" s="166" t="n">
         <f aca="false">B40/12</f>
         <v>-13096.25</v>
       </c>
-      <c r="D40" s="159" t="n">
+      <c r="D40" s="160" t="n">
         <f aca="false">B40/258287</f>
         <v>-0.60845106412634</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="166" t="s">
+      <c r="A42" s="167" t="s">
         <v>713</v>
       </c>
-      <c r="B42" s="166"/>
-      <c r="C42" s="166"/>
-      <c r="D42" s="166"/>
+      <c r="B42" s="167"/>
+      <c r="C42" s="167"/>
+      <c r="D42" s="167"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="166"/>
-      <c r="B43" s="166"/>
-      <c r="C43" s="166"/>
-      <c r="D43" s="166"/>
+      <c r="A43" s="167"/>
+      <c r="B43" s="167"/>
+      <c r="C43" s="167"/>
+      <c r="D43" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -35203,7 +35208,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="99" t="s">
         <v>714</v>
       </c>
       <c r="B1" s="38"/>
@@ -35216,663 +35221,663 @@
       <c r="I1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="100" t="s">
         <v>715</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="124" t="s">
+      <c r="A4" s="125" t="s">
         <v>716</v>
       </c>
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="125" t="s">
         <v>717</v>
       </c>
-      <c r="C4" s="125" t="s">
+      <c r="C4" s="126" t="s">
         <v>718</v>
       </c>
-      <c r="D4" s="125" t="s">
+      <c r="D4" s="126" t="s">
         <v>719</v>
       </c>
-      <c r="E4" s="125" t="s">
+      <c r="E4" s="126" t="s">
         <v>720</v>
       </c>
-      <c r="F4" s="125" t="s">
+      <c r="F4" s="126" t="s">
         <v>721</v>
       </c>
-      <c r="G4" s="125" t="s">
+      <c r="G4" s="126" t="s">
         <v>722</v>
       </c>
-      <c r="H4" s="125" t="s">
+      <c r="H4" s="126" t="s">
         <v>723</v>
       </c>
-      <c r="I4" s="125" t="s">
+      <c r="I4" s="126" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="168" t="s">
         <v>725</v>
       </c>
-      <c r="B5" s="168"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="169"/>
-      <c r="E5" s="169"/>
-      <c r="F5" s="169"/>
-      <c r="G5" s="169"/>
-      <c r="H5" s="169"/>
-      <c r="I5" s="169"/>
+      <c r="B5" s="169"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="170"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="170"/>
+      <c r="H5" s="170"/>
+      <c r="I5" s="170"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="126" t="s">
+      <c r="A6" s="127" t="s">
         <v>726</v>
       </c>
-      <c r="B6" s="122" t="s">
+      <c r="B6" s="123" t="s">
         <v>727</v>
       </c>
-      <c r="C6" s="170" t="n">
+      <c r="C6" s="171" t="n">
         <v>5728</v>
       </c>
-      <c r="D6" s="171" t="n">
+      <c r="D6" s="172" t="n">
         <f aca="false">IF(C6=0,0,E6/C6)</f>
         <v>4.5</v>
       </c>
-      <c r="E6" s="109" t="n">
+      <c r="E6" s="110" t="n">
         <v>25776</v>
       </c>
-      <c r="F6" s="172" t="n">
+      <c r="F6" s="173" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="171" t="n">
+      <c r="G6" s="172" t="n">
         <f aca="false">D6+F6</f>
         <v>5</v>
       </c>
-      <c r="H6" s="109" t="n">
+      <c r="H6" s="110" t="n">
         <f aca="false">E6+I6</f>
         <v>28640</v>
       </c>
-      <c r="I6" s="87" t="n">
+      <c r="I6" s="88" t="n">
         <f aca="false">C6*F6</f>
         <v>2864</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="127" t="s">
         <v>728</v>
       </c>
-      <c r="B7" s="122" t="s">
+      <c r="B7" s="123" t="s">
         <v>727</v>
       </c>
-      <c r="C7" s="170" t="n">
+      <c r="C7" s="171" t="n">
         <v>3537</v>
       </c>
-      <c r="D7" s="171" t="n">
+      <c r="D7" s="172" t="n">
         <f aca="false">IF(C7=0,0,E7/C7)</f>
         <v>3</v>
       </c>
-      <c r="E7" s="109" t="n">
+      <c r="E7" s="110" t="n">
         <v>10611</v>
       </c>
-      <c r="F7" s="172" t="n">
+      <c r="F7" s="173" t="n">
         <v>0.5</v>
       </c>
-      <c r="G7" s="171" t="n">
+      <c r="G7" s="172" t="n">
         <f aca="false">D7+F7</f>
         <v>3.5</v>
       </c>
-      <c r="H7" s="109" t="n">
+      <c r="H7" s="110" t="n">
         <f aca="false">E7+I7</f>
         <v>12379.5</v>
       </c>
-      <c r="I7" s="87" t="n">
+      <c r="I7" s="88" t="n">
         <f aca="false">C7*F7</f>
         <v>1768.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="127" t="s">
         <v>729</v>
       </c>
-      <c r="B8" s="122" t="s">
+      <c r="B8" s="123" t="s">
         <v>727</v>
       </c>
-      <c r="C8" s="170" t="n">
+      <c r="C8" s="171" t="n">
         <v>1869</v>
       </c>
-      <c r="D8" s="171" t="n">
+      <c r="D8" s="172" t="n">
         <f aca="false">IF(C8=0,0,E8/C8)</f>
         <v>4.5</v>
       </c>
-      <c r="E8" s="109" t="n">
+      <c r="E8" s="110" t="n">
         <v>8410.5</v>
       </c>
-      <c r="F8" s="172" t="n">
+      <c r="F8" s="173" t="n">
         <v>0.45</v>
       </c>
-      <c r="G8" s="171" t="n">
+      <c r="G8" s="172" t="n">
         <f aca="false">D8+F8</f>
         <v>4.95</v>
       </c>
-      <c r="H8" s="109" t="n">
+      <c r="H8" s="110" t="n">
         <f aca="false">E8+I8</f>
         <v>9251.55</v>
       </c>
-      <c r="I8" s="87" t="n">
+      <c r="I8" s="88" t="n">
         <f aca="false">C8*F8</f>
         <v>841.05</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="126" t="s">
+      <c r="A9" s="127" t="s">
         <v>730</v>
       </c>
-      <c r="B9" s="122" t="s">
+      <c r="B9" s="123" t="s">
         <v>727</v>
       </c>
-      <c r="C9" s="170" t="n">
+      <c r="C9" s="171" t="n">
         <v>1305</v>
       </c>
-      <c r="D9" s="171" t="n">
+      <c r="D9" s="172" t="n">
         <f aca="false">IF(C9=0,0,E9/C9)</f>
         <v>4.75</v>
       </c>
-      <c r="E9" s="109" t="n">
+      <c r="E9" s="110" t="n">
         <v>6198.75</v>
       </c>
-      <c r="F9" s="172" t="n">
+      <c r="F9" s="173" t="n">
         <v>0.5</v>
       </c>
-      <c r="G9" s="171" t="n">
+      <c r="G9" s="172" t="n">
         <f aca="false">D9+F9</f>
         <v>5.25</v>
       </c>
-      <c r="H9" s="109" t="n">
+      <c r="H9" s="110" t="n">
         <f aca="false">E9+I9</f>
         <v>6851.25</v>
       </c>
-      <c r="I9" s="87" t="n">
+      <c r="I9" s="88" t="n">
         <f aca="false">C9*F9</f>
         <v>652.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="126" t="s">
+      <c r="A10" s="127" t="s">
         <v>731</v>
       </c>
-      <c r="B10" s="122" t="s">
+      <c r="B10" s="123" t="s">
         <v>727</v>
       </c>
-      <c r="C10" s="170" t="n">
+      <c r="C10" s="171" t="n">
         <v>1212</v>
       </c>
-      <c r="D10" s="171" t="n">
+      <c r="D10" s="172" t="n">
         <f aca="false">IF(C10=0,0,E10/C10)</f>
         <v>4</v>
       </c>
-      <c r="E10" s="109" t="n">
+      <c r="E10" s="110" t="n">
         <v>4848</v>
       </c>
-      <c r="F10" s="172" t="n">
+      <c r="F10" s="173" t="n">
         <v>0.25</v>
       </c>
-      <c r="G10" s="171" t="n">
+      <c r="G10" s="172" t="n">
         <f aca="false">D10+F10</f>
         <v>4.25</v>
       </c>
-      <c r="H10" s="109" t="n">
+      <c r="H10" s="110" t="n">
         <f aca="false">E10+I10</f>
         <v>5151</v>
       </c>
-      <c r="I10" s="87" t="n">
+      <c r="I10" s="88" t="n">
         <f aca="false">C10*F10</f>
         <v>303</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="126" t="s">
+      <c r="A11" s="127" t="s">
         <v>732</v>
       </c>
-      <c r="B11" s="122" t="s">
+      <c r="B11" s="123" t="s">
         <v>727</v>
       </c>
-      <c r="C11" s="170" t="n">
+      <c r="C11" s="171" t="n">
         <v>888</v>
       </c>
-      <c r="D11" s="171" t="n">
+      <c r="D11" s="172" t="n">
         <f aca="false">IF(C11=0,0,E11/C11)</f>
         <v>6</v>
       </c>
-      <c r="E11" s="109" t="n">
+      <c r="E11" s="110" t="n">
         <v>5328</v>
       </c>
-      <c r="F11" s="172" t="n">
+      <c r="F11" s="173" t="n">
         <v>0.5</v>
       </c>
-      <c r="G11" s="171" t="n">
+      <c r="G11" s="172" t="n">
         <f aca="false">D11+F11</f>
         <v>6.5</v>
       </c>
-      <c r="H11" s="109" t="n">
+      <c r="H11" s="110" t="n">
         <f aca="false">E11+I11</f>
         <v>5772</v>
       </c>
-      <c r="I11" s="87" t="n">
+      <c r="I11" s="88" t="n">
         <f aca="false">C11*F11</f>
         <v>444</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="126" t="s">
+      <c r="A12" s="127" t="s">
         <v>733</v>
       </c>
-      <c r="B12" s="122" t="s">
+      <c r="B12" s="123" t="s">
         <v>727</v>
       </c>
-      <c r="C12" s="170" t="n">
+      <c r="C12" s="171" t="n">
         <v>319</v>
       </c>
-      <c r="D12" s="171" t="n">
+      <c r="D12" s="172" t="n">
         <f aca="false">IF(C12=0,0,E12/C12)</f>
         <v>5.25</v>
       </c>
-      <c r="E12" s="109" t="n">
+      <c r="E12" s="110" t="n">
         <v>1674.75</v>
       </c>
-      <c r="F12" s="172" t="n">
+      <c r="F12" s="173" t="n">
         <v>0.25</v>
       </c>
-      <c r="G12" s="171" t="n">
+      <c r="G12" s="172" t="n">
         <f aca="false">D12+F12</f>
         <v>5.5</v>
       </c>
-      <c r="H12" s="109" t="n">
+      <c r="H12" s="110" t="n">
         <f aca="false">E12+I12</f>
         <v>1754.5</v>
       </c>
-      <c r="I12" s="87" t="n">
+      <c r="I12" s="88" t="n">
         <f aca="false">C12*F12</f>
         <v>79.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="126" t="s">
+      <c r="A13" s="127" t="s">
         <v>734</v>
       </c>
-      <c r="B13" s="122" t="s">
+      <c r="B13" s="123" t="s">
         <v>406</v>
       </c>
-      <c r="C13" s="170" t="n">
+      <c r="C13" s="171" t="n">
         <v>2352</v>
       </c>
-      <c r="D13" s="171" t="n">
+      <c r="D13" s="172" t="n">
         <f aca="false">IF(C13=0,0,E13/C13)</f>
         <v>10</v>
       </c>
-      <c r="E13" s="109" t="n">
+      <c r="E13" s="110" t="n">
         <v>23520</v>
       </c>
-      <c r="F13" s="172" t="n">
+      <c r="F13" s="173" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="171" t="n">
+      <c r="G13" s="172" t="n">
         <f aca="false">D13+F13</f>
         <v>11</v>
       </c>
-      <c r="H13" s="109" t="n">
+      <c r="H13" s="110" t="n">
         <f aca="false">E13+I13</f>
         <v>25872</v>
       </c>
-      <c r="I13" s="87" t="n">
+      <c r="I13" s="88" t="n">
         <f aca="false">C13*F13</f>
         <v>2352</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="126" t="s">
+      <c r="A14" s="127" t="s">
         <v>735</v>
       </c>
-      <c r="B14" s="122" t="s">
+      <c r="B14" s="123" t="s">
         <v>727</v>
       </c>
-      <c r="C14" s="170" t="n">
+      <c r="C14" s="171" t="n">
         <v>619</v>
       </c>
-      <c r="D14" s="173" t="n">
+      <c r="D14" s="174" t="n">
         <f aca="false">IF(C14=0,0,E14/C14)</f>
         <v>8</v>
       </c>
-      <c r="E14" s="109" t="n">
+      <c r="E14" s="110" t="n">
         <v>4952</v>
       </c>
-      <c r="F14" s="174" t="n">
+      <c r="F14" s="175" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="173" t="n">
+      <c r="G14" s="174" t="n">
         <f aca="false">D14+F14</f>
         <v>9</v>
       </c>
-      <c r="H14" s="109" t="n">
+      <c r="H14" s="110" t="n">
         <f aca="false">E14+I14</f>
         <v>5571</v>
       </c>
-      <c r="I14" s="87" t="n">
+      <c r="I14" s="88" t="n">
         <f aca="false">C14*F14</f>
         <v>619</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="126" t="s">
+      <c r="A15" s="127" t="s">
         <v>736</v>
       </c>
-      <c r="B15" s="122" t="s">
+      <c r="B15" s="123" t="s">
         <v>406</v>
       </c>
-      <c r="C15" s="175" t="n">
+      <c r="C15" s="176" t="n">
         <v>510</v>
       </c>
-      <c r="D15" s="173" t="n">
+      <c r="D15" s="174" t="n">
         <f aca="false">IF(C15=0,0,E15/C15)</f>
         <v>6</v>
       </c>
-      <c r="E15" s="176" t="n">
+      <c r="E15" s="177" t="n">
         <v>3060</v>
       </c>
-      <c r="F15" s="174" t="n">
+      <c r="F15" s="175" t="n">
         <v>0.5</v>
       </c>
-      <c r="G15" s="173" t="n">
+      <c r="G15" s="174" t="n">
         <f aca="false">D15+F15</f>
         <v>6.5</v>
       </c>
-      <c r="H15" s="176" t="n">
+      <c r="H15" s="177" t="n">
         <f aca="false">E15+I15</f>
         <v>3315</v>
       </c>
-      <c r="I15" s="177" t="n">
+      <c r="I15" s="178" t="n">
         <f aca="false">C15*F15</f>
         <v>255</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="167" t="s">
+      <c r="A16" s="168" t="s">
         <v>737</v>
       </c>
-      <c r="B16" s="168"/>
-      <c r="C16" s="168"/>
-      <c r="D16" s="168"/>
-      <c r="E16" s="168"/>
-      <c r="F16" s="168"/>
-      <c r="G16" s="168"/>
-      <c r="H16" s="168"/>
-      <c r="I16" s="168"/>
+      <c r="B16" s="169"/>
+      <c r="C16" s="169"/>
+      <c r="D16" s="169"/>
+      <c r="E16" s="169"/>
+      <c r="F16" s="169"/>
+      <c r="G16" s="169"/>
+      <c r="H16" s="169"/>
+      <c r="I16" s="169"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="126" t="s">
+      <c r="A17" s="127" t="s">
         <v>738</v>
       </c>
-      <c r="B17" s="122" t="s">
+      <c r="B17" s="123" t="s">
         <v>727</v>
       </c>
-      <c r="C17" s="170" t="n">
+      <c r="C17" s="171" t="n">
         <v>5211</v>
       </c>
-      <c r="D17" s="173" t="n">
+      <c r="D17" s="174" t="n">
         <f aca="false">IF(C17=0,0,E17/C17)</f>
         <v>5</v>
       </c>
-      <c r="E17" s="176" t="n">
+      <c r="E17" s="177" t="n">
         <v>26055</v>
       </c>
-      <c r="F17" s="174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="173" t="n">
+      <c r="F17" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="174" t="n">
         <f aca="false">D17+F17</f>
         <v>5</v>
       </c>
-      <c r="H17" s="176" t="n">
+      <c r="H17" s="177" t="n">
         <f aca="false">E17+I17</f>
         <v>26055</v>
       </c>
-      <c r="I17" s="177" t="n">
+      <c r="I17" s="178" t="n">
         <f aca="false">C17*F17</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="126" t="s">
+      <c r="A18" s="127" t="s">
         <v>739</v>
       </c>
-      <c r="B18" s="122" t="s">
+      <c r="B18" s="123" t="s">
         <v>406</v>
       </c>
-      <c r="C18" s="170" t="n">
+      <c r="C18" s="171" t="n">
         <v>1198</v>
       </c>
-      <c r="D18" s="173" t="n">
+      <c r="D18" s="174" t="n">
         <f aca="false">IF(C18=0,0,E18/C18)</f>
         <v>11.5</v>
       </c>
-      <c r="E18" s="176" t="n">
+      <c r="E18" s="177" t="n">
         <v>13777</v>
       </c>
-      <c r="F18" s="174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="173" t="n">
+      <c r="F18" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="174" t="n">
         <f aca="false">D18+F18</f>
         <v>11.5</v>
       </c>
-      <c r="H18" s="176" t="n">
+      <c r="H18" s="177" t="n">
         <f aca="false">E18+I18</f>
         <v>13777</v>
       </c>
-      <c r="I18" s="177" t="n">
+      <c r="I18" s="178" t="n">
         <f aca="false">C18*F18</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="126" t="s">
+      <c r="A19" s="127" t="s">
         <v>740</v>
       </c>
-      <c r="B19" s="122" t="s">
+      <c r="B19" s="123" t="s">
         <v>406</v>
       </c>
-      <c r="C19" s="170" t="n">
+      <c r="C19" s="171" t="n">
         <v>4396</v>
       </c>
-      <c r="D19" s="173" t="n">
+      <c r="D19" s="174" t="n">
         <f aca="false">IF(C19=0,0,E19/C19)</f>
         <v>4.31</v>
       </c>
-      <c r="E19" s="176" t="n">
+      <c r="E19" s="177" t="n">
         <v>18946.76</v>
       </c>
-      <c r="F19" s="174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="173" t="n">
+      <c r="F19" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="174" t="n">
         <f aca="false">D19+F19</f>
         <v>4.31</v>
       </c>
-      <c r="H19" s="176" t="n">
+      <c r="H19" s="177" t="n">
         <f aca="false">E19+I19</f>
         <v>18946.76</v>
       </c>
-      <c r="I19" s="177" t="n">
+      <c r="I19" s="178" t="n">
         <f aca="false">C19*F19</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="126" t="s">
+      <c r="A20" s="127" t="s">
         <v>579</v>
       </c>
-      <c r="B20" s="122" t="s">
+      <c r="B20" s="123" t="s">
         <v>406</v>
       </c>
-      <c r="C20" s="170" t="n">
+      <c r="C20" s="171" t="n">
         <v>1757</v>
       </c>
-      <c r="D20" s="173" t="n">
+      <c r="D20" s="174" t="n">
         <f aca="false">IF(C20=0,0,E20/C20)</f>
         <v>5.96</v>
       </c>
-      <c r="E20" s="176" t="n">
+      <c r="E20" s="177" t="n">
         <v>10471.72</v>
       </c>
-      <c r="F20" s="174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="173" t="n">
+      <c r="F20" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="174" t="n">
         <f aca="false">D20+F20</f>
         <v>5.96</v>
       </c>
-      <c r="H20" s="176" t="n">
+      <c r="H20" s="177" t="n">
         <f aca="false">E20+I20</f>
         <v>10471.72</v>
       </c>
-      <c r="I20" s="177" t="n">
+      <c r="I20" s="178" t="n">
         <f aca="false">C20*F20</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="126" t="s">
+      <c r="A21" s="127" t="s">
         <v>575</v>
       </c>
-      <c r="B21" s="122" t="s">
+      <c r="B21" s="123" t="s">
         <v>406</v>
       </c>
-      <c r="C21" s="175" t="n">
+      <c r="C21" s="176" t="n">
         <v>2519</v>
       </c>
-      <c r="D21" s="173" t="n">
+      <c r="D21" s="174" t="n">
         <f aca="false">IF(C21=0,0,E21/C21)</f>
         <v>4.43</v>
       </c>
-      <c r="E21" s="176" t="n">
+      <c r="E21" s="177" t="n">
         <v>11159.17</v>
       </c>
-      <c r="F21" s="174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="173" t="n">
+      <c r="F21" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="174" t="n">
         <f aca="false">D21+F21</f>
         <v>4.43</v>
       </c>
-      <c r="H21" s="176" t="n">
+      <c r="H21" s="177" t="n">
         <f aca="false">E21+I21</f>
         <v>11159.17</v>
       </c>
-      <c r="I21" s="177" t="n">
+      <c r="I21" s="178" t="n">
         <f aca="false">C21*F21</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="126" t="s">
+      <c r="A22" s="127" t="s">
         <v>741</v>
       </c>
-      <c r="B22" s="122" t="s">
+      <c r="B22" s="123" t="s">
         <v>727</v>
       </c>
-      <c r="C22" s="175" t="n">
+      <c r="C22" s="176" t="n">
         <v>4935</v>
       </c>
-      <c r="D22" s="173" t="n">
+      <c r="D22" s="174" t="n">
         <f aca="false">IF(C22=0,0,E22/C22)</f>
         <v>4.69</v>
       </c>
-      <c r="E22" s="176" t="n">
+      <c r="E22" s="177" t="n">
         <v>23145.15</v>
       </c>
-      <c r="F22" s="174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="173" t="n">
+      <c r="F22" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="174" t="n">
         <f aca="false">D22+F22</f>
         <v>4.69</v>
       </c>
-      <c r="H22" s="176" t="n">
+      <c r="H22" s="177" t="n">
         <f aca="false">E22+I22</f>
         <v>23145.15</v>
       </c>
-      <c r="I22" s="177" t="n">
+      <c r="I22" s="178" t="n">
         <f aca="false">C22*F22</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="126" t="s">
+      <c r="A23" s="127" t="s">
         <v>742</v>
       </c>
-      <c r="B23" s="122" t="s">
+      <c r="B23" s="123" t="s">
         <v>743</v>
       </c>
-      <c r="C23" s="170" t="n">
+      <c r="C23" s="171" t="n">
         <v>1309</v>
       </c>
-      <c r="D23" s="173" t="n">
+      <c r="D23" s="174" t="n">
         <f aca="false">IF(C23=0,0,E23/C23)</f>
         <v>13.1</v>
       </c>
-      <c r="E23" s="176" t="n">
+      <c r="E23" s="177" t="n">
         <v>17147.9</v>
       </c>
-      <c r="F23" s="174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="173" t="n">
+      <c r="F23" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="174" t="n">
         <f aca="false">D23+F23</f>
         <v>13.1</v>
       </c>
-      <c r="H23" s="176" t="n">
+      <c r="H23" s="177" t="n">
         <f aca="false">E23+I23</f>
         <v>17147.9</v>
       </c>
-      <c r="I23" s="177" t="n">
+      <c r="I23" s="178" t="n">
         <f aca="false">C23*F23</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="126" t="s">
+      <c r="A24" s="127" t="s">
         <v>744</v>
       </c>
-      <c r="B24" s="122" t="s">
+      <c r="B24" s="123" t="s">
         <v>406</v>
       </c>
-      <c r="C24" s="170" t="n">
+      <c r="C24" s="171" t="n">
         <v>845</v>
       </c>
-      <c r="D24" s="173" t="n">
+      <c r="D24" s="174" t="n">
         <f aca="false">IF(C24=0,0,E24/C24)</f>
         <v>6.05</v>
       </c>
-      <c r="E24" s="176" t="n">
+      <c r="E24" s="177" t="n">
         <v>5112.25</v>
       </c>
-      <c r="F24" s="174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="173" t="n">
+      <c r="F24" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="174" t="n">
         <f aca="false">D24+F24</f>
         <v>6.05</v>
       </c>
-      <c r="H24" s="176" t="n">
+      <c r="H24" s="177" t="n">
         <f aca="false">E24+I24</f>
         <v>5112.25</v>
       </c>
-      <c r="I24" s="177" t="n">
+      <c r="I24" s="178" t="n">
         <f aca="false">C24*F24</f>
         <v>0</v>
       </c>
@@ -35911,7 +35916,7 @@
       <c r="I27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="178"/>
+      <c r="A28" s="179"/>
       <c r="B28" s="19"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
@@ -35922,32 +35927,32 @@
       <c r="I28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="94" t="s">
+      <c r="A29" s="95" t="s">
         <v>745</v>
       </c>
-      <c r="B29" s="168"/>
-      <c r="C29" s="179" t="n">
+      <c r="B29" s="169"/>
+      <c r="C29" s="180" t="n">
         <f aca="false">SUM(C6:C28)</f>
         <v>40509</v>
       </c>
-      <c r="D29" s="169"/>
+      <c r="D29" s="170"/>
       <c r="E29" s="45" t="n">
         <f aca="false">SUM(E6:E28)</f>
         <v>220193.95</v>
       </c>
-      <c r="F29" s="168"/>
-      <c r="G29" s="168"/>
-      <c r="H29" s="180" t="n">
+      <c r="F29" s="169"/>
+      <c r="G29" s="169"/>
+      <c r="H29" s="181" t="n">
         <f aca="false">SUM(H6:H28)</f>
         <v>230372.75</v>
       </c>
-      <c r="I29" s="180" t="n">
+      <c r="I29" s="181" t="n">
         <f aca="false">SUM(I6:I28)</f>
         <v>10178.8</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="122" t="s">
+      <c r="A30" s="123" t="s">
         <v>746</v>
       </c>
       <c r="B30" s="19"/>
@@ -35971,24 +35976,24 @@
       <c r="I31" s="19"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="136" t="s">
+      <c r="A32" s="137" t="s">
         <v>747</v>
       </c>
-      <c r="B32" s="136"/>
-      <c r="C32" s="136"/>
-      <c r="D32" s="136"/>
-      <c r="E32" s="136"/>
-      <c r="F32" s="136"/>
-      <c r="G32" s="136"/>
-      <c r="H32" s="136"/>
-      <c r="I32" s="136"/>
+      <c r="B32" s="137"/>
+      <c r="C32" s="137"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="137"/>
+      <c r="G32" s="137"/>
+      <c r="H32" s="137"/>
+      <c r="I32" s="137"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="67" t="s">
         <v>748</v>
       </c>
       <c r="B33" s="19"/>
-      <c r="C33" s="87" t="n">
+      <c r="C33" s="88" t="n">
         <f aca="false">SUMIF($B$6:$B$28,"NA",$I$6:$I$28)</f>
         <v>7571.8</v>
       </c>
@@ -36000,11 +36005,11 @@
       <c r="I33" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="66" t="s">
+      <c r="A34" s="67" t="s">
         <v>749</v>
       </c>
       <c r="B34" s="19"/>
-      <c r="C34" s="87" t="n">
+      <c r="C34" s="88" t="n">
         <f aca="false">SUMIF($B$6:$B$28,"Food",$I$6:$I$28)</f>
         <v>2607</v>
       </c>
@@ -36016,11 +36021,11 @@
       <c r="I34" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="66" t="s">
+      <c r="A35" s="67" t="s">
         <v>750</v>
       </c>
       <c r="B35" s="19"/>
-      <c r="C35" s="87" t="n">
+      <c r="C35" s="88" t="n">
         <f aca="false">I29</f>
         <v>10178.8</v>
       </c>
@@ -36032,11 +36037,11 @@
       <c r="I35" s="19"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="122" t="s">
+      <c r="A36" s="123" t="s">
         <v>751</v>
       </c>
       <c r="B36" s="19"/>
-      <c r="C36" s="181" t="n">
+      <c r="C36" s="182" t="n">
         <f aca="false">I29/258287</f>
         <v>0.0394088746239648</v>
       </c>
@@ -36059,7 +36064,7 @@
       <c r="I37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="66" t="s">
+      <c r="A38" s="67" t="s">
         <v>752</v>
       </c>
       <c r="B38" s="19"/>
@@ -36072,11 +36077,11 @@
       <c r="I38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="126" t="s">
+      <c r="A39" s="127" t="s">
         <v>753</v>
       </c>
       <c r="B39" s="19"/>
-      <c r="C39" s="176" t="n">
+      <c r="C39" s="177" t="n">
         <f aca="false">I29*1</f>
         <v>10178.8</v>
       </c>
@@ -36088,11 +36093,11 @@
       <c r="I39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="126" t="s">
+      <c r="A40" s="127" t="s">
         <v>754</v>
       </c>
       <c r="B40" s="19"/>
-      <c r="C40" s="176" t="n">
+      <c r="C40" s="177" t="n">
         <f aca="false">I29*0.9</f>
         <v>9160.92</v>
       </c>
@@ -36104,11 +36109,11 @@
       <c r="I40" s="19"/>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="182" t="s">
+      <c r="A41" s="183" t="s">
         <v>755</v>
       </c>
       <c r="B41" s="19"/>
-      <c r="C41" s="176" t="n">
+      <c r="C41" s="177" t="n">
         <f aca="false">I29*0.8</f>
         <v>8143.04</v>
       </c>
@@ -36120,7 +36125,7 @@
       <c r="I41" s="19"/>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="183"/>
+      <c r="A42" s="184"/>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
       <c r="D42" s="19"/>
@@ -36131,82 +36136,82 @@
       <c r="I42" s="19"/>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="184" t="s">
+      <c r="A43" s="185" t="s">
         <v>756</v>
       </c>
-      <c r="B43" s="184"/>
-      <c r="C43" s="184"/>
-      <c r="D43" s="184"/>
-      <c r="E43" s="184"/>
-      <c r="F43" s="184"/>
-      <c r="G43" s="184"/>
-      <c r="H43" s="184"/>
-      <c r="I43" s="184"/>
+      <c r="B43" s="185"/>
+      <c r="C43" s="185"/>
+      <c r="D43" s="185"/>
+      <c r="E43" s="185"/>
+      <c r="F43" s="185"/>
+      <c r="G43" s="185"/>
+      <c r="H43" s="185"/>
+      <c r="I43" s="185"/>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="185" t="s">
+      <c r="A44" s="186" t="s">
         <v>757</v>
       </c>
-      <c r="B44" s="185"/>
-      <c r="C44" s="185"/>
-      <c r="D44" s="185"/>
-      <c r="E44" s="185"/>
-      <c r="F44" s="185"/>
-      <c r="G44" s="185"/>
-      <c r="H44" s="185"/>
-      <c r="I44" s="185"/>
+      <c r="B44" s="186"/>
+      <c r="C44" s="186"/>
+      <c r="D44" s="186"/>
+      <c r="E44" s="186"/>
+      <c r="F44" s="186"/>
+      <c r="G44" s="186"/>
+      <c r="H44" s="186"/>
+      <c r="I44" s="186"/>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="185" t="s">
+      <c r="A45" s="186" t="s">
         <v>758</v>
       </c>
-      <c r="B45" s="185"/>
-      <c r="C45" s="185"/>
-      <c r="D45" s="185"/>
-      <c r="E45" s="185"/>
-      <c r="F45" s="185"/>
-      <c r="G45" s="185"/>
-      <c r="H45" s="185"/>
-      <c r="I45" s="185"/>
+      <c r="B45" s="186"/>
+      <c r="C45" s="186"/>
+      <c r="D45" s="186"/>
+      <c r="E45" s="186"/>
+      <c r="F45" s="186"/>
+      <c r="G45" s="186"/>
+      <c r="H45" s="186"/>
+      <c r="I45" s="186"/>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="185" t="s">
+      <c r="A46" s="186" t="s">
         <v>759</v>
       </c>
-      <c r="B46" s="185"/>
-      <c r="C46" s="185"/>
-      <c r="D46" s="185"/>
-      <c r="E46" s="185"/>
-      <c r="F46" s="185"/>
-      <c r="G46" s="185"/>
-      <c r="H46" s="185"/>
-      <c r="I46" s="185"/>
+      <c r="B46" s="186"/>
+      <c r="C46" s="186"/>
+      <c r="D46" s="186"/>
+      <c r="E46" s="186"/>
+      <c r="F46" s="186"/>
+      <c r="G46" s="186"/>
+      <c r="H46" s="186"/>
+      <c r="I46" s="186"/>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="185" t="s">
+      <c r="A47" s="186" t="s">
         <v>760</v>
       </c>
-      <c r="B47" s="185"/>
-      <c r="C47" s="185"/>
-      <c r="D47" s="185"/>
-      <c r="E47" s="185"/>
-      <c r="F47" s="185"/>
-      <c r="G47" s="185"/>
-      <c r="H47" s="185"/>
-      <c r="I47" s="185"/>
+      <c r="B47" s="186"/>
+      <c r="C47" s="186"/>
+      <c r="D47" s="186"/>
+      <c r="E47" s="186"/>
+      <c r="F47" s="186"/>
+      <c r="G47" s="186"/>
+      <c r="H47" s="186"/>
+      <c r="I47" s="186"/>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="185" t="s">
+      <c r="A48" s="186" t="s">
         <v>761</v>
       </c>
-      <c r="B48" s="185"/>
-      <c r="C48" s="185"/>
-      <c r="D48" s="185"/>
-      <c r="E48" s="185"/>
-      <c r="F48" s="185"/>
-      <c r="G48" s="185"/>
-      <c r="H48" s="185"/>
-      <c r="I48" s="185"/>
+      <c r="B48" s="186"/>
+      <c r="C48" s="186"/>
+      <c r="D48" s="186"/>
+      <c r="E48" s="186"/>
+      <c r="F48" s="186"/>
+      <c r="G48" s="186"/>
+      <c r="H48" s="186"/>
+      <c r="I48" s="186"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="19"/>
@@ -36220,7 +36225,7 @@
       <c r="I49" s="19"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="66" t="s">
+      <c r="A50" s="67" t="s">
         <v>762</v>
       </c>
       <c r="B50" s="19"/>
@@ -36233,11 +36238,11 @@
       <c r="I50" s="19"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="126" t="s">
+      <c r="A51" s="127" t="s">
         <v>763</v>
       </c>
       <c r="B51" s="19"/>
-      <c r="C51" s="176" t="n">
+      <c r="C51" s="177" t="n">
         <f aca="false">I29</f>
         <v>10178.8</v>
       </c>
@@ -36249,11 +36254,11 @@
       <c r="I51" s="19"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="126" t="s">
+      <c r="A52" s="127" t="s">
         <v>764</v>
       </c>
       <c r="B52" s="19"/>
-      <c r="C52" s="93" t="n">
+      <c r="C52" s="94" t="n">
         <v>0.9</v>
       </c>
       <c r="D52" s="19"/>
@@ -36264,11 +36269,11 @@
       <c r="I52" s="19"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="66" t="s">
+      <c r="A53" s="67" t="s">
         <v>765</v>
       </c>
       <c r="B53" s="19"/>
-      <c r="C53" s="177" t="n">
+      <c r="C53" s="178" t="n">
         <f aca="false">C51*C52</f>
         <v>9160.92</v>
       </c>
@@ -36372,10 +36377,10 @@
       <c r="B5" s="24" t="n">
         <v>35102</v>
       </c>
-      <c r="C5" s="186" t="n">
+      <c r="C5" s="187" t="n">
         <v>4000</v>
       </c>
-      <c r="D5" s="119" t="n">
+      <c r="D5" s="120" t="n">
         <v>0.42</v>
       </c>
       <c r="E5" s="24" t="n">
@@ -36394,10 +36399,10 @@
       <c r="B6" s="24" t="n">
         <v>18308</v>
       </c>
-      <c r="C6" s="186" t="n">
+      <c r="C6" s="187" t="n">
         <v>12000</v>
       </c>
-      <c r="D6" s="119" t="n">
+      <c r="D6" s="120" t="n">
         <v>0.42</v>
       </c>
       <c r="E6" s="24" t="n">
@@ -36416,10 +36421,10 @@
       <c r="B7" s="24" t="n">
         <v>13158</v>
       </c>
-      <c r="C7" s="186" t="n">
+      <c r="C7" s="187" t="n">
         <v>8000</v>
       </c>
-      <c r="D7" s="119" t="n">
+      <c r="D7" s="120" t="n">
         <v>0.42</v>
       </c>
       <c r="E7" s="24" t="n">
@@ -36438,10 +36443,10 @@
       <c r="B8" s="24" t="n">
         <v>1416</v>
       </c>
-      <c r="C8" s="186" t="n">
+      <c r="C8" s="187" t="n">
         <v>4000</v>
       </c>
-      <c r="D8" s="119" t="n">
+      <c r="D8" s="120" t="n">
         <v>0.42</v>
       </c>
       <c r="E8" s="24" t="n">
@@ -36460,10 +36465,10 @@
       <c r="B9" s="24" t="n">
         <v>857</v>
       </c>
-      <c r="C9" s="186" t="n">
+      <c r="C9" s="187" t="n">
         <v>4000</v>
       </c>
-      <c r="D9" s="119" t="n">
+      <c r="D9" s="120" t="n">
         <v>0.42</v>
       </c>
       <c r="E9" s="24" t="n">
@@ -36482,10 +36487,10 @@
       <c r="B10" s="24" t="n">
         <v>570</v>
       </c>
-      <c r="C10" s="186" t="n">
+      <c r="C10" s="187" t="n">
         <v>3000</v>
       </c>
-      <c r="D10" s="119" t="n">
+      <c r="D10" s="120" t="n">
         <v>0.42</v>
       </c>
       <c r="E10" s="24" t="n">
@@ -36504,10 +36509,10 @@
       <c r="B11" s="24" t="n">
         <v>387</v>
       </c>
-      <c r="C11" s="186" t="n">
+      <c r="C11" s="187" t="n">
         <v>6000</v>
       </c>
-      <c r="D11" s="119" t="n">
+      <c r="D11" s="120" t="n">
         <v>0.42</v>
       </c>
       <c r="E11" s="24" t="n">
@@ -36526,10 +36531,10 @@
       <c r="B12" s="24" t="n">
         <v>198</v>
       </c>
-      <c r="C12" s="186" t="n">
+      <c r="C12" s="187" t="n">
         <v>1500</v>
       </c>
-      <c r="D12" s="119" t="n">
+      <c r="D12" s="120" t="n">
         <v>0.42</v>
       </c>
       <c r="E12" s="24" t="n">
@@ -36548,10 +36553,10 @@
       <c r="B13" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="186" t="n">
+      <c r="C13" s="187" t="n">
         <v>1500</v>
       </c>
-      <c r="D13" s="119" t="n">
+      <c r="D13" s="120" t="n">
         <v>0.42</v>
       </c>
       <c r="E13" s="24" t="n">
@@ -36570,10 +36575,10 @@
       <c r="B14" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="186" t="n">
+      <c r="C14" s="187" t="n">
         <v>924</v>
       </c>
-      <c r="D14" s="119" t="n">
+      <c r="D14" s="120" t="n">
         <v>0.42</v>
       </c>
       <c r="E14" s="24" t="n">
@@ -36597,7 +36602,7 @@
         <f aca="false">SUM(C5:C14)</f>
         <v>44924</v>
       </c>
-      <c r="D15" s="187" t="n">
+      <c r="D15" s="188" t="n">
         <f aca="false">SUMPRODUCT(C5:C14,D5:D14)/C15</f>
         <v>0.42</v>
       </c>
@@ -36642,7 +36647,7 @@
       <c r="A20" s="5" t="s">
         <v>787</v>
       </c>
-      <c r="C20" s="188" t="n">
+      <c r="C20" s="189" t="n">
         <f aca="false">D15</f>
         <v>0.42</v>
       </c>
@@ -44504,27 +44509,27 @@
       <c r="D2" s="40"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="61" t="s">
         <v>276</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="62" t="s">
         <v>277</v>
       </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="C6" s="62" t="n">
+      <c r="C6" s="63" t="n">
         <v>3720</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>279</v>
       </c>
     </row>
@@ -44532,10 +44537,10 @@
       <c r="B7" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="C7" s="64" t="n">
+      <c r="C7" s="65" t="n">
         <v>0.713</v>
       </c>
-      <c r="D7" s="63" t="s">
+      <c r="D7" s="64" t="s">
         <v>281</v>
       </c>
     </row>
@@ -44543,11 +44548,11 @@
       <c r="B8" s="47" t="s">
         <v>282</v>
       </c>
-      <c r="C8" s="64" t="n">
+      <c r="C8" s="65" t="n">
         <f aca="false">2880/3720</f>
         <v>0.774193548387097</v>
       </c>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="64" t="s">
         <v>283</v>
       </c>
     </row>
@@ -44555,29 +44560,29 @@
       <c r="B9" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C9" s="64" t="n">
+      <c r="C9" s="65" t="n">
         <v>0.2</v>
       </c>
-      <c r="D9" s="63" t="s">
+      <c r="D9" s="64" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="62" t="s">
         <v>286</v>
       </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="47" t="s">
         <v>287</v>
       </c>
-      <c r="C12" s="64" t="n">
+      <c r="C12" s="65" t="n">
         <f aca="false">1600/2880</f>
         <v>0.555555555555556</v>
       </c>
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="64" t="s">
         <v>288</v>
       </c>
     </row>
@@ -44585,26 +44590,26 @@
       <c r="B13" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="C13" s="64" t="n">
+      <c r="C13" s="65" t="n">
         <v>0.25</v>
       </c>
-      <c r="D13" s="63" t="str">
+      <c r="D13" s="64" t="str">
         <f aca="false">TEXT(1-$C$13,"0%")&amp;" margin"</f>
         <v>75% margin</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="62" t="s">
         <v>290</v>
       </c>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="47" t="s">
         <v>291</v>
       </c>
-      <c r="C16" s="65" t="n">
+      <c r="C16" s="66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -44612,7 +44617,7 @@
       <c r="B17" s="47" t="s">
         <v>292</v>
       </c>
-      <c r="C17" s="65" t="n">
+      <c r="C17" s="66" t="n">
         <v>2</v>
       </c>
     </row>
@@ -44620,7 +44625,7 @@
       <c r="B18" s="47" t="s">
         <v>293</v>
       </c>
-      <c r="C18" s="62" t="n">
+      <c r="C18" s="63" t="n">
         <v>35</v>
       </c>
     </row>
@@ -44628,15 +44633,15 @@
       <c r="B19" s="47" t="s">
         <v>294</v>
       </c>
-      <c r="C19" s="65" t="n">
+      <c r="C19" s="66" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="67" t="s">
         <v>295</v>
       </c>
-      <c r="C20" s="67" t="n">
+      <c r="C20" s="68" t="n">
         <f aca="false">(C16+C17)*C18*C19</f>
         <v>525</v>
       </c>
@@ -44645,11 +44650,11 @@
       <c r="B21" s="47" t="s">
         <v>296</v>
       </c>
-      <c r="C21" s="67" t="n">
+      <c r="C21" s="68" t="n">
         <f aca="false">'Vessel GL Basis'!D8</f>
         <v>1435.83333333333</v>
       </c>
-      <c r="D21" s="63" t="s">
+      <c r="D21" s="64" t="s">
         <v>297</v>
       </c>
     </row>
@@ -44657,30 +44662,30 @@
       <c r="B22" s="47" t="s">
         <v>298</v>
       </c>
-      <c r="C22" s="64" t="n">
+      <c r="C22" s="65" t="n">
         <f aca="false">114/692</f>
         <v>0.164739884393064</v>
       </c>
-      <c r="D22" s="63" t="s">
+      <c r="D22" s="64" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="61" t="s">
+      <c r="B24" s="62" t="s">
         <v>300</v>
       </c>
-      <c r="C24" s="61"/>
-      <c r="D24" s="61"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="62"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="47" t="s">
         <v>301</v>
       </c>
-      <c r="C25" s="67" t="n">
+      <c r="C25" s="68" t="n">
         <f aca="false">'Vessel GL Basis'!D18</f>
         <v>6718.66666666667</v>
       </c>
-      <c r="D25" s="63" t="s">
+      <c r="D25" s="64" t="s">
         <v>297</v>
       </c>
     </row>
@@ -44688,11 +44693,11 @@
       <c r="B26" s="47" t="s">
         <v>302</v>
       </c>
-      <c r="C26" s="67" t="n">
+      <c r="C26" s="68" t="n">
         <f aca="false">'Vessel GL Basis'!D24</f>
         <v>1045.41666666667</v>
       </c>
-      <c r="D26" s="63" t="s">
+      <c r="D26" s="64" t="s">
         <v>297</v>
       </c>
     </row>
@@ -44700,36 +44705,36 @@
       <c r="B27" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="C27" s="64" t="n">
+      <c r="C27" s="65" t="n">
         <v>0.025</v>
       </c>
-      <c r="D27" s="63" t="s">
+      <c r="D27" s="64" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="62" t="s">
         <v>305</v>
       </c>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="C30" s="68" t="n">
+      <c r="C30" s="69" t="n">
         <v>0.04</v>
       </c>
-      <c r="D30" s="63" t="s">
+      <c r="D30" s="64" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="66" t="s">
+      <c r="B31" s="67" t="s">
         <v>308</v>
       </c>
-      <c r="C31" s="69" t="n">
+      <c r="C31" s="70" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -44740,7 +44745,7 @@
       <c r="B32" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C32" s="70" t="n">
+      <c r="C32" s="71" t="n">
         <v>0.05</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -44751,10 +44756,10 @@
       <c r="B34" s="47" t="s">
         <v>312</v>
       </c>
-      <c r="C34" s="68" t="n">
+      <c r="C34" s="69" t="n">
         <v>0.03</v>
       </c>
-      <c r="D34" s="63" t="s">
+      <c r="D34" s="64" t="s">
         <v>313</v>
       </c>
     </row>
@@ -44762,10 +44767,10 @@
       <c r="B35" s="47" t="s">
         <v>314</v>
       </c>
-      <c r="C35" s="68" t="n">
+      <c r="C35" s="69" t="n">
         <v>0.04</v>
       </c>
-      <c r="D35" s="63" t="s">
+      <c r="D35" s="64" t="s">
         <v>315</v>
       </c>
     </row>
@@ -44773,10 +44778,10 @@
       <c r="B36" s="47" t="s">
         <v>316</v>
       </c>
-      <c r="C36" s="71" t="n">
+      <c r="C36" s="72" t="n">
         <v>55</v>
       </c>
-      <c r="D36" s="63" t="s">
+      <c r="D36" s="64" t="s">
         <v>317</v>
       </c>
     </row>
@@ -44784,10 +44789,10 @@
       <c r="B37" s="47" t="s">
         <v>318</v>
       </c>
-      <c r="C37" s="71" t="n">
+      <c r="C37" s="72" t="n">
         <v>112</v>
       </c>
-      <c r="D37" s="63" t="s">
+      <c r="D37" s="64" t="s">
         <v>317</v>
       </c>
     </row>
@@ -44795,11 +44800,11 @@
       <c r="B38" s="47" t="s">
         <v>319</v>
       </c>
-      <c r="C38" s="72" t="n">
+      <c r="C38" s="73" t="n">
         <f aca="false">575/4650</f>
         <v>0.123655913978495</v>
       </c>
-      <c r="D38" s="63" t="s">
+      <c r="D38" s="64" t="s">
         <v>320</v>
       </c>
     </row>
@@ -44807,11 +44812,11 @@
       <c r="B39" s="47" t="s">
         <v>321</v>
       </c>
-      <c r="C39" s="72" t="n">
+      <c r="C39" s="73" t="n">
         <f aca="false">116/4650</f>
         <v>0.0249462365591398</v>
       </c>
-      <c r="D39" s="63" t="s">
+      <c r="D39" s="64" t="s">
         <v>322</v>
       </c>
     </row>
@@ -45082,46 +45087,46 @@
       <c r="A8" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="C8" s="73" t="n">
+      <c r="C8" s="74" t="n">
         <v>13</v>
       </c>
-      <c r="E8" s="73" t="n">
+      <c r="E8" s="74" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="73" t="n">
+      <c r="G8" s="74" t="n">
         <v>13</v>
       </c>
-      <c r="I8" s="73" t="n">
+      <c r="I8" s="74" t="n">
         <v>4</v>
       </c>
-      <c r="K8" s="73" t="n">
+      <c r="K8" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="M8" s="74" t="n">
+      <c r="M8" s="75" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
-      <c r="O8" s="74" t="n">
+      <c r="O8" s="75" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
-      <c r="Q8" s="74" t="n">
+      <c r="Q8" s="75" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
-      <c r="S8" s="74" t="n">
+      <c r="S8" s="75" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
-      <c r="U8" s="74" t="n">
+      <c r="U8" s="75" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
-      <c r="W8" s="74" t="n">
+      <c r="W8" s="75" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
-      <c r="Y8" s="74" t="n">
+      <c r="Y8" s="75" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
@@ -45134,55 +45139,55 @@
       <c r="A9" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="C9" s="74" t="n">
+      <c r="C9" s="75" t="n">
         <f aca="false">C8*'Vessel Assumptions'!$C$7</f>
         <v>9.269</v>
       </c>
-      <c r="E9" s="74" t="n">
+      <c r="E9" s="75" t="n">
         <f aca="false">E8*'Vessel Assumptions'!$C$7</f>
         <v>2.852</v>
       </c>
-      <c r="G9" s="74" t="n">
+      <c r="G9" s="75" t="n">
         <f aca="false">G8*'Vessel Assumptions'!$C$7</f>
         <v>9.269</v>
       </c>
-      <c r="I9" s="74" t="n">
+      <c r="I9" s="75" t="n">
         <f aca="false">I8*'Vessel Assumptions'!$C$7</f>
         <v>2.852</v>
       </c>
-      <c r="K9" s="74" t="n">
+      <c r="K9" s="75" t="n">
         <f aca="false">K8*'Vessel Assumptions'!$C$7</f>
         <v>7.13</v>
       </c>
-      <c r="M9" s="74" t="n">
+      <c r="M9" s="75" t="n">
         <f aca="false">M8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="O9" s="74" t="n">
+      <c r="O9" s="75" t="n">
         <f aca="false">O8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="Q9" s="74" t="n">
+      <c r="Q9" s="75" t="n">
         <f aca="false">Q8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="S9" s="74" t="n">
+      <c r="S9" s="75" t="n">
         <f aca="false">S8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="U9" s="74" t="n">
+      <c r="U9" s="75" t="n">
         <f aca="false">U8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="W9" s="74" t="n">
+      <c r="W9" s="75" t="n">
         <f aca="false">W8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="Y9" s="74" t="n">
+      <c r="Y9" s="75" t="n">
         <f aca="false">Y8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="AB9" s="74" t="n">
+      <c r="AB9" s="75" t="n">
         <f aca="false">SUM(C9,E9,G9,I9,K9,M9,O9,Q9,S9,U9,W9,Y9)</f>
         <v>75.2928</v>
       </c>
@@ -50110,7 +50115,7 @@
       <c r="A5" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B5" s="75" t="n">
+      <c r="B5" s="76" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -50121,7 +50126,7 @@
       <c r="A6" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="B6" s="76" t="n">
+      <c r="B6" s="77" t="n">
         <v>0.06</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -50153,27 +50158,27 @@
       <c r="A9" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="B9" s="77" t="n">
+      <c r="B9" s="78" t="n">
         <f aca="false">'Vessel Budget'!$AB$9</f>
         <v>75.2928</v>
       </c>
-      <c r="C9" s="77" t="n">
+      <c r="C9" s="78" t="n">
         <f aca="false">B9+$B$5</f>
         <v>85.2928</v>
       </c>
-      <c r="D9" s="77" t="n">
+      <c r="D9" s="78" t="n">
         <f aca="false">C9+$B$5</f>
         <v>95.2928</v>
       </c>
-      <c r="E9" s="77" t="n">
+      <c r="E9" s="78" t="n">
         <f aca="false">D9+$B$5</f>
         <v>105.2928</v>
       </c>
-      <c r="F9" s="77" t="n">
+      <c r="F9" s="78" t="n">
         <f aca="false">E9+$B$5</f>
         <v>115.2928</v>
       </c>
-      <c r="G9" s="78" t="s">
+      <c r="G9" s="79" t="s">
         <v>347</v>
       </c>
     </row>
@@ -50181,27 +50186,27 @@
       <c r="A10" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="B10" s="79" t="n">
+      <c r="B10" s="80" t="n">
         <f aca="false">'Vessel Budget'!$AB$20/'Vessel Budget'!$AB$9</f>
         <v>4650</v>
       </c>
-      <c r="C10" s="79" t="n">
+      <c r="C10" s="80" t="n">
         <f aca="false">B10*(1+$B$6)</f>
         <v>4929</v>
       </c>
-      <c r="D10" s="79" t="n">
+      <c r="D10" s="80" t="n">
         <f aca="false">C10*(1+$B$6)</f>
         <v>5224.74</v>
       </c>
-      <c r="E10" s="79" t="n">
+      <c r="E10" s="80" t="n">
         <f aca="false">D10*(1+$B$6)</f>
         <v>5538.2244</v>
       </c>
-      <c r="F10" s="79" t="n">
+      <c r="F10" s="80" t="n">
         <f aca="false">E10*(1+$B$6)</f>
         <v>5870.517864</v>
       </c>
-      <c r="G10" s="78" t="s">
+      <c r="G10" s="79" t="s">
         <v>349</v>
       </c>
     </row>
@@ -50209,27 +50214,27 @@
       <c r="A11" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="B11" s="80" t="n">
+      <c r="B11" s="81" t="n">
         <f aca="false">B9*B10</f>
         <v>350111.52</v>
       </c>
-      <c r="C11" s="80" t="n">
+      <c r="C11" s="81" t="n">
         <f aca="false">C9*C10</f>
         <v>420408.2112</v>
       </c>
-      <c r="D11" s="80" t="n">
+      <c r="D11" s="81" t="n">
         <f aca="false">D9*D10</f>
         <v>497880.103872</v>
       </c>
-      <c r="E11" s="80" t="n">
+      <c r="E11" s="81" t="n">
         <f aca="false">E9*E10</f>
         <v>583135.15410432</v>
       </c>
-      <c r="F11" s="80" t="n">
+      <c r="F11" s="81" t="n">
         <f aca="false">F9*F10</f>
         <v>676828.441990579</v>
       </c>
-      <c r="G11" s="81" t="s">
+      <c r="G11" s="82" t="s">
         <v>351</v>
       </c>
     </row>
@@ -50237,27 +50242,27 @@
       <c r="A12" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="B12" s="82" t="n">
+      <c r="B12" s="83" t="n">
         <f aca="false">'Vessel Budget'!$AB$62/'Vessel Budget'!$AB$20</f>
         <v>0.248817204301075</v>
       </c>
-      <c r="C12" s="82" t="n">
+      <c r="C12" s="83" t="n">
         <f aca="false">$B$12</f>
         <v>0.248817204301075</v>
       </c>
-      <c r="D12" s="82" t="n">
+      <c r="D12" s="83" t="n">
         <f aca="false">$B$12</f>
         <v>0.248817204301075</v>
       </c>
-      <c r="E12" s="82" t="n">
+      <c r="E12" s="83" t="n">
         <f aca="false">$B$12</f>
         <v>0.248817204301075</v>
       </c>
-      <c r="F12" s="82" t="n">
+      <c r="F12" s="83" t="n">
         <f aca="false">$B$12</f>
         <v>0.248817204301075</v>
       </c>
-      <c r="G12" s="82" t="n">
+      <c r="G12" s="83" t="n">
         <f aca="false">$B$12</f>
         <v>0.248817204301075</v>
       </c>
@@ -50266,27 +50271,27 @@
       <c r="A13" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="B13" s="83" t="n">
+      <c r="B13" s="84" t="n">
         <f aca="false">B11*B12</f>
         <v>87113.7696</v>
       </c>
-      <c r="C13" s="83" t="n">
+      <c r="C13" s="84" t="n">
         <f aca="false">C11*C12</f>
         <v>104604.795776</v>
       </c>
-      <c r="D13" s="83" t="n">
+      <c r="D13" s="84" t="n">
         <f aca="false">D11*D12</f>
         <v>123881.13552256</v>
       </c>
-      <c r="E13" s="83" t="n">
+      <c r="E13" s="84" t="n">
         <f aca="false">E11*E12</f>
         <v>145094.058773914</v>
       </c>
-      <c r="F13" s="83" t="n">
+      <c r="F13" s="84" t="n">
         <f aca="false">F11*F12</f>
         <v>168406.560727548</v>
       </c>
-      <c r="G13" s="84" t="s">
+      <c r="G13" s="85" t="s">
         <v>354</v>
       </c>
     </row>

--- a/Method_Operating_Model_2027_28.xlsx
+++ b/Method_Operating_Model_2027_28.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="782">
   <si>
     <t xml:space="preserve">LITTLE WING — DECK TIE-OUT</t>
   </si>
@@ -1068,49 +1068,28 @@
     <t xml:space="preserve">2027 · IMMEDIATE</t>
   </si>
   <si>
-    <t xml:space="preserve">2028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STABILIZED TARGET</t>
+    <t xml:space="preserve">2028 · BUILDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2029 · STABILIZED</t>
   </si>
   <si>
     <t xml:space="preserve">Annual events</t>
   </si>
   <si>
-    <t xml:space="preserve">~125–130</t>
-  </si>
-  <si>
     <t xml:space="preserve">Avg. revenue / event</t>
   </si>
   <si>
-    <t xml:space="preserve">$4,800+</t>
-  </si>
-  <si>
     <t xml:space="preserve">Annual revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">$600K+</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOI margin (per-event card)</t>
   </si>
   <si>
     <t xml:space="preserve">Annual NOP</t>
   </si>
   <si>
-    <t xml:space="preserve">$150K+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027 links live to the Vessel Budget (per-event card: $4,650 revenue · $1,157 NOP · 24.9% margin — margin holds at any volume because every cost scales per event or per revenue). Growth years add +10 events/yr and compound +6%/yr average event revenue: ~$500K by 2029, $600K+ by 2030 — reaching the stabilized calendar (~125–130 events) by 2032. Added benefit: larger average events and more of them, generating incremental ROOST room sales.</t>
+    <t xml:space="preserve">2027 links live to the Vessel Budget (per-event card: $4,650 revenue · $1,157 NOP · 24.9% margin — margin holds at any volume). Roadmap: +10 events per year and +6%/yr average event revenue → stabilized in year 3 (2029): ~95 events, ~$498K revenue, ~$124K NOP at 25%. Growth comes from both a fuller calendar and larger average events, generating incremental ROOST room sales.</t>
   </si>
   <si>
     <t xml:space="preserve">VESSEL — GL COST BASIS</t>
@@ -2416,7 +2395,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="16">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\)"/>
     <numFmt numFmtId="166" formatCode="0.0%;\-0.0%"/>
@@ -2425,14 +2404,13 @@
     <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
     <numFmt numFmtId="171" formatCode="0"/>
-    <numFmt numFmtId="172" formatCode="General"/>
-    <numFmt numFmtId="173" formatCode="\$#,##0"/>
-    <numFmt numFmtId="174" formatCode="0.00%"/>
-    <numFmt numFmtId="175" formatCode="0.0"/>
-    <numFmt numFmtId="176" formatCode="0%"/>
-    <numFmt numFmtId="177" formatCode="@"/>
-    <numFmt numFmtId="178" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="179" formatCode="\$#,##0;;\–"/>
+    <numFmt numFmtId="172" formatCode="\$#,##0"/>
+    <numFmt numFmtId="173" formatCode="0.00%"/>
+    <numFmt numFmtId="174" formatCode="0.0"/>
+    <numFmt numFmtId="175" formatCode="0%"/>
+    <numFmt numFmtId="176" formatCode="@"/>
+    <numFmt numFmtId="177" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="178" formatCode="\$#,##0;;\–"/>
   </numFmts>
   <fonts count="44">
     <font>
@@ -2871,764 +2849,752 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="187">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="22" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="21" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="25" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="25" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="25" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="25" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="21" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="25" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="28" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="25" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="25" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="25" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="37" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="174" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="172" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="37" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="40" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="41" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="177" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="28" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="177" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="179" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="179" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="40" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="41" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="43" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4637,39 +4603,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
       <c r="D1" s="40"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="61" t="s">
-        <v>357</v>
-      </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
+      <c r="A2" s="41" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="86" t="s">
-        <v>358</v>
+      <c r="B4" s="83" t="s">
+        <v>351</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="42" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="49" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C8" s="50" t="n">
         <f aca="false">'Vessel 2026 P&amp;L'!$AB$28</f>
@@ -4682,12 +4648,12 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="42" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="49" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C11" s="50" t="n">
         <v>18543</v>
@@ -4699,7 +4665,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="49" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C12" s="50" t="n">
         <v>30300</v>
@@ -4711,7 +4677,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="49" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C13" s="50" t="n">
         <v>13917</v>
@@ -4723,7 +4689,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="49" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C14" s="50" t="n">
         <v>6750</v>
@@ -4735,7 +4701,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="49" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C15" s="50" t="n">
         <v>5748</v>
@@ -4759,7 +4725,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="44" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C17" s="45" t="n">
         <f aca="false">SUM(C11:C16)</f>
@@ -4771,26 +4737,26 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="64" t="s">
-        <v>370</v>
-      </c>
-      <c r="C18" s="87" t="n">
+      <c r="B18" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="C18" s="84" t="n">
         <f aca="false">'Vessel 2026 P&amp;L'!$AB$44</f>
         <v>80624</v>
       </c>
-      <c r="D18" s="88" t="n">
+      <c r="D18" s="85" t="n">
         <f aca="false">C18/12</f>
         <v>6718.66666666667</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="42" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="49" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C21" s="50" t="n">
         <v>2106</v>
@@ -4802,7 +4768,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="49" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C22" s="50" t="n">
         <v>1800</v>
@@ -4814,7 +4780,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="49" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C23" s="50" t="n">
         <v>4855</v>
@@ -4826,7 +4792,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="44" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C24" s="45" t="n">
         <f aca="false">'Vessel 2026 P&amp;L'!$AB$47+'Vessel 2026 P&amp;L'!$AB$49+'Vessel 2026 P&amp;L'!$AB$51+'Vessel 2026 P&amp;L'!$AB$52</f>
@@ -4839,12 +4805,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="42" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="49" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="C27" s="50" t="n">
         <v>2745</v>
@@ -4856,7 +4822,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="49" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C28" s="50" t="n">
         <v>48000</v>
@@ -4868,7 +4834,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="49" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C29" s="50" t="n">
         <f aca="false">'Vessel 2026 P&amp;L'!$AB$48</f>
@@ -4941,12 +4907,12 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4999,61 +4965,61 @@
       </c>
       <c r="Z5" s="30"/>
       <c r="AB5" s="30" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AC5" s="30"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="H6" s="32"/>
       <c r="I6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="J6" s="32"/>
       <c r="K6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="L6" s="32"/>
       <c r="M6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="N6" s="32"/>
       <c r="O6" s="32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="P6" s="32"/>
       <c r="Q6" s="32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="R6" s="32"/>
       <c r="S6" s="32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="T6" s="32"/>
       <c r="U6" s="32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="V6" s="32"/>
       <c r="W6" s="32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X6" s="32"/>
       <c r="Y6" s="32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="Z6" s="32"/>
       <c r="AB6" s="32" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="AC6" s="32"/>
     </row>
@@ -9449,17 +9415,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9512,61 +9478,61 @@
       </c>
       <c r="Z5" s="30"/>
       <c r="AB5" s="30" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AC5" s="30"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="H6" s="32"/>
       <c r="I6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="J6" s="32"/>
       <c r="K6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="L6" s="32"/>
       <c r="M6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="N6" s="32"/>
       <c r="O6" s="32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="P6" s="32"/>
       <c r="Q6" s="32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="R6" s="32"/>
       <c r="S6" s="32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="T6" s="32"/>
       <c r="U6" s="32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="V6" s="32"/>
       <c r="W6" s="32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="X6" s="32"/>
       <c r="Y6" s="32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="Z6" s="32"/>
       <c r="AB6" s="32" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="AC6" s="32"/>
     </row>
@@ -13962,28 +13928,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="C4" s="89" t="n">
+        <v>381</v>
+      </c>
+      <c r="C4" s="86" t="n">
         <v>46235</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14036,61 +14002,61 @@
       </c>
       <c r="Z5" s="30"/>
       <c r="AB5" s="30" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AC5" s="30"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="H6" s="32"/>
       <c r="I6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="J6" s="32"/>
       <c r="K6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="L6" s="32"/>
       <c r="M6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="N6" s="32"/>
       <c r="O6" s="32" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="P6" s="32"/>
       <c r="Q6" s="32" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="R6" s="32"/>
       <c r="S6" s="32" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="T6" s="32"/>
       <c r="U6" s="32" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="V6" s="32"/>
       <c r="W6" s="32" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="X6" s="32"/>
       <c r="Y6" s="32" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="Z6" s="32"/>
       <c r="AB6" s="32" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="AC6" s="32"/>
     </row>
@@ -14726,7 +14692,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C17" s="24" t="n">
         <f aca="false">IF(1&gt;=MONTH($C$4),('LW Assumptions'!$C$47+'LW Assumptions'!$C$36)/12,0)</f>
@@ -14944,7 +14910,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C19" s="24" t="n">
         <f aca="false">IF(1&gt;=MONTH($C$4),-SUM(C12:C18)*'LW Assumptions'!$C$53,'LW 2026 P&amp;L'!C15)</f>
@@ -15167,7 +15133,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">IF(1&gt;=MONTH($C$4),'LW 2026 P&amp;L'!C9*'LW Assumptions'!$C$51,'LW 2026 P&amp;L'!C19)</f>
@@ -16921,7 +16887,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C44" s="24" t="n">
         <f aca="false">IF(1&gt;=MONTH($C$4),C20*'LW Assumptions'!$C$48,'LW 2026 P&amp;L'!C39)</f>
@@ -17895,7 +17861,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C55" s="24" t="n">
         <f aca="false">IF(1&gt;=MONTH($C$4),C20*'LW Assumptions'!$C$52,'LW 2026 P&amp;L'!C49)</f>
@@ -19191,7 +19157,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -19280,23 +19246,23 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="C4" s="89" t="n">
+        <v>381</v>
+      </c>
+      <c r="C4" s="86" t="n">
         <v>46266</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19349,61 +19315,61 @@
       </c>
       <c r="Z5" s="30"/>
       <c r="AB5" s="30" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AC5" s="30"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="H6" s="32"/>
       <c r="I6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="J6" s="32"/>
       <c r="K6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="L6" s="32"/>
       <c r="M6" s="32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="N6" s="32"/>
       <c r="O6" s="32" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="P6" s="32"/>
       <c r="Q6" s="32" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="R6" s="32"/>
       <c r="S6" s="32" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="T6" s="32"/>
       <c r="U6" s="32" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="V6" s="32"/>
       <c r="W6" s="32" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="X6" s="32"/>
       <c r="Y6" s="32" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="Z6" s="32"/>
       <c r="AB6" s="32" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="AC6" s="32"/>
     </row>
@@ -20039,7 +20005,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C17" s="24" t="n">
         <v>0</v>
@@ -20136,7 +20102,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C18" s="24" t="n">
         <f aca="false">IF(1&gt;=MONTH($C$4),'Vessel 2026 P&amp;L'!C14+SUM(C12:C16)*'Vessel Assumptions'!$C$32,'Vessel 2026 P&amp;L'!C14)</f>
@@ -22210,7 +22176,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C44" s="24" t="n">
         <f aca="false">IF(1&gt;=MONTH($C$4),C20*'Vessel Assumptions'!$C$34,'Vessel 2026 P&amp;L'!C39)</f>
@@ -24480,7 +24446,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -24539,397 +24505,397 @@
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
       <c r="D1" s="40"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="61" t="s">
-        <v>404</v>
-      </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
+      <c r="A2" s="41" t="s">
+        <v>397</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="62" t="s">
-        <v>405</v>
-      </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
+      <c r="B4" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="47" t="s">
-        <v>406</v>
-      </c>
-      <c r="C5" s="63" t="n">
+        <v>399</v>
+      </c>
+      <c r="C5" s="62" t="n">
         <v>106838.2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="47" t="s">
-        <v>407</v>
-      </c>
-      <c r="C6" s="63" t="n">
+        <v>400</v>
+      </c>
+      <c r="C6" s="62" t="n">
         <v>131727.36</v>
       </c>
-      <c r="D6" s="64" t="s">
-        <v>408</v>
+      <c r="D6" s="63" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="47" t="s">
-        <v>409</v>
-      </c>
-      <c r="C7" s="63" t="n">
+        <v>402</v>
+      </c>
+      <c r="C7" s="62" t="n">
         <v>13996.3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="47" t="s">
-        <v>410</v>
-      </c>
-      <c r="C8" s="63" t="n">
+        <v>403</v>
+      </c>
+      <c r="C8" s="62" t="n">
         <v>5847.56</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="47" t="s">
-        <v>411</v>
-      </c>
-      <c r="C9" s="63" t="n">
+        <v>404</v>
+      </c>
+      <c r="C9" s="62" t="n">
         <v>7792.6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="67" t="s">
-        <v>413</v>
-      </c>
-      <c r="C10" s="68" t="n">
+      <c r="B10" s="66" t="s">
+        <v>406</v>
+      </c>
+      <c r="C10" s="67" t="n">
         <f aca="false">SUM(C5:C9)</f>
         <v>266202.02</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
+      <c r="B12" s="61" t="s">
+        <v>407</v>
+      </c>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="47" t="s">
-        <v>415</v>
-      </c>
-      <c r="C13" s="65" t="n">
+        <v>408</v>
+      </c>
+      <c r="C13" s="64" t="n">
         <v>0.4407</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="47" t="s">
-        <v>417</v>
-      </c>
-      <c r="C14" s="65" t="n">
+        <v>410</v>
+      </c>
+      <c r="C14" s="64" t="n">
         <v>0.2216</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="47" t="s">
-        <v>418</v>
-      </c>
-      <c r="C15" s="65" t="n">
+        <v>411</v>
+      </c>
+      <c r="C15" s="64" t="n">
         <v>0.3328</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="47" t="s">
-        <v>419</v>
-      </c>
-      <c r="C16" s="65" t="n">
+        <v>412</v>
+      </c>
+      <c r="C16" s="64" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="47" t="s">
-        <v>421</v>
-      </c>
-      <c r="C17" s="65" t="n">
+        <v>414</v>
+      </c>
+      <c r="C17" s="64" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="62" t="s">
-        <v>423</v>
-      </c>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
+      <c r="B19" s="61" t="s">
+        <v>416</v>
+      </c>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="47" t="s">
-        <v>424</v>
-      </c>
-      <c r="C20" s="66" t="n">
+        <v>417</v>
+      </c>
+      <c r="C20" s="65" t="n">
         <v>10</v>
       </c>
-      <c r="D20" s="64" t="s">
-        <v>425</v>
+      <c r="D20" s="63" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="47" t="s">
-        <v>426</v>
-      </c>
-      <c r="C21" s="66" t="n">
+        <v>419</v>
+      </c>
+      <c r="C21" s="65" t="n">
         <f aca="false">2*4/7</f>
         <v>1.14285714285714</v>
       </c>
-      <c r="D21" s="64" t="s">
-        <v>427</v>
+      <c r="D21" s="63" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="47" t="s">
-        <v>428</v>
-      </c>
-      <c r="C22" s="66" t="n">
+        <v>421</v>
+      </c>
+      <c r="C22" s="65" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="47" t="s">
-        <v>429</v>
-      </c>
-      <c r="C23" s="63" t="n">
+        <v>422</v>
+      </c>
+      <c r="C23" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="D23" s="64" t="s">
-        <v>430</v>
+      <c r="D23" s="63" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="47" t="s">
         <v>298</v>
       </c>
-      <c r="C24" s="65" t="n">
+      <c r="C24" s="64" t="n">
         <v>0.16</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="67" t="s">
-        <v>431</v>
-      </c>
-      <c r="C25" s="68" t="n">
+      <c r="B25" s="66" t="s">
+        <v>424</v>
+      </c>
+      <c r="C25" s="67" t="n">
         <f aca="false">(C20+C21)*C22*52*C23*(1+C24)+C26*52*(1+C24)</f>
         <v>111953.92</v>
       </c>
-      <c r="D25" s="64" t="s">
-        <v>432</v>
+      <c r="D25" s="63" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="47" t="s">
-        <v>433</v>
-      </c>
-      <c r="C26" s="63" t="n">
+        <v>426</v>
+      </c>
+      <c r="C26" s="62" t="n">
         <v>296</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="62" t="s">
-        <v>435</v>
-      </c>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
+      <c r="B27" s="61" t="s">
+        <v>428</v>
+      </c>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="47" t="s">
-        <v>436</v>
-      </c>
-      <c r="C28" s="63" t="n">
+        <v>429</v>
+      </c>
+      <c r="C28" s="62" t="n">
         <v>164857</v>
       </c>
-      <c r="D28" s="64" t="s">
-        <v>437</v>
+      <c r="D28" s="63" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="62" t="s">
-        <v>438</v>
-      </c>
-      <c r="C30" s="62"/>
-      <c r="D30" s="62"/>
+      <c r="B30" s="61" t="s">
+        <v>431</v>
+      </c>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="C31" s="65" t="n">
+      <c r="C31" s="64" t="n">
         <v>0.025</v>
       </c>
-      <c r="D31" s="64" t="s">
-        <v>439</v>
+      <c r="D31" s="63" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="47" t="s">
-        <v>440</v>
-      </c>
-      <c r="C32" s="63" t="n">
+        <v>433</v>
+      </c>
+      <c r="C32" s="62" t="n">
         <v>89675</v>
       </c>
-      <c r="D32" s="64" t="s">
-        <v>441</v>
+      <c r="D32" s="63" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="C33" s="63" t="n">
+      <c r="C33" s="62" t="n">
         <v>5657</v>
       </c>
-      <c r="D33" s="64" t="s">
-        <v>442</v>
+      <c r="D33" s="63" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="62" t="s">
-        <v>443</v>
-      </c>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
+      <c r="B35" s="61" t="s">
+        <v>436</v>
+      </c>
+      <c r="C35" s="61"/>
+      <c r="D35" s="61"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="47" t="s">
-        <v>444</v>
-      </c>
-      <c r="C36" s="63" t="n">
+        <v>437</v>
+      </c>
+      <c r="C36" s="62" t="n">
         <f aca="false">'LW Retail Plan'!$C$19</f>
         <v>42000.22</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="47" t="s">
-        <v>446</v>
-      </c>
-      <c r="C37" s="90" t="n">
+        <v>439</v>
+      </c>
+      <c r="C37" s="87" t="n">
         <f aca="false">'LW Retail Plan'!$C$20</f>
         <v>0.42</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="91" t="s">
-        <v>448</v>
-      </c>
-      <c r="C39" s="91"/>
-      <c r="D39" s="91"/>
+      <c r="B39" s="88" t="s">
+        <v>441</v>
+      </c>
+      <c r="C39" s="88"/>
+      <c r="D39" s="88"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="47" t="s">
-        <v>449</v>
-      </c>
-      <c r="C40" s="92" t="n">
+        <v>442</v>
+      </c>
+      <c r="C40" s="89" t="n">
         <v>0.04</v>
       </c>
-      <c r="D40" s="64" t="s">
-        <v>450</v>
+      <c r="D40" s="63" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="47" t="s">
-        <v>451</v>
-      </c>
-      <c r="C41" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="64" t="s">
-        <v>452</v>
+        <v>444</v>
+      </c>
+      <c r="C41" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="63" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="47" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C42" s="45" t="n">
         <v>10012</v>
       </c>
-      <c r="D42" s="64" t="s">
-        <v>454</v>
+      <c r="D42" s="63" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="47" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C43" s="45" t="n">
         <f aca="false">'LW Menu Pricing'!$C$53</f>
         <v>9160.92</v>
       </c>
-      <c r="D43" s="64" t="s">
-        <v>456</v>
+      <c r="D43" s="63" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="47" t="s">
-        <v>457</v>
-      </c>
-      <c r="C44" s="93" t="n">
+        <v>450</v>
+      </c>
+      <c r="C44" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="64" t="s">
-        <v>458</v>
+      <c r="D44" s="63" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="47" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="C45" s="45" t="n">
         <v>12880</v>
       </c>
-      <c r="D45" s="64" t="s">
-        <v>460</v>
+      <c r="D45" s="63" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C46" s="94" t="n">
+        <v>454</v>
+      </c>
+      <c r="C46" s="91" t="n">
         <v>0.5</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C47" s="87" t="n">
+        <v>456</v>
+      </c>
+      <c r="C47" s="84" t="n">
         <f aca="false">'LW Assumptions'!$C$8*'LW Assumptions'!$C$46</f>
         <v>2923.78</v>
       </c>
@@ -24938,62 +24904,62 @@
       <c r="B48" s="47" t="s">
         <v>312</v>
       </c>
-      <c r="C48" s="92" t="n">
+      <c r="C48" s="89" t="n">
         <v>0.125</v>
       </c>
-      <c r="D48" s="64" t="s">
-        <v>464</v>
+      <c r="D48" s="63" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="47" t="s">
-        <v>465</v>
-      </c>
-      <c r="C49" s="92" t="n">
+        <v>458</v>
+      </c>
+      <c r="C49" s="89" t="n">
         <v>0.035</v>
       </c>
-      <c r="D49" s="64"/>
+      <c r="D49" s="63"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="47" t="s">
         <v>314</v>
       </c>
-      <c r="C50" s="92" t="n">
+      <c r="C50" s="89" t="n">
         <v>0.085</v>
       </c>
-      <c r="D50" s="64"/>
+      <c r="D50" s="63"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="47" t="s">
-        <v>466</v>
-      </c>
-      <c r="C51" s="92" t="n">
+        <v>459</v>
+      </c>
+      <c r="C51" s="89" t="n">
         <v>0.4</v>
       </c>
-      <c r="D51" s="64" t="s">
-        <v>467</v>
+      <c r="D51" s="63" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="47" t="s">
-        <v>468</v>
-      </c>
-      <c r="C52" s="92" t="n">
+        <v>461</v>
+      </c>
+      <c r="C52" s="89" t="n">
         <v>0.045</v>
       </c>
-      <c r="D52" s="64" t="s">
-        <v>469</v>
+      <c r="D52" s="63" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="47" t="s">
-        <v>470</v>
-      </c>
-      <c r="C53" s="92" t="n">
+        <v>463</v>
+      </c>
+      <c r="C53" s="89" t="n">
         <v>0.025</v>
       </c>
-      <c r="D53" s="64" t="s">
-        <v>471</v>
+      <c r="D53" s="63" t="s">
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -25039,12 +25005,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25054,33 +25020,33 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C5" s="30" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="D5" s="30"/>
       <c r="E5" s="31"/>
       <c r="F5" s="30" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="31"/>
       <c r="I5" s="30" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="J5" s="30"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C6" s="32" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="33"/>
       <c r="F6" s="32" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="G6" s="32"/>
       <c r="H6" s="33"/>
       <c r="I6" s="32" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="J6" s="32"/>
     </row>
@@ -26065,7 +26031,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="C54" s="24" t="n">
         <f aca="false">C20*0.06</f>
@@ -26430,7 +26396,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -26494,12 +26460,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27247,7 +27213,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C17" s="24" t="n">
         <f aca="false">('LW Assumptions'!$C$47+'LW Assumptions'!$C$36)/12</f>
@@ -27465,7 +27431,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="C19" s="24" t="n">
         <f aca="false">-SUM(C12:C18)*'LW Assumptions'!$C$53</f>
@@ -27688,7 +27654,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">'LW 2026 P&amp;L'!$Y$9*'LW Assumptions'!$C$51</f>
@@ -29001,7 +28967,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="C37" s="24" t="n">
         <v>0</v>
@@ -29431,7 +29397,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="C44" s="24" t="n">
         <f aca="false">C20*'LW Assumptions'!$C$48</f>
@@ -30405,7 +30371,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="C55" s="24" t="n">
         <f aca="false">C20*'LW Assumptions'!$C$52</f>
@@ -31701,30 +31667,30 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="C76" s="75" t="n">
+        <v>481</v>
+      </c>
+      <c r="C76" s="74" t="n">
         <f aca="false">'LW Assumptions'!$C$20+'LW Assumptions'!$C$21</f>
         <v>11.1428571428571</v>
       </c>
@@ -31735,9 +31701,9 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="C77" s="75" t="n">
+        <v>482</v>
+      </c>
+      <c r="C77" s="74" t="n">
         <v>8</v>
       </c>
       <c r="E77" s="24" t="n">
@@ -31747,9 +31713,9 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="C78" s="75" t="n">
+        <v>483</v>
+      </c>
+      <c r="C78" s="74" t="n">
         <v>13.5</v>
       </c>
       <c r="E78" s="24" t="n">
@@ -31759,9 +31725,9 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="C79" s="75" t="n">
+        <v>484</v>
+      </c>
+      <c r="C79" s="74" t="n">
         <v>16</v>
       </c>
       <c r="E79" s="24" t="n">
@@ -31828,7 +31794,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="40" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -31839,48 +31805,48 @@
       <c r="H1" s="40"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="61" t="s">
-        <v>493</v>
-      </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
+      <c r="A2" s="41" t="s">
+        <v>486</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="42" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="86" t="s">
-        <v>496</v>
+      <c r="B5" s="83" t="s">
+        <v>489</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>497</v>
-      </c>
-      <c r="F5" s="86" t="s">
-        <v>498</v>
+        <v>490</v>
+      </c>
+      <c r="F5" s="83" t="s">
+        <v>491</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="H5" s="43" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="47" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="C6" s="50" t="n">
         <v>42998</v>
@@ -31890,7 +31856,7 @@
         <v>0.161523943357004</v>
       </c>
       <c r="F6" s="47" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="G6" s="50" t="n">
         <v>72907</v>
@@ -31902,7 +31868,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="47" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C7" s="50" t="n">
         <v>54634</v>
@@ -31912,7 +31878,7 @@
         <v>0.205235106780933</v>
       </c>
       <c r="F7" s="47" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="G7" s="50" t="n">
         <v>32396</v>
@@ -31924,7 +31890,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="47" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C8" s="50" t="n">
         <v>30727</v>
@@ -31933,8 +31899,8 @@
         <f aca="false">C8/'LW Assumptions'!C10</f>
         <v>0.115427373541343</v>
       </c>
-      <c r="F8" s="95" t="s">
-        <v>506</v>
+      <c r="F8" s="92" t="s">
+        <v>499</v>
       </c>
       <c r="G8" s="45" t="n">
         <f aca="false">G6+G7</f>
@@ -31947,7 +31913,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="47" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="C9" s="50" t="n">
         <v>12880</v>
@@ -31959,7 +31925,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="47" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="C10" s="50" t="n">
         <v>886</v>
@@ -31968,13 +31934,13 @@
         <f aca="false">C10/'LW Assumptions'!C10</f>
         <v>0.00332829931192859</v>
       </c>
-      <c r="F10" s="64" t="s">
-        <v>509</v>
+      <c r="F10" s="63" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="47" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C11" s="50" t="n">
         <v>22733</v>
@@ -31983,13 +31949,13 @@
         <f aca="false">C11/'LW Assumptions'!C10</f>
         <v>0.0853975488240097</v>
       </c>
-      <c r="F11" s="64" t="s">
-        <v>511</v>
+      <c r="F11" s="63" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="95" t="s">
-        <v>512</v>
+      <c r="B12" s="92" t="s">
+        <v>505</v>
       </c>
       <c r="C12" s="45" t="n">
         <f aca="false">SUM(C6:C11)</f>
@@ -31999,27 +31965,27 @@
         <f aca="false">C12/'LW Assumptions'!C10</f>
         <v>0.619296577839642</v>
       </c>
-      <c r="F12" s="64" t="s">
-        <v>513</v>
+      <c r="F12" s="63" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="42" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="47" t="s">
-        <v>515</v>
-      </c>
-      <c r="C15" s="96" t="n">
+        <v>508</v>
+      </c>
+      <c r="C15" s="93" t="n">
         <f aca="false">'LW Assumptions'!C20+'LW Assumptions'!C21</f>
         <v>11.1428571428571</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="47" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="C16" s="54" t="n">
         <f aca="false">('LW Assumptions'!C20+'LW Assumptions'!C21)*'LW Assumptions'!C22*52</f>
@@ -32028,7 +31994,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="47" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="C17" s="50" t="n">
         <f aca="false">C16*'LW Assumptions'!C23</f>
@@ -32037,7 +32003,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="47" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C18" s="50" t="n">
         <f aca="false">'LW Assumptions'!C26*52</f>
@@ -32046,7 +32012,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="47" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="C19" s="50" t="n">
         <f aca="false">(C17+C18)*'LW Assumptions'!C24</f>
@@ -32055,7 +32021,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="47" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="C20" s="54" t="n">
         <f aca="false">C17+C18+C19</f>
@@ -32063,17 +32029,17 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="97" t="s">
-        <v>521</v>
-      </c>
-      <c r="C21" s="98" t="n">
+      <c r="B21" s="94" t="s">
+        <v>514</v>
+      </c>
+      <c r="C21" s="95" t="n">
         <f aca="false">C12-C20</f>
         <v>52904.08</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="60" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="C23" s="60"/>
       <c r="D23" s="60"/>
@@ -32121,349 +32087,349 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="99" t="s">
-        <v>523</v>
+      <c r="A1" s="96" t="s">
+        <v>516</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
       <c r="D1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="100" t="s">
-        <v>524</v>
-      </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
+      <c r="A2" s="97" t="s">
+        <v>517</v>
+      </c>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="86"/>
+      <c r="A4" s="83"/>
       <c r="B4" s="43" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="95" t="s">
-        <v>528</v>
-      </c>
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
+      <c r="A5" s="92" t="s">
+        <v>521</v>
+      </c>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="102" t="s">
-        <v>529</v>
-      </c>
-      <c r="B6" s="103" t="s">
-        <v>530</v>
-      </c>
-      <c r="C6" s="103" t="n">
+      <c r="A6" s="99" t="s">
+        <v>522</v>
+      </c>
+      <c r="B6" s="100" t="s">
+        <v>523</v>
+      </c>
+      <c r="C6" s="100" t="n">
         <f aca="false">'LW Assumptions'!$C$20+'LW Assumptions'!$C$21</f>
         <v>11.1428571428571</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="102" t="s">
-        <v>531</v>
-      </c>
-      <c r="B7" s="104" t="n">
+      <c r="A7" s="99" t="s">
+        <v>524</v>
+      </c>
+      <c r="B7" s="101" t="n">
         <v>7</v>
       </c>
-      <c r="C7" s="104" t="n">
+      <c r="C7" s="101" t="n">
         <f aca="false">'LW Assumptions'!$C$22</f>
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="95" t="s">
-        <v>532</v>
-      </c>
-      <c r="B9" s="101"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
+      <c r="A9" s="92" t="s">
+        <v>525</v>
+      </c>
+      <c r="B9" s="98"/>
+      <c r="C9" s="98"/>
+      <c r="D9" s="98"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="102" t="s">
-        <v>533</v>
-      </c>
-      <c r="B10" s="105" t="n">
+      <c r="A10" s="99" t="s">
+        <v>526</v>
+      </c>
+      <c r="B10" s="102" t="n">
         <v>111.8</v>
       </c>
-      <c r="C10" s="105" t="n">
+      <c r="C10" s="102" t="n">
         <f aca="false">('LW Assumptions'!$C$20+'LW Assumptions'!$C$21)*'LW Assumptions'!$C$22</f>
         <v>78</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="102" t="s">
-        <v>534</v>
-      </c>
-      <c r="B11" s="105" t="n">
+      <c r="A11" s="99" t="s">
+        <v>527</v>
+      </c>
+      <c r="B11" s="102" t="n">
         <v>13.3</v>
       </c>
-      <c r="C11" s="105" t="n">
+      <c r="C11" s="102" t="n">
         <f aca="false">B11</f>
         <v>13.3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="106" t="s">
-        <v>535</v>
-      </c>
-      <c r="B12" s="107" t="n">
+      <c r="A12" s="103" t="s">
+        <v>528</v>
+      </c>
+      <c r="B12" s="104" t="n">
         <v>125.1</v>
       </c>
-      <c r="C12" s="107" t="n">
+      <c r="C12" s="104" t="n">
         <f aca="false">('LW Assumptions'!$C$20+'LW Assumptions'!$C$21)*'LW Assumptions'!$C$22+C11</f>
         <v>91.3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="108"/>
-      <c r="B13" s="109"/>
-      <c r="C13" s="109"/>
+      <c r="A13" s="105"/>
+      <c r="B13" s="106"/>
+      <c r="C13" s="106"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="95" t="s">
-        <v>536</v>
-      </c>
-      <c r="B14" s="101"/>
-      <c r="C14" s="101"/>
-      <c r="D14" s="101"/>
+      <c r="A14" s="92" t="s">
+        <v>529</v>
+      </c>
+      <c r="B14" s="98"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="102" t="s">
-        <v>537</v>
-      </c>
-      <c r="B15" s="110" t="n">
+      <c r="A15" s="99" t="s">
+        <v>530</v>
+      </c>
+      <c r="B15" s="107" t="n">
         <v>2207</v>
       </c>
-      <c r="C15" s="110" t="n">
+      <c r="C15" s="107" t="n">
         <f aca="false">('LW Assumptions'!$C$20+'LW Assumptions'!$C$21)*'LW Assumptions'!$C$22*'LW Assumptions'!$C$23</f>
         <v>1560</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="102" t="s">
-        <v>538</v>
-      </c>
-      <c r="B16" s="110" t="n">
+      <c r="A16" s="99" t="s">
+        <v>531</v>
+      </c>
+      <c r="B16" s="107" t="n">
         <v>296</v>
       </c>
-      <c r="C16" s="110" t="n">
+      <c r="C16" s="107" t="n">
         <f aca="false">'LW Assumptions'!$C$26</f>
         <v>296</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="108" t="s">
-        <v>539</v>
-      </c>
-      <c r="B17" s="88" t="n">
+      <c r="A17" s="105" t="s">
+        <v>532</v>
+      </c>
+      <c r="B17" s="85" t="n">
         <v>2503</v>
       </c>
-      <c r="C17" s="88" t="n">
+      <c r="C17" s="85" t="n">
         <f aca="false">C15+C16</f>
         <v>1856</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="102" t="s">
-        <v>540</v>
-      </c>
-      <c r="B18" s="110" t="n">
+      <c r="A18" s="99" t="s">
+        <v>533</v>
+      </c>
+      <c r="B18" s="107" t="n">
         <f aca="false">'LW Assumptions'!$C$45/52</f>
         <v>247.692307692308</v>
       </c>
-      <c r="C18" s="110" t="n">
+      <c r="C18" s="107" t="n">
         <f aca="false">'LW Assumptions'!$C$45/52</f>
         <v>247.692307692308</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="102" t="s">
-        <v>541</v>
-      </c>
-      <c r="B19" s="110" t="n">
+      <c r="A19" s="99" t="s">
+        <v>534</v>
+      </c>
+      <c r="B19" s="107" t="n">
         <f aca="false">(B17+B18)*'LW Assumptions'!$C$24</f>
         <v>440.110769230769</v>
       </c>
-      <c r="C19" s="110" t="n">
+      <c r="C19" s="107" t="n">
         <f aca="false">(C17+C18)*'LW Assumptions'!$C$24</f>
         <v>336.590769230769</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="111" t="s">
-        <v>542</v>
-      </c>
-      <c r="B20" s="112" t="n">
+      <c r="A20" s="108" t="s">
+        <v>535</v>
+      </c>
+      <c r="B20" s="109" t="n">
         <f aca="false">B17+B18+B19</f>
         <v>3190.80307692308</v>
       </c>
-      <c r="C20" s="112" t="n">
+      <c r="C20" s="109" t="n">
         <f aca="false">C17+C18+C19</f>
         <v>2440.28307692308</v>
       </c>
-      <c r="D20" s="112" t="n">
+      <c r="D20" s="109" t="n">
         <f aca="false">C20-B20</f>
         <v>-750.52</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="113"/>
-      <c r="B21" s="114"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
+      <c r="A21" s="110"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="108" t="s">
-        <v>543</v>
-      </c>
-      <c r="B22" s="88" t="n">
+      <c r="A22" s="105" t="s">
+        <v>536</v>
+      </c>
+      <c r="B22" s="85" t="n">
         <f aca="false">B20*52</f>
         <v>165921.76</v>
       </c>
-      <c r="C22" s="88" t="n">
+      <c r="C22" s="85" t="n">
         <f aca="false">C20*52</f>
         <v>126894.72</v>
       </c>
-      <c r="D22" s="88" t="n">
+      <c r="D22" s="85" t="n">
         <f aca="false">C22-B22</f>
         <v>-39027.04</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="108"/>
-      <c r="B23" s="88"/>
-      <c r="C23" s="88"/>
-      <c r="D23" s="88"/>
+      <c r="A23" s="105"/>
+      <c r="B23" s="85"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="85"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="95" t="s">
-        <v>544</v>
-      </c>
-      <c r="B24" s="101"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="101"/>
+      <c r="A24" s="92" t="s">
+        <v>537</v>
+      </c>
+      <c r="B24" s="98"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="98"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="102" t="s">
-        <v>545</v>
-      </c>
-      <c r="B25" s="110" t="n">
+      <c r="A25" s="99" t="s">
+        <v>538</v>
+      </c>
+      <c r="B25" s="107" t="n">
         <v>5888.94</v>
       </c>
-      <c r="C25" s="110" t="n">
+      <c r="C25" s="107" t="n">
         <v>5888.94</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="108" t="s">
-        <v>546</v>
-      </c>
-      <c r="B26" s="115" t="n">
+      <c r="A26" s="105" t="s">
+        <v>539</v>
+      </c>
+      <c r="B26" s="112" t="n">
         <f aca="false">B20/B25</f>
         <v>0.541829782086942</v>
       </c>
-      <c r="C26" s="115" t="n">
+      <c r="C26" s="112" t="n">
         <f aca="false">C20/C25</f>
         <v>0.414384095766484</v>
       </c>
-      <c r="D26" s="115" t="n">
+      <c r="D26" s="112" t="n">
         <f aca="false">C26-B26</f>
         <v>-0.127445686320458</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="108"/>
-      <c r="B27" s="115"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="115"/>
+      <c r="A27" s="105"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="112"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="116" t="s">
-        <v>547</v>
-      </c>
-      <c r="B28" s="116"/>
-      <c r="C28" s="116"/>
-      <c r="D28" s="116"/>
+      <c r="A28" s="113" t="s">
+        <v>540</v>
+      </c>
+      <c r="B28" s="113"/>
+      <c r="C28" s="113"/>
+      <c r="D28" s="113"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="108" t="s">
-        <v>548</v>
-      </c>
-      <c r="C29" s="88" t="n">
+      <c r="A29" s="105" t="s">
+        <v>541</v>
+      </c>
+      <c r="C29" s="85" t="n">
         <f aca="false">B20-C20</f>
         <v>750.52</v>
       </c>
-      <c r="D29" s="88" t="n">
+      <c r="D29" s="85" t="n">
         <f aca="false">C22-B22</f>
         <v>-39027.04</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="117" t="s">
-        <v>549</v>
+      <c r="A31" s="114" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="118" t="s">
-        <v>550</v>
-      </c>
-      <c r="B32" s="118"/>
-      <c r="C32" s="118"/>
-      <c r="D32" s="118"/>
+      <c r="A32" s="115" t="s">
+        <v>543</v>
+      </c>
+      <c r="B32" s="115"/>
+      <c r="C32" s="115"/>
+      <c r="D32" s="115"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="118"/>
-      <c r="B33" s="118"/>
-      <c r="C33" s="118"/>
-      <c r="D33" s="118"/>
+      <c r="A33" s="115"/>
+      <c r="B33" s="115"/>
+      <c r="C33" s="115"/>
+      <c r="D33" s="115"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="117" t="s">
-        <v>551</v>
+      <c r="A35" s="114" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="118" t="s">
-        <v>552</v>
-      </c>
-      <c r="B36" s="118"/>
-      <c r="C36" s="118"/>
-      <c r="D36" s="118"/>
+      <c r="A36" s="115" t="s">
+        <v>545</v>
+      </c>
+      <c r="B36" s="115"/>
+      <c r="C36" s="115"/>
+      <c r="D36" s="115"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="118"/>
-      <c r="B37" s="118"/>
-      <c r="C37" s="118"/>
-      <c r="D37" s="118"/>
+      <c r="A37" s="115"/>
+      <c r="B37" s="115"/>
+      <c r="C37" s="115"/>
+      <c r="D37" s="115"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="119" t="s">
-        <v>553</v>
+      <c r="A39" s="116" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="118" t="s">
-        <v>554</v>
-      </c>
-      <c r="B40" s="118"/>
-      <c r="C40" s="118"/>
-      <c r="D40" s="118"/>
+      <c r="A40" s="115" t="s">
+        <v>547</v>
+      </c>
+      <c r="B40" s="115"/>
+      <c r="C40" s="115"/>
+      <c r="D40" s="115"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="118"/>
-      <c r="B41" s="118"/>
-      <c r="C41" s="118"/>
-      <c r="D41" s="118"/>
+      <c r="A41" s="115"/>
+      <c r="B41" s="115"/>
+      <c r="C41" s="115"/>
+      <c r="D41" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -33215,29 +33181,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4" t="s">
         <v>255</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>2411</v>
@@ -33249,7 +33215,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="C6" s="24" t="n">
         <v>89592</v>
@@ -33261,7 +33227,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="C7" s="24" t="n">
         <v>13203</v>
@@ -33273,7 +33239,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>27886</v>
@@ -33285,7 +33251,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C9" s="27" t="n">
         <f aca="false">SUM(C5:C8)</f>
@@ -33294,22 +33260,22 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33404,27 +33370,27 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4" t="s">
         <v>255</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="C22" s="24" t="n">
         <v>5637</v>
@@ -33434,12 +33400,12 @@
         <v>0.20214444524134</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="C23" s="24" t="n">
         <v>3913</v>
@@ -33449,12 +33415,12 @@
         <v>0.140321308183318</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="C24" s="24" t="n">
         <v>3678</v>
@@ -33464,12 +33430,12 @@
         <v>0.131894140428889</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>2744</v>
@@ -33479,12 +33445,12 @@
         <v>0.0984006311410744</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>2071</v>
@@ -33494,12 +33460,12 @@
         <v>0.0742666571039231</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>1937</v>
@@ -33509,12 +33475,12 @@
         <v>0.0694613784694829</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C28" s="24" t="n">
         <v>1726</v>
@@ -33524,12 +33490,12 @@
         <v>0.0618948576346554</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="C29" s="24" t="n">
         <v>1029</v>
@@ -33539,12 +33505,12 @@
         <v>0.0369002366779029</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="C30" s="24" t="n">
         <v>902</v>
@@ -33554,12 +33520,12 @@
         <v>0.0323459800616797</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="C31" s="24" t="n">
         <v>612</v>
@@ -33569,12 +33535,12 @@
         <v>0.0219464964498315</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="C32" s="24" t="n">
         <v>514</v>
@@ -33584,12 +33550,12 @@
         <v>0.0184321881947931</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="C33" s="24" t="n">
         <v>501</v>
@@ -33599,12 +33565,12 @@
         <v>0.0179660044466758</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="C34" s="24" t="n">
         <v>378</v>
@@ -33614,12 +33580,12 @@
         <v>0.0135551889837194</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="C35" s="24" t="n">
         <v>335</v>
@@ -33629,12 +33595,12 @@
         <v>0.0120131965861006</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="C36" s="24" t="n">
         <v>333</v>
@@ -33644,12 +33610,12 @@
         <v>0.0119414760094671</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="C37" s="24" t="n">
         <v>267</v>
@@ -33659,12 +33625,12 @@
         <v>0.00957469698056373</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="C38" s="24" t="n">
         <v>260</v>
@@ -33674,12 +33640,12 @@
         <v>0.0093236749623467</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="C39" s="24" t="n">
         <v>337</v>
@@ -33689,12 +33655,12 @@
         <v>0.012084917162734</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="C40" s="24" t="n">
         <v>712</v>
@@ -33704,12 +33670,12 @@
         <v>0.0255325252815033</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="C41" s="27" t="n">
         <f aca="false">SUMIF(E22:E40,"BARISTA",C22:C40)</f>
@@ -33722,7 +33688,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="C42" s="7" t="n">
         <f aca="false">C8-C41</f>
@@ -33735,7 +33701,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -33743,7 +33709,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="C45" s="24" t="n">
         <f aca="false">C41*2</f>
@@ -33752,15 +33718,15 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="C46" s="120" t="n">
+        <v>590</v>
+      </c>
+      <c r="C46" s="117" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="C47" s="24" t="n">
         <f aca="false">C45*C46</f>
@@ -33769,7 +33735,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="C48" s="7" t="n">
         <f aca="false">-C47*0.685</f>
@@ -33778,18 +33744,18 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C49" s="121" t="n">
+        <v>593</v>
+      </c>
+      <c r="C49" s="118" t="n">
         <v>0.25</v>
       </c>
-      <c r="D49" s="121" t="n">
+      <c r="D49" s="118" t="n">
         <v>0.5</v>
       </c>
-      <c r="E49" s="121" t="n">
+      <c r="E49" s="118" t="n">
         <v>0.75</v>
       </c>
-      <c r="F49" s="121" t="n">
+      <c r="F49" s="118" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33813,7 +33779,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -33821,7 +33787,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="C53" s="24" t="n">
         <v>2411</v>
@@ -33829,7 +33795,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="C54" s="24" t="n">
         <f aca="false">C53*2</f>
@@ -33838,12 +33804,12 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="B58" s="38"/>
       <c r="C58" s="38"/>
@@ -33853,7 +33819,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="C59" s="24" t="n">
         <v>42319</v>
@@ -33862,12 +33828,12 @@
         <v>0.173</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="C60" s="24" t="n">
         <v>9118</v>
@@ -33876,12 +33842,12 @@
         <v>0.215</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="C61" s="24" t="n">
         <v>33201</v>
@@ -33890,12 +33856,12 @@
         <v>0.785</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="C62" s="24" t="n">
         <v>14404</v>
@@ -33904,12 +33870,12 @@
         <v>0.059</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="C63" s="24" t="n">
         <v>3007</v>
@@ -33918,17 +33884,17 @@
         <v>0.012</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="B67" s="38"/>
       <c r="C67" s="38"/>
@@ -33938,7 +33904,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="C68" s="24" t="n">
         <f aca="false">4*7*52*'LW Assumptions'!$C$23*(1+'LW Assumptions'!$C$24)</f>
@@ -33947,7 +33913,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="C69" s="24" t="n">
         <f aca="false">C60*0.685</f>
@@ -33956,7 +33922,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="C70" s="7" t="n">
         <f aca="false">C68-C69</f>
@@ -33993,8 +33959,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="122" t="s">
-        <v>621</v>
+      <c r="A1" s="119" t="s">
+        <v>614</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -34008,379 +33974,379 @@
       <c r="K1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="100" t="s">
-        <v>622</v>
-      </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
+      <c r="A2" s="97" t="s">
+        <v>615</v>
+      </c>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="117" t="s">
-        <v>623</v>
-      </c>
-      <c r="B4" s="123" t="s">
-        <v>624</v>
-      </c>
-      <c r="C4" s="124" t="n">
+      <c r="A4" s="114" t="s">
+        <v>616</v>
+      </c>
+      <c r="B4" s="120" t="s">
+        <v>617</v>
+      </c>
+      <c r="C4" s="121" t="n">
         <f aca="false">'LW Assumptions'!$C$23</f>
         <v>20</v>
       </c>
-      <c r="D4" s="123" t="s">
-        <v>625</v>
-      </c>
-      <c r="E4" s="124" t="n">
+      <c r="D4" s="120" t="s">
+        <v>618</v>
+      </c>
+      <c r="E4" s="121" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="42" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="122" t="s">
+        <v>620</v>
+      </c>
+      <c r="B7" s="122" t="s">
+        <v>489</v>
+      </c>
+      <c r="C7" s="123" t="s">
+        <v>621</v>
+      </c>
+      <c r="D7" s="123" t="s">
+        <v>622</v>
+      </c>
+      <c r="E7" s="123" t="s">
+        <v>623</v>
+      </c>
+      <c r="F7" s="123" t="s">
+        <v>624</v>
+      </c>
+      <c r="G7" s="123" t="s">
+        <v>625</v>
+      </c>
+      <c r="H7" s="123" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="125" t="s">
+      <c r="I7" s="123" t="s">
         <v>627</v>
       </c>
-      <c r="B7" s="125" t="s">
-        <v>496</v>
-      </c>
-      <c r="C7" s="126" t="s">
+      <c r="J7" s="123" t="s">
         <v>628</v>
       </c>
-      <c r="D7" s="126" t="s">
+      <c r="K7" s="123" t="s">
         <v>629</v>
       </c>
-      <c r="E7" s="126" t="s">
+      <c r="L7" s="123" t="s">
         <v>630</v>
       </c>
-      <c r="F7" s="126" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="124" t="s">
         <v>631</v>
       </c>
-      <c r="G7" s="126" t="s">
+      <c r="B8" s="125" t="s">
         <v>632</v>
       </c>
-      <c r="H7" s="126" t="s">
-        <v>633</v>
-      </c>
-      <c r="I7" s="126" t="s">
-        <v>634</v>
-      </c>
-      <c r="J7" s="126" t="s">
-        <v>635</v>
-      </c>
-      <c r="K7" s="126" t="s">
-        <v>636</v>
-      </c>
-      <c r="L7" s="126" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="127" t="s">
-        <v>638</v>
-      </c>
-      <c r="B8" s="128" t="s">
-        <v>639</v>
-      </c>
-      <c r="C8" s="129" t="n">
+      <c r="C8" s="126" t="n">
         <v>18.29</v>
       </c>
-      <c r="D8" s="130" t="n">
+      <c r="D8" s="127" t="n">
         <f aca="false">6*$C8</f>
         <v>109.74</v>
       </c>
-      <c r="E8" s="130" t="n">
+      <c r="E8" s="127" t="n">
         <f aca="false">7.75*$C8</f>
         <v>141.7475</v>
       </c>
-      <c r="F8" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="132" t="n">
+      <c r="F8" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="129" t="n">
         <v>13.75</v>
       </c>
-      <c r="L8" s="133" t="n">
+      <c r="L8" s="130" t="n">
         <f aca="false">SUM(D8:J8)</f>
         <v>251.4875</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="127" t="s">
-        <v>638</v>
-      </c>
-      <c r="B9" s="128" t="s">
-        <v>640</v>
-      </c>
-      <c r="C9" s="129" t="n">
+      <c r="A9" s="124" t="s">
+        <v>631</v>
+      </c>
+      <c r="B9" s="125" t="s">
+        <v>633</v>
+      </c>
+      <c r="C9" s="126" t="n">
         <v>21.03</v>
       </c>
-      <c r="D9" s="130" t="n">
+      <c r="D9" s="127" t="n">
         <f aca="false">1.75*$C9</f>
         <v>36.8025</v>
       </c>
-      <c r="E9" s="130" t="n">
+      <c r="E9" s="127" t="n">
         <f aca="false">1.75*$C9</f>
         <v>36.8025</v>
       </c>
-      <c r="F9" s="130" t="n">
+      <c r="F9" s="127" t="n">
         <f aca="false">7.75*$C9</f>
         <v>162.9825</v>
       </c>
-      <c r="G9" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="132" t="n">
+      <c r="G9" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="129" t="n">
         <v>11.25</v>
       </c>
-      <c r="L9" s="133" t="n">
+      <c r="L9" s="130" t="n">
         <f aca="false">SUM(D9:J9)</f>
         <v>236.5875</v>
       </c>
-      <c r="M9" s="134" t="s">
-        <v>641</v>
+      <c r="M9" s="131" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="127" t="s">
-        <v>642</v>
-      </c>
-      <c r="B10" s="128" t="s">
-        <v>639</v>
-      </c>
-      <c r="C10" s="129" t="n">
+      <c r="A10" s="124" t="s">
+        <v>635</v>
+      </c>
+      <c r="B10" s="125" t="s">
+        <v>632</v>
+      </c>
+      <c r="C10" s="126" t="n">
         <v>17.79</v>
       </c>
-      <c r="D10" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="130" t="n">
+      <c r="D10" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="127" t="n">
         <f aca="false">8*$C10</f>
         <v>142.32</v>
       </c>
-      <c r="I10" s="130" t="n">
+      <c r="I10" s="127" t="n">
         <f aca="false">8*$C10</f>
         <v>142.32</v>
       </c>
-      <c r="J10" s="130" t="n">
+      <c r="J10" s="127" t="n">
         <f aca="false">8*$C10</f>
         <v>142.32</v>
       </c>
-      <c r="K10" s="132" t="n">
+      <c r="K10" s="129" t="n">
         <v>24</v>
       </c>
-      <c r="L10" s="133" t="n">
+      <c r="L10" s="130" t="n">
         <f aca="false">SUM(D10:J10)</f>
         <v>426.96</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="127" t="s">
-        <v>643</v>
-      </c>
-      <c r="B11" s="128" t="s">
-        <v>644</v>
-      </c>
-      <c r="C11" s="129" t="n">
+      <c r="A11" s="124" t="s">
+        <v>636</v>
+      </c>
+      <c r="B11" s="125" t="s">
+        <v>637</v>
+      </c>
+      <c r="C11" s="126" t="n">
         <v>19.79</v>
       </c>
-      <c r="D11" s="130" t="n">
+      <c r="D11" s="127" t="n">
         <f aca="false">8*$C11</f>
         <v>158.32</v>
       </c>
-      <c r="E11" s="130" t="n">
+      <c r="E11" s="127" t="n">
         <f aca="false">8*$C11</f>
         <v>158.32</v>
       </c>
-      <c r="F11" s="130" t="n">
+      <c r="F11" s="127" t="n">
         <f aca="false">8*$C11</f>
         <v>158.32</v>
       </c>
-      <c r="G11" s="130" t="n">
+      <c r="G11" s="127" t="n">
         <f aca="false">8*$C11</f>
         <v>158.32</v>
       </c>
-      <c r="H11" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="130" t="n">
+      <c r="H11" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="127" t="n">
         <f aca="false">3*$C11</f>
         <v>59.37</v>
       </c>
-      <c r="K11" s="132" t="n">
+      <c r="K11" s="129" t="n">
         <v>35</v>
       </c>
-      <c r="L11" s="133" t="n">
+      <c r="L11" s="130" t="n">
         <f aca="false">SUM(D11:J11)</f>
         <v>692.65</v>
       </c>
-      <c r="M11" s="134" t="s">
-        <v>645</v>
+      <c r="M11" s="131" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="127" t="s">
-        <v>646</v>
-      </c>
-      <c r="B12" s="128" t="s">
-        <v>644</v>
-      </c>
-      <c r="C12" s="129" t="n">
+      <c r="A12" s="124" t="s">
+        <v>639</v>
+      </c>
+      <c r="B12" s="125" t="s">
+        <v>637</v>
+      </c>
+      <c r="C12" s="126" t="n">
         <v>21.21</v>
       </c>
-      <c r="D12" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="130" t="n">
+      <c r="D12" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="127" t="n">
         <f aca="false">8*$C12</f>
         <v>169.68</v>
       </c>
-      <c r="G12" s="130" t="n">
+      <c r="G12" s="127" t="n">
         <f aca="false">8*$C12</f>
         <v>169.68</v>
       </c>
-      <c r="H12" s="130" t="n">
+      <c r="H12" s="127" t="n">
         <f aca="false">8*$C12</f>
         <v>169.68</v>
       </c>
-      <c r="I12" s="130" t="n">
+      <c r="I12" s="127" t="n">
         <f aca="false">8*$C12</f>
         <v>169.68</v>
       </c>
-      <c r="J12" s="130" t="n">
+      <c r="J12" s="127" t="n">
         <f aca="false">8*$C12</f>
         <v>169.68</v>
       </c>
-      <c r="K12" s="132" t="n">
+      <c r="K12" s="129" t="n">
         <v>40</v>
       </c>
-      <c r="L12" s="133" t="n">
+      <c r="L12" s="130" t="n">
         <f aca="false">SUM(D12:J12)</f>
         <v>848.4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="127" t="s">
-        <v>647</v>
-      </c>
-      <c r="B13" s="128" t="s">
-        <v>648</v>
-      </c>
-      <c r="C13" s="129" t="n">
+      <c r="A13" s="124" t="s">
+        <v>640</v>
+      </c>
+      <c r="B13" s="125" t="s">
+        <v>641</v>
+      </c>
+      <c r="C13" s="126" t="n">
         <v>25</v>
       </c>
-      <c r="D13" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="130" t="n">
+      <c r="D13" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="127" t="n">
         <f aca="false">8*$C13</f>
         <v>200</v>
       </c>
-      <c r="H13" s="130" t="n">
+      <c r="H13" s="127" t="n">
         <f aca="false">8*$C13</f>
         <v>200</v>
       </c>
-      <c r="I13" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="132" t="n">
+      <c r="I13" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="129" t="n">
         <v>16</v>
       </c>
-      <c r="L13" s="133" t="n">
+      <c r="L13" s="130" t="n">
         <f aca="false">SUM(D13:J13)</f>
         <v>400</v>
       </c>
-      <c r="M13" s="134" t="s">
-        <v>649</v>
+      <c r="M13" s="131" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="95" t="s">
-        <v>650</v>
-      </c>
-      <c r="B14" s="101"/>
-      <c r="C14" s="135"/>
-      <c r="D14" s="135" t="n">
+      <c r="A14" s="92" t="s">
+        <v>643</v>
+      </c>
+      <c r="B14" s="98"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132" t="n">
         <f aca="false">SUM(D8:D13)</f>
         <v>304.8625</v>
       </c>
-      <c r="E14" s="135" t="n">
+      <c r="E14" s="132" t="n">
         <f aca="false">SUM(E8:E13)</f>
         <v>336.87</v>
       </c>
-      <c r="F14" s="135" t="n">
+      <c r="F14" s="132" t="n">
         <f aca="false">SUM(F8:F13)</f>
         <v>490.9825</v>
       </c>
-      <c r="G14" s="135" t="n">
+      <c r="G14" s="132" t="n">
         <f aca="false">SUM(G8:G13)</f>
         <v>528</v>
       </c>
-      <c r="H14" s="135" t="n">
+      <c r="H14" s="132" t="n">
         <f aca="false">SUM(H8:H13)</f>
         <v>512</v>
       </c>
-      <c r="I14" s="135" t="n">
+      <c r="I14" s="132" t="n">
         <f aca="false">SUM(I8:I13)</f>
         <v>312</v>
       </c>
-      <c r="J14" s="135" t="n">
+      <c r="J14" s="132" t="n">
         <f aca="false">SUM(J8:J13)</f>
         <v>371.37</v>
       </c>
-      <c r="K14" s="136" t="n">
+      <c r="K14" s="133" t="n">
         <f aca="false">SUM(K8:K13)</f>
         <v>140</v>
       </c>
@@ -34388,236 +34354,236 @@
         <f aca="false">SUM(L8:L13)</f>
         <v>2856.085</v>
       </c>
-      <c r="M14" s="128" t="s">
+      <c r="M14" s="125" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="134" t="s">
+        <v>645</v>
+      </c>
+      <c r="B17" s="134"/>
+      <c r="C17" s="134"/>
+      <c r="D17" s="134"/>
+      <c r="E17" s="134"/>
+      <c r="F17" s="134"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="134"/>
+      <c r="K17" s="134"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="122"/>
+      <c r="B18" s="122" t="s">
+        <v>646</v>
+      </c>
+      <c r="D18" s="123" t="s">
+        <v>647</v>
+      </c>
+      <c r="F18" s="123" t="s">
+        <v>648</v>
+      </c>
+      <c r="G18" s="123" t="s">
+        <v>649</v>
+      </c>
+      <c r="H18" s="123" t="s">
+        <v>650</v>
+      </c>
+      <c r="J18" s="123" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="137" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="114" t="s">
         <v>652</v>
       </c>
-      <c r="B17" s="137"/>
-      <c r="C17" s="137"/>
-      <c r="D17" s="137"/>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="137"/>
-      <c r="H17" s="137"/>
-      <c r="I17" s="137"/>
-      <c r="J17" s="137"/>
-      <c r="K17" s="137"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="125"/>
-      <c r="B18" s="125" t="s">
+      <c r="B19" s="124" t="s">
         <v>653</v>
       </c>
-      <c r="D18" s="126" t="s">
+      <c r="D19" s="135" t="s">
         <v>654</v>
       </c>
-      <c r="F18" s="126" t="s">
+      <c r="F19" s="136" t="s">
         <v>655</v>
       </c>
-      <c r="G18" s="126" t="s">
-        <v>656</v>
-      </c>
-      <c r="H18" s="126" t="s">
-        <v>657</v>
-      </c>
-      <c r="J18" s="126" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="117" t="s">
-        <v>659</v>
-      </c>
-      <c r="B19" s="127" t="s">
-        <v>660</v>
-      </c>
-      <c r="D19" s="138" t="s">
-        <v>661</v>
-      </c>
-      <c r="F19" s="139" t="s">
-        <v>662</v>
-      </c>
-      <c r="G19" s="140" t="n">
+      <c r="G19" s="137" t="n">
         <v>8</v>
       </c>
-      <c r="H19" s="130" t="n">
+      <c r="H19" s="127" t="n">
         <f aca="false">8*$C$4</f>
         <v>160</v>
       </c>
-      <c r="J19" s="133" t="n">
+      <c r="J19" s="130" t="n">
         <f aca="false">H19*7</f>
         <v>1120</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="117"/>
-      <c r="B20" s="127" t="s">
-        <v>663</v>
-      </c>
-      <c r="D20" s="138" t="s">
-        <v>664</v>
-      </c>
-      <c r="F20" s="139" t="s">
-        <v>662</v>
-      </c>
-      <c r="G20" s="140" t="n">
+      <c r="A20" s="114"/>
+      <c r="B20" s="124" t="s">
+        <v>656</v>
+      </c>
+      <c r="D20" s="135" t="s">
+        <v>657</v>
+      </c>
+      <c r="F20" s="136" t="s">
+        <v>655</v>
+      </c>
+      <c r="G20" s="137" t="n">
         <v>8</v>
       </c>
-      <c r="H20" s="130" t="n">
+      <c r="H20" s="127" t="n">
         <f aca="false">8*$C$4</f>
         <v>160</v>
       </c>
-      <c r="J20" s="133" t="n">
+      <c r="J20" s="130" t="n">
         <f aca="false">H20*7</f>
         <v>1120</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="117"/>
-      <c r="B21" s="127" t="s">
-        <v>665</v>
-      </c>
-      <c r="D21" s="138" t="s">
-        <v>666</v>
-      </c>
-      <c r="F21" s="139" t="s">
-        <v>667</v>
-      </c>
-      <c r="G21" s="140" t="n">
+      <c r="A21" s="114"/>
+      <c r="B21" s="124" t="s">
+        <v>658</v>
+      </c>
+      <c r="D21" s="135" t="s">
+        <v>659</v>
+      </c>
+      <c r="F21" s="136" t="s">
+        <v>660</v>
+      </c>
+      <c r="G21" s="137" t="n">
         <v>4</v>
       </c>
-      <c r="H21" s="130" t="n">
+      <c r="H21" s="127" t="n">
         <f aca="false">4*$E$4</f>
         <v>100</v>
       </c>
-      <c r="J21" s="133" t="n">
+      <c r="J21" s="130" t="n">
         <f aca="false">H21*7</f>
         <v>700</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="141" t="s">
-        <v>668</v>
-      </c>
-      <c r="B22" s="101"/>
-      <c r="D22" s="101"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="136" t="n">
+      <c r="A22" s="138" t="s">
+        <v>661</v>
+      </c>
+      <c r="B22" s="98"/>
+      <c r="D22" s="98"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="133" t="n">
         <f aca="false">G19+G20+G21</f>
         <v>20</v>
       </c>
-      <c r="H22" s="135" t="n">
+      <c r="H22" s="132" t="n">
         <f aca="false">H19+H20+H21</f>
         <v>420</v>
       </c>
-      <c r="J22" s="135" t="n">
+      <c r="J22" s="132" t="n">
         <f aca="false">H22*7</f>
         <v>2940</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="141" t="s">
-        <v>669</v>
-      </c>
-      <c r="B24" s="142" t="s">
-        <v>670</v>
-      </c>
-      <c r="C24" s="101"/>
-      <c r="D24" s="143" t="s">
-        <v>671</v>
-      </c>
-      <c r="E24" s="101"/>
-      <c r="F24" s="144" t="s">
-        <v>672</v>
-      </c>
-      <c r="G24" s="145" t="n">
+      <c r="A24" s="138" t="s">
+        <v>662</v>
+      </c>
+      <c r="B24" s="139" t="s">
+        <v>663</v>
+      </c>
+      <c r="C24" s="98"/>
+      <c r="D24" s="140" t="s">
+        <v>664</v>
+      </c>
+      <c r="E24" s="98"/>
+      <c r="F24" s="141" t="s">
+        <v>665</v>
+      </c>
+      <c r="G24" s="142" t="n">
         <v>10</v>
       </c>
-      <c r="H24" s="146" t="n">
+      <c r="H24" s="143" t="n">
         <f aca="false">10*$C$4</f>
         <v>200</v>
       </c>
-      <c r="I24" s="101"/>
-      <c r="J24" s="135" t="n">
+      <c r="I24" s="98"/>
+      <c r="J24" s="132" t="n">
         <f aca="false">H24*7</f>
         <v>1400</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="147"/>
-      <c r="B25" s="148" t="s">
-        <v>673</v>
-      </c>
-      <c r="C25" s="149"/>
-      <c r="D25" s="150" t="s">
-        <v>674</v>
-      </c>
-      <c r="E25" s="149"/>
-      <c r="F25" s="151" t="s">
-        <v>675</v>
-      </c>
-      <c r="G25" s="152" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="153" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="149"/>
-      <c r="J25" s="154" t="n">
+      <c r="A25" s="144"/>
+      <c r="B25" s="145" t="s">
+        <v>666</v>
+      </c>
+      <c r="C25" s="146"/>
+      <c r="D25" s="147" t="s">
+        <v>667</v>
+      </c>
+      <c r="E25" s="146"/>
+      <c r="F25" s="148" t="s">
+        <v>668</v>
+      </c>
+      <c r="G25" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="146"/>
+      <c r="J25" s="151" t="n">
         <f aca="false">H25*7</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="141" t="s">
-        <v>676</v>
-      </c>
-      <c r="B26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="136" t="n">
+      <c r="A26" s="138" t="s">
+        <v>669</v>
+      </c>
+      <c r="B26" s="98"/>
+      <c r="D26" s="98"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="133" t="n">
         <v>10</v>
       </c>
-      <c r="H26" s="135" t="n">
+      <c r="H26" s="132" t="n">
         <f aca="false">10*$C$4</f>
         <v>200</v>
       </c>
-      <c r="J26" s="135" t="n">
+      <c r="J26" s="132" t="n">
         <f aca="false">H26*7</f>
         <v>1400</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="155" t="s">
-        <v>677</v>
-      </c>
-      <c r="B28" s="155"/>
-      <c r="C28" s="155"/>
-      <c r="D28" s="155"/>
-      <c r="E28" s="155"/>
-      <c r="F28" s="155"/>
-      <c r="G28" s="155"/>
-      <c r="H28" s="155"/>
-      <c r="I28" s="155"/>
-      <c r="J28" s="155"/>
-      <c r="K28" s="155"/>
+      <c r="A28" s="152" t="s">
+        <v>670</v>
+      </c>
+      <c r="B28" s="152"/>
+      <c r="C28" s="152"/>
+      <c r="D28" s="152"/>
+      <c r="E28" s="152"/>
+      <c r="F28" s="152"/>
+      <c r="G28" s="152"/>
+      <c r="H28" s="152"/>
+      <c r="I28" s="152"/>
+      <c r="J28" s="152"/>
+      <c r="K28" s="152"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="155"/>
-      <c r="B29" s="155"/>
-      <c r="C29" s="155"/>
-      <c r="D29" s="155"/>
-      <c r="E29" s="155"/>
-      <c r="F29" s="155"/>
-      <c r="G29" s="155"/>
-      <c r="H29" s="155"/>
-      <c r="I29" s="155"/>
-      <c r="J29" s="155"/>
-      <c r="K29" s="155"/>
+      <c r="A29" s="152"/>
+      <c r="B29" s="152"/>
+      <c r="C29" s="152"/>
+      <c r="D29" s="152"/>
+      <c r="E29" s="152"/>
+      <c r="F29" s="152"/>
+      <c r="G29" s="152"/>
+      <c r="H29" s="152"/>
+      <c r="I29" s="152"/>
+      <c r="J29" s="152"/>
+      <c r="K29" s="152"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -34649,151 +34615,151 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="156" t="s">
-        <v>678</v>
+      <c r="A1" s="153" t="s">
+        <v>671</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
       <c r="D1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="157" t="s">
-        <v>679</v>
-      </c>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
+      <c r="A2" s="154" t="s">
+        <v>672</v>
+      </c>
+      <c r="B2" s="154"/>
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="86" t="s">
-        <v>680</v>
+      <c r="A4" s="83" t="s">
+        <v>673</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>682</v>
-      </c>
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
+        <v>675</v>
+      </c>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="102" t="s">
-        <v>683</v>
-      </c>
-      <c r="B6" s="110" t="n">
+      <c r="A6" s="99" t="s">
+        <v>676</v>
+      </c>
+      <c r="B6" s="107" t="n">
         <v>119121</v>
       </c>
-      <c r="C6" s="110" t="n">
+      <c r="C6" s="107" t="n">
         <f aca="false">B6/12</f>
         <v>9926.75</v>
       </c>
-      <c r="D6" s="158" t="n">
+      <c r="D6" s="155" t="n">
         <f aca="false">B6/258287</f>
         <v>0.461196266169029</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="102" t="s">
-        <v>684</v>
-      </c>
-      <c r="B7" s="110" t="n">
+      <c r="A7" s="99" t="s">
+        <v>677</v>
+      </c>
+      <c r="B7" s="107" t="n">
         <v>133545</v>
       </c>
-      <c r="C7" s="110" t="n">
+      <c r="C7" s="107" t="n">
         <f aca="false">B7/12</f>
         <v>11128.75</v>
       </c>
-      <c r="D7" s="158" t="n">
+      <c r="D7" s="155" t="n">
         <f aca="false">B7/258287</f>
         <v>0.517041120923624</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="102" t="s">
-        <v>685</v>
-      </c>
-      <c r="B8" s="110" t="n">
+      <c r="A8" s="99" t="s">
+        <v>678</v>
+      </c>
+      <c r="B8" s="107" t="n">
         <v>17887</v>
       </c>
-      <c r="C8" s="110" t="n">
+      <c r="C8" s="107" t="n">
         <f aca="false">B8/12</f>
         <v>1490.58333333333</v>
       </c>
-      <c r="D8" s="158" t="n">
+      <c r="D8" s="155" t="n">
         <f aca="false">B8/258287</f>
         <v>0.0692524207567551</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="102" t="s">
-        <v>686</v>
-      </c>
-      <c r="B9" s="110" t="n">
+      <c r="A9" s="99" t="s">
+        <v>679</v>
+      </c>
+      <c r="B9" s="107" t="n">
         <v>6836</v>
       </c>
-      <c r="C9" s="110" t="n">
+      <c r="C9" s="107" t="n">
         <f aca="false">B9/12</f>
         <v>569.666666666667</v>
       </c>
-      <c r="D9" s="158" t="n">
+      <c r="D9" s="155" t="n">
         <f aca="false">B9/258287</f>
         <v>0.026466682411426</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="102" t="s">
-        <v>687</v>
-      </c>
-      <c r="B10" s="110" t="n">
+      <c r="A10" s="99" t="s">
+        <v>680</v>
+      </c>
+      <c r="B10" s="107" t="n">
         <v>-20307</v>
       </c>
-      <c r="C10" s="110" t="n">
+      <c r="C10" s="107" t="n">
         <f aca="false">B10/12</f>
         <v>-1692.25</v>
       </c>
-      <c r="D10" s="158" t="n">
+      <c r="D10" s="155" t="n">
         <f aca="false">B10/258287</f>
         <v>-0.0786218431434799</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="102" t="s">
-        <v>688</v>
-      </c>
-      <c r="B11" s="110" t="n">
+      <c r="A11" s="99" t="s">
+        <v>681</v>
+      </c>
+      <c r="B11" s="107" t="n">
         <v>1204</v>
       </c>
-      <c r="C11" s="110" t="n">
+      <c r="C11" s="107" t="n">
         <f aca="false">B11/12</f>
         <v>100.333333333333</v>
       </c>
-      <c r="D11" s="158" t="n">
+      <c r="D11" s="155" t="n">
         <f aca="false">B11/258287</f>
         <v>0.00466148122050277</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="B12" s="45" t="n">
         <v>258287</v>
       </c>
-      <c r="C12" s="159" t="n">
+      <c r="C12" s="156" t="n">
         <f aca="false">B12/12</f>
         <v>21523.9166666667</v>
       </c>
-      <c r="D12" s="160" t="n">
+      <c r="D12" s="157" t="n">
         <f aca="false">B12/258287</f>
         <v>1</v>
       </c>
@@ -34805,104 +34771,104 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="44" t="s">
-        <v>690</v>
-      </c>
-      <c r="B14" s="161"/>
-      <c r="C14" s="162"/>
-      <c r="D14" s="162"/>
+        <v>683</v>
+      </c>
+      <c r="B14" s="158"/>
+      <c r="C14" s="159"/>
+      <c r="D14" s="159"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="102" t="s">
-        <v>691</v>
-      </c>
-      <c r="B15" s="110" t="n">
+      <c r="A15" s="99" t="s">
+        <v>684</v>
+      </c>
+      <c r="B15" s="107" t="n">
         <v>48655</v>
       </c>
-      <c r="C15" s="110" t="n">
+      <c r="C15" s="107" t="n">
         <f aca="false">B15/12</f>
         <v>4054.58333333333</v>
       </c>
-      <c r="D15" s="158" t="n">
+      <c r="D15" s="155" t="n">
         <f aca="false">B15/258287</f>
         <v>0.188375721581032</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="102" t="s">
-        <v>692</v>
-      </c>
-      <c r="B16" s="110" t="n">
+      <c r="A16" s="99" t="s">
+        <v>685</v>
+      </c>
+      <c r="B16" s="107" t="n">
         <v>27428</v>
       </c>
-      <c r="C16" s="110" t="n">
+      <c r="C16" s="107" t="n">
         <f aca="false">B16/12</f>
         <v>2285.66666666667</v>
       </c>
-      <c r="D16" s="158" t="n">
+      <c r="D16" s="155" t="n">
         <f aca="false">B16/258287</f>
         <v>0.106191949265739</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="102" t="s">
-        <v>693</v>
-      </c>
-      <c r="B17" s="110" t="n">
+      <c r="A17" s="99" t="s">
+        <v>686</v>
+      </c>
+      <c r="B17" s="107" t="n">
         <v>5516</v>
       </c>
-      <c r="C17" s="110" t="n">
+      <c r="C17" s="107" t="n">
         <f aca="false">B17/12</f>
         <v>459.666666666667</v>
       </c>
-      <c r="D17" s="158" t="n">
+      <c r="D17" s="155" t="n">
         <f aca="false">B17/258287</f>
         <v>0.0213560883823034</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="102" t="s">
-        <v>694</v>
-      </c>
-      <c r="B18" s="110" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="110" t="n">
+      <c r="A18" s="99" t="s">
+        <v>687</v>
+      </c>
+      <c r="B18" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="107" t="n">
         <f aca="false">B18/12</f>
         <v>0</v>
       </c>
-      <c r="D18" s="158" t="n">
+      <c r="D18" s="155" t="n">
         <f aca="false">B18/258287</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="44" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="B19" s="45" t="n">
         <v>81599</v>
       </c>
-      <c r="C19" s="159" t="n">
+      <c r="C19" s="156" t="n">
         <f aca="false">B19/12</f>
         <v>6799.91666666667</v>
       </c>
-      <c r="D19" s="160" t="n">
+      <c r="D19" s="157" t="n">
         <f aca="false">B19/258287</f>
         <v>0.315923759229075</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="44" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="B20" s="45" t="n">
         <v>176688</v>
       </c>
-      <c r="C20" s="159" t="n">
+      <c r="C20" s="156" t="n">
         <f aca="false">B20/12</f>
         <v>14724</v>
       </c>
-      <c r="D20" s="160" t="n">
+      <c r="D20" s="157" t="n">
         <f aca="false">B20/258287</f>
         <v>0.684076240770925</v>
       </c>
@@ -34916,70 +34882,70 @@
       <c r="A22" s="44" t="s">
         <v>290</v>
       </c>
-      <c r="B22" s="161"/>
-      <c r="C22" s="162"/>
-      <c r="D22" s="162"/>
+      <c r="B22" s="158"/>
+      <c r="C22" s="159"/>
+      <c r="D22" s="159"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="102" t="s">
-        <v>697</v>
-      </c>
-      <c r="B23" s="110" t="n">
+      <c r="A23" s="99" t="s">
+        <v>690</v>
+      </c>
+      <c r="B23" s="107" t="n">
         <v>142124</v>
       </c>
-      <c r="C23" s="110" t="n">
+      <c r="C23" s="107" t="n">
         <f aca="false">B23/12</f>
         <v>11843.6666666667</v>
       </c>
-      <c r="D23" s="158" t="n">
+      <c r="D23" s="155" t="n">
         <f aca="false">B23/258287</f>
         <v>0.550256110450778</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="102" t="s">
-        <v>698</v>
-      </c>
-      <c r="B24" s="110" t="n">
+      <c r="A24" s="99" t="s">
+        <v>691</v>
+      </c>
+      <c r="B24" s="107" t="n">
         <v>16219</v>
       </c>
-      <c r="C24" s="110" t="n">
+      <c r="C24" s="107" t="n">
         <f aca="false">B24/12</f>
         <v>1351.58333333333</v>
       </c>
-      <c r="D24" s="158" t="n">
+      <c r="D24" s="155" t="n">
         <f aca="false">B24/258287</f>
         <v>0.0627944883017728</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="102" t="s">
-        <v>699</v>
-      </c>
-      <c r="B25" s="110" t="n">
+      <c r="A25" s="99" t="s">
+        <v>692</v>
+      </c>
+      <c r="B25" s="107" t="n">
         <v>6514</v>
       </c>
-      <c r="C25" s="110" t="n">
+      <c r="C25" s="107" t="n">
         <f aca="false">B25/12</f>
         <v>542.833333333333</v>
       </c>
-      <c r="D25" s="158" t="n">
+      <c r="D25" s="155" t="n">
         <f aca="false">B25/258287</f>
         <v>0.0252200072012916</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="44" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="B26" s="45" t="n">
         <v>164857</v>
       </c>
-      <c r="C26" s="159" t="n">
+      <c r="C26" s="156" t="n">
         <f aca="false">B26/12</f>
         <v>13738.0833333333</v>
       </c>
-      <c r="D26" s="160" t="n">
+      <c r="D26" s="157" t="n">
         <f aca="false">B26/258287</f>
         <v>0.638270605953842</v>
       </c>
@@ -34991,193 +34957,193 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="44" t="s">
-        <v>701</v>
-      </c>
-      <c r="B28" s="161"/>
-      <c r="C28" s="162"/>
-      <c r="D28" s="162"/>
+        <v>694</v>
+      </c>
+      <c r="B28" s="158"/>
+      <c r="C28" s="159"/>
+      <c r="D28" s="159"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="102" t="s">
-        <v>702</v>
-      </c>
-      <c r="B29" s="110" t="n">
+      <c r="A29" s="99" t="s">
+        <v>695</v>
+      </c>
+      <c r="B29" s="107" t="n">
         <v>44540</v>
       </c>
-      <c r="C29" s="110" t="n">
+      <c r="C29" s="107" t="n">
         <f aca="false">B29/12</f>
         <v>3711.66666666667</v>
       </c>
-      <c r="D29" s="158" t="n">
+      <c r="D29" s="155" t="n">
         <f aca="false">B29/258287</f>
         <v>0.172443831861456</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="102" t="s">
-        <v>703</v>
-      </c>
-      <c r="B30" s="110" t="n">
+      <c r="A30" s="99" t="s">
+        <v>696</v>
+      </c>
+      <c r="B30" s="107" t="n">
         <v>11918</v>
       </c>
-      <c r="C30" s="110" t="n">
+      <c r="C30" s="107" t="n">
         <f aca="false">B30/12</f>
         <v>993.166666666667</v>
       </c>
-      <c r="D30" s="158" t="n">
+      <c r="D30" s="155" t="n">
         <f aca="false">B30/258287</f>
         <v>0.0461424694235482</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="102" t="s">
-        <v>704</v>
-      </c>
-      <c r="B31" s="110" t="n">
+      <c r="A31" s="99" t="s">
+        <v>697</v>
+      </c>
+      <c r="B31" s="107" t="n">
         <v>2912</v>
       </c>
-      <c r="C31" s="110" t="n">
+      <c r="C31" s="107" t="n">
         <f aca="false">B31/12</f>
         <v>242.666666666667</v>
       </c>
-      <c r="D31" s="158" t="n">
+      <c r="D31" s="155" t="n">
         <f aca="false">B31/258287</f>
         <v>0.011274280161216</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="102" t="s">
-        <v>705</v>
-      </c>
-      <c r="B32" s="110" t="n">
+      <c r="A32" s="99" t="s">
+        <v>698</v>
+      </c>
+      <c r="B32" s="107" t="n">
         <v>30305</v>
       </c>
-      <c r="C32" s="110" t="n">
+      <c r="C32" s="107" t="n">
         <f aca="false">B32/12</f>
         <v>2525.41666666667</v>
       </c>
-      <c r="D32" s="158" t="n">
+      <c r="D32" s="155" t="n">
         <f aca="false">B32/258287</f>
         <v>0.117330721251941</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="44" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="B33" s="45" t="n">
         <v>89675</v>
       </c>
-      <c r="C33" s="159" t="n">
+      <c r="C33" s="156" t="n">
         <f aca="false">B33/12</f>
         <v>7472.91666666667</v>
       </c>
-      <c r="D33" s="160" t="n">
+      <c r="D33" s="157" t="n">
         <f aca="false">B33/258287</f>
         <v>0.347191302698161</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="163" t="s">
-        <v>707</v>
-      </c>
-      <c r="B34" s="110" t="n">
+      <c r="A34" s="160" t="s">
+        <v>700</v>
+      </c>
+      <c r="B34" s="107" t="n">
         <v>10012</v>
       </c>
-      <c r="C34" s="110" t="n">
+      <c r="C34" s="107" t="n">
         <f aca="false">B34/12</f>
         <v>834.333333333333</v>
       </c>
-      <c r="D34" s="158" t="n">
+      <c r="D34" s="155" t="n">
         <f aca="false">B34/258287</f>
         <v>0.0387630813784666</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="164" t="s">
-        <v>708</v>
-      </c>
-      <c r="B35" s="88" t="n">
+      <c r="A35" s="161" t="s">
+        <v>701</v>
+      </c>
+      <c r="B35" s="85" t="n">
         <v>5657</v>
       </c>
-      <c r="C35" s="110" t="n">
+      <c r="C35" s="107" t="n">
         <f aca="false">B35/12</f>
         <v>471.416666666667</v>
       </c>
-      <c r="D35" s="158" t="n">
+      <c r="D35" s="155" t="n">
         <f aca="false">B35/258287</f>
         <v>0.0219019927445051</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="165" t="s">
-        <v>709</v>
-      </c>
-      <c r="B37" s="112" t="n">
+      <c r="A37" s="162" t="s">
+        <v>702</v>
+      </c>
+      <c r="B37" s="109" t="n">
         <v>-93513</v>
       </c>
-      <c r="C37" s="166" t="n">
+      <c r="C37" s="163" t="n">
         <f aca="false">B37/12</f>
         <v>-7792.75</v>
       </c>
-      <c r="D37" s="160" t="n">
+      <c r="D37" s="157" t="n">
         <f aca="false">B37/258287</f>
         <v>-0.36205074200405</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="102" t="s">
-        <v>710</v>
-      </c>
-      <c r="B38" s="110" t="n">
+      <c r="A38" s="99" t="s">
+        <v>703</v>
+      </c>
+      <c r="B38" s="107" t="n">
         <v>-48000</v>
       </c>
-      <c r="C38" s="110" t="n">
+      <c r="C38" s="107" t="n">
         <f aca="false">B38/12</f>
         <v>-4000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="102" t="s">
-        <v>711</v>
-      </c>
-      <c r="B39" s="110" t="n">
+      <c r="A39" s="99" t="s">
+        <v>704</v>
+      </c>
+      <c r="B39" s="107" t="n">
         <v>-15642</v>
       </c>
-      <c r="C39" s="110" t="n">
+      <c r="C39" s="107" t="n">
         <f aca="false">B39/12</f>
         <v>-1303.5</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="165" t="s">
-        <v>712</v>
-      </c>
-      <c r="B40" s="112" t="n">
+      <c r="A40" s="162" t="s">
+        <v>705</v>
+      </c>
+      <c r="B40" s="109" t="n">
         <v>-157155</v>
       </c>
-      <c r="C40" s="166" t="n">
+      <c r="C40" s="163" t="n">
         <f aca="false">B40/12</f>
         <v>-13096.25</v>
       </c>
-      <c r="D40" s="160" t="n">
+      <c r="D40" s="157" t="n">
         <f aca="false">B40/258287</f>
         <v>-0.60845106412634</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="167" t="s">
-        <v>713</v>
-      </c>
-      <c r="B42" s="167"/>
-      <c r="C42" s="167"/>
-      <c r="D42" s="167"/>
+      <c r="A42" s="164" t="s">
+        <v>706</v>
+      </c>
+      <c r="B42" s="164"/>
+      <c r="C42" s="164"/>
+      <c r="D42" s="164"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="167"/>
-      <c r="B43" s="167"/>
-      <c r="C43" s="167"/>
-      <c r="D43" s="167"/>
+      <c r="A43" s="164"/>
+      <c r="B43" s="164"/>
+      <c r="C43" s="164"/>
+      <c r="D43" s="164"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -35208,8 +35174,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="99" t="s">
-        <v>714</v>
+      <c r="A1" s="96" t="s">
+        <v>707</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -35221,663 +35187,663 @@
       <c r="I1" s="38"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="100" t="s">
+      <c r="A2" s="97" t="s">
+        <v>708</v>
+      </c>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="122" t="s">
+        <v>709</v>
+      </c>
+      <c r="B4" s="122" t="s">
+        <v>710</v>
+      </c>
+      <c r="C4" s="123" t="s">
+        <v>711</v>
+      </c>
+      <c r="D4" s="123" t="s">
+        <v>712</v>
+      </c>
+      <c r="E4" s="123" t="s">
+        <v>713</v>
+      </c>
+      <c r="F4" s="123" t="s">
+        <v>714</v>
+      </c>
+      <c r="G4" s="123" t="s">
         <v>715</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="125" t="s">
+      <c r="H4" s="123" t="s">
         <v>716</v>
       </c>
-      <c r="B4" s="125" t="s">
+      <c r="I4" s="123" t="s">
         <v>717</v>
       </c>
-      <c r="C4" s="126" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="165" t="s">
         <v>718</v>
       </c>
-      <c r="D4" s="126" t="s">
+      <c r="B5" s="166"/>
+      <c r="C5" s="167"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="167"/>
+      <c r="F5" s="167"/>
+      <c r="G5" s="167"/>
+      <c r="H5" s="167"/>
+      <c r="I5" s="167"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="124" t="s">
         <v>719</v>
       </c>
-      <c r="E4" s="126" t="s">
+      <c r="B6" s="120" t="s">
         <v>720</v>
       </c>
-      <c r="F4" s="126" t="s">
-        <v>721</v>
-      </c>
-      <c r="G4" s="126" t="s">
-        <v>722</v>
-      </c>
-      <c r="H4" s="126" t="s">
-        <v>723</v>
-      </c>
-      <c r="I4" s="126" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="168" t="s">
-        <v>725</v>
-      </c>
-      <c r="B5" s="169"/>
-      <c r="C5" s="170"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="170"/>
-      <c r="F5" s="170"/>
-      <c r="G5" s="170"/>
-      <c r="H5" s="170"/>
-      <c r="I5" s="170"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="127" t="s">
-        <v>726</v>
-      </c>
-      <c r="B6" s="123" t="s">
-        <v>727</v>
-      </c>
-      <c r="C6" s="171" t="n">
+      <c r="C6" s="168" t="n">
         <v>5728</v>
       </c>
-      <c r="D6" s="172" t="n">
+      <c r="D6" s="169" t="n">
         <f aca="false">IF(C6=0,0,E6/C6)</f>
         <v>4.5</v>
       </c>
-      <c r="E6" s="110" t="n">
+      <c r="E6" s="107" t="n">
         <v>25776</v>
       </c>
-      <c r="F6" s="173" t="n">
+      <c r="F6" s="170" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="172" t="n">
+      <c r="G6" s="169" t="n">
         <f aca="false">D6+F6</f>
         <v>5</v>
       </c>
-      <c r="H6" s="110" t="n">
+      <c r="H6" s="107" t="n">
         <f aca="false">E6+I6</f>
         <v>28640</v>
       </c>
-      <c r="I6" s="88" t="n">
+      <c r="I6" s="85" t="n">
         <f aca="false">C6*F6</f>
         <v>2864</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="127" t="s">
-        <v>728</v>
-      </c>
-      <c r="B7" s="123" t="s">
-        <v>727</v>
-      </c>
-      <c r="C7" s="171" t="n">
+      <c r="A7" s="124" t="s">
+        <v>721</v>
+      </c>
+      <c r="B7" s="120" t="s">
+        <v>720</v>
+      </c>
+      <c r="C7" s="168" t="n">
         <v>3537</v>
       </c>
-      <c r="D7" s="172" t="n">
+      <c r="D7" s="169" t="n">
         <f aca="false">IF(C7=0,0,E7/C7)</f>
         <v>3</v>
       </c>
-      <c r="E7" s="110" t="n">
+      <c r="E7" s="107" t="n">
         <v>10611</v>
       </c>
-      <c r="F7" s="173" t="n">
+      <c r="F7" s="170" t="n">
         <v>0.5</v>
       </c>
-      <c r="G7" s="172" t="n">
+      <c r="G7" s="169" t="n">
         <f aca="false">D7+F7</f>
         <v>3.5</v>
       </c>
-      <c r="H7" s="110" t="n">
+      <c r="H7" s="107" t="n">
         <f aca="false">E7+I7</f>
         <v>12379.5</v>
       </c>
-      <c r="I7" s="88" t="n">
+      <c r="I7" s="85" t="n">
         <f aca="false">C7*F7</f>
         <v>1768.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="127" t="s">
-        <v>729</v>
-      </c>
-      <c r="B8" s="123" t="s">
-        <v>727</v>
-      </c>
-      <c r="C8" s="171" t="n">
+      <c r="A8" s="124" t="s">
+        <v>722</v>
+      </c>
+      <c r="B8" s="120" t="s">
+        <v>720</v>
+      </c>
+      <c r="C8" s="168" t="n">
         <v>1869</v>
       </c>
-      <c r="D8" s="172" t="n">
+      <c r="D8" s="169" t="n">
         <f aca="false">IF(C8=0,0,E8/C8)</f>
         <v>4.5</v>
       </c>
-      <c r="E8" s="110" t="n">
+      <c r="E8" s="107" t="n">
         <v>8410.5</v>
       </c>
-      <c r="F8" s="173" t="n">
+      <c r="F8" s="170" t="n">
         <v>0.45</v>
       </c>
-      <c r="G8" s="172" t="n">
+      <c r="G8" s="169" t="n">
         <f aca="false">D8+F8</f>
         <v>4.95</v>
       </c>
-      <c r="H8" s="110" t="n">
+      <c r="H8" s="107" t="n">
         <f aca="false">E8+I8</f>
         <v>9251.55</v>
       </c>
-      <c r="I8" s="88" t="n">
+      <c r="I8" s="85" t="n">
         <f aca="false">C8*F8</f>
         <v>841.05</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="127" t="s">
-        <v>730</v>
-      </c>
-      <c r="B9" s="123" t="s">
-        <v>727</v>
-      </c>
-      <c r="C9" s="171" t="n">
+      <c r="A9" s="124" t="s">
+        <v>723</v>
+      </c>
+      <c r="B9" s="120" t="s">
+        <v>720</v>
+      </c>
+      <c r="C9" s="168" t="n">
         <v>1305</v>
       </c>
-      <c r="D9" s="172" t="n">
+      <c r="D9" s="169" t="n">
         <f aca="false">IF(C9=0,0,E9/C9)</f>
         <v>4.75</v>
       </c>
-      <c r="E9" s="110" t="n">
+      <c r="E9" s="107" t="n">
         <v>6198.75</v>
       </c>
-      <c r="F9" s="173" t="n">
+      <c r="F9" s="170" t="n">
         <v>0.5</v>
       </c>
-      <c r="G9" s="172" t="n">
+      <c r="G9" s="169" t="n">
         <f aca="false">D9+F9</f>
         <v>5.25</v>
       </c>
-      <c r="H9" s="110" t="n">
+      <c r="H9" s="107" t="n">
         <f aca="false">E9+I9</f>
         <v>6851.25</v>
       </c>
-      <c r="I9" s="88" t="n">
+      <c r="I9" s="85" t="n">
         <f aca="false">C9*F9</f>
         <v>652.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="127" t="s">
-        <v>731</v>
-      </c>
-      <c r="B10" s="123" t="s">
-        <v>727</v>
-      </c>
-      <c r="C10" s="171" t="n">
+      <c r="A10" s="124" t="s">
+        <v>724</v>
+      </c>
+      <c r="B10" s="120" t="s">
+        <v>720</v>
+      </c>
+      <c r="C10" s="168" t="n">
         <v>1212</v>
       </c>
-      <c r="D10" s="172" t="n">
+      <c r="D10" s="169" t="n">
         <f aca="false">IF(C10=0,0,E10/C10)</f>
         <v>4</v>
       </c>
-      <c r="E10" s="110" t="n">
+      <c r="E10" s="107" t="n">
         <v>4848</v>
       </c>
-      <c r="F10" s="173" t="n">
+      <c r="F10" s="170" t="n">
         <v>0.25</v>
       </c>
-      <c r="G10" s="172" t="n">
+      <c r="G10" s="169" t="n">
         <f aca="false">D10+F10</f>
         <v>4.25</v>
       </c>
-      <c r="H10" s="110" t="n">
+      <c r="H10" s="107" t="n">
         <f aca="false">E10+I10</f>
         <v>5151</v>
       </c>
-      <c r="I10" s="88" t="n">
+      <c r="I10" s="85" t="n">
         <f aca="false">C10*F10</f>
         <v>303</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="127" t="s">
-        <v>732</v>
-      </c>
-      <c r="B11" s="123" t="s">
-        <v>727</v>
-      </c>
-      <c r="C11" s="171" t="n">
+      <c r="A11" s="124" t="s">
+        <v>725</v>
+      </c>
+      <c r="B11" s="120" t="s">
+        <v>720</v>
+      </c>
+      <c r="C11" s="168" t="n">
         <v>888</v>
       </c>
-      <c r="D11" s="172" t="n">
+      <c r="D11" s="169" t="n">
         <f aca="false">IF(C11=0,0,E11/C11)</f>
         <v>6</v>
       </c>
-      <c r="E11" s="110" t="n">
+      <c r="E11" s="107" t="n">
         <v>5328</v>
       </c>
-      <c r="F11" s="173" t="n">
+      <c r="F11" s="170" t="n">
         <v>0.5</v>
       </c>
-      <c r="G11" s="172" t="n">
+      <c r="G11" s="169" t="n">
         <f aca="false">D11+F11</f>
         <v>6.5</v>
       </c>
-      <c r="H11" s="110" t="n">
+      <c r="H11" s="107" t="n">
         <f aca="false">E11+I11</f>
         <v>5772</v>
       </c>
-      <c r="I11" s="88" t="n">
+      <c r="I11" s="85" t="n">
         <f aca="false">C11*F11</f>
         <v>444</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="127" t="s">
-        <v>733</v>
-      </c>
-      <c r="B12" s="123" t="s">
-        <v>727</v>
-      </c>
-      <c r="C12" s="171" t="n">
+      <c r="A12" s="124" t="s">
+        <v>726</v>
+      </c>
+      <c r="B12" s="120" t="s">
+        <v>720</v>
+      </c>
+      <c r="C12" s="168" t="n">
         <v>319</v>
       </c>
-      <c r="D12" s="172" t="n">
+      <c r="D12" s="169" t="n">
         <f aca="false">IF(C12=0,0,E12/C12)</f>
         <v>5.25</v>
       </c>
-      <c r="E12" s="110" t="n">
+      <c r="E12" s="107" t="n">
         <v>1674.75</v>
       </c>
-      <c r="F12" s="173" t="n">
+      <c r="F12" s="170" t="n">
         <v>0.25</v>
       </c>
-      <c r="G12" s="172" t="n">
+      <c r="G12" s="169" t="n">
         <f aca="false">D12+F12</f>
         <v>5.5</v>
       </c>
-      <c r="H12" s="110" t="n">
+      <c r="H12" s="107" t="n">
         <f aca="false">E12+I12</f>
         <v>1754.5</v>
       </c>
-      <c r="I12" s="88" t="n">
+      <c r="I12" s="85" t="n">
         <f aca="false">C12*F12</f>
         <v>79.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="127" t="s">
-        <v>734</v>
-      </c>
-      <c r="B13" s="123" t="s">
-        <v>406</v>
-      </c>
-      <c r="C13" s="171" t="n">
+      <c r="A13" s="124" t="s">
+        <v>727</v>
+      </c>
+      <c r="B13" s="120" t="s">
+        <v>399</v>
+      </c>
+      <c r="C13" s="168" t="n">
         <v>2352</v>
       </c>
-      <c r="D13" s="172" t="n">
+      <c r="D13" s="169" t="n">
         <f aca="false">IF(C13=0,0,E13/C13)</f>
         <v>10</v>
       </c>
-      <c r="E13" s="110" t="n">
+      <c r="E13" s="107" t="n">
         <v>23520</v>
       </c>
-      <c r="F13" s="173" t="n">
+      <c r="F13" s="170" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="172" t="n">
+      <c r="G13" s="169" t="n">
         <f aca="false">D13+F13</f>
         <v>11</v>
       </c>
-      <c r="H13" s="110" t="n">
+      <c r="H13" s="107" t="n">
         <f aca="false">E13+I13</f>
         <v>25872</v>
       </c>
-      <c r="I13" s="88" t="n">
+      <c r="I13" s="85" t="n">
         <f aca="false">C13*F13</f>
         <v>2352</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="127" t="s">
-        <v>735</v>
-      </c>
-      <c r="B14" s="123" t="s">
-        <v>727</v>
-      </c>
-      <c r="C14" s="171" t="n">
+      <c r="A14" s="124" t="s">
+        <v>728</v>
+      </c>
+      <c r="B14" s="120" t="s">
+        <v>720</v>
+      </c>
+      <c r="C14" s="168" t="n">
         <v>619</v>
       </c>
-      <c r="D14" s="174" t="n">
+      <c r="D14" s="171" t="n">
         <f aca="false">IF(C14=0,0,E14/C14)</f>
         <v>8</v>
       </c>
-      <c r="E14" s="110" t="n">
+      <c r="E14" s="107" t="n">
         <v>4952</v>
       </c>
-      <c r="F14" s="175" t="n">
+      <c r="F14" s="172" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="174" t="n">
+      <c r="G14" s="171" t="n">
         <f aca="false">D14+F14</f>
         <v>9</v>
       </c>
-      <c r="H14" s="110" t="n">
+      <c r="H14" s="107" t="n">
         <f aca="false">E14+I14</f>
         <v>5571</v>
       </c>
-      <c r="I14" s="88" t="n">
+      <c r="I14" s="85" t="n">
         <f aca="false">C14*F14</f>
         <v>619</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="127" t="s">
-        <v>736</v>
-      </c>
-      <c r="B15" s="123" t="s">
-        <v>406</v>
-      </c>
-      <c r="C15" s="176" t="n">
+      <c r="A15" s="124" t="s">
+        <v>729</v>
+      </c>
+      <c r="B15" s="120" t="s">
+        <v>399</v>
+      </c>
+      <c r="C15" s="173" t="n">
         <v>510</v>
       </c>
-      <c r="D15" s="174" t="n">
+      <c r="D15" s="171" t="n">
         <f aca="false">IF(C15=0,0,E15/C15)</f>
         <v>6</v>
       </c>
-      <c r="E15" s="177" t="n">
+      <c r="E15" s="174" t="n">
         <v>3060</v>
       </c>
-      <c r="F15" s="175" t="n">
+      <c r="F15" s="172" t="n">
         <v>0.5</v>
       </c>
-      <c r="G15" s="174" t="n">
+      <c r="G15" s="171" t="n">
         <f aca="false">D15+F15</f>
         <v>6.5</v>
       </c>
-      <c r="H15" s="177" t="n">
+      <c r="H15" s="174" t="n">
         <f aca="false">E15+I15</f>
         <v>3315</v>
       </c>
-      <c r="I15" s="178" t="n">
+      <c r="I15" s="175" t="n">
         <f aca="false">C15*F15</f>
         <v>255</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="168" t="s">
-        <v>737</v>
-      </c>
-      <c r="B16" s="169"/>
-      <c r="C16" s="169"/>
-      <c r="D16" s="169"/>
-      <c r="E16" s="169"/>
-      <c r="F16" s="169"/>
-      <c r="G16" s="169"/>
-      <c r="H16" s="169"/>
-      <c r="I16" s="169"/>
+      <c r="A16" s="165" t="s">
+        <v>730</v>
+      </c>
+      <c r="B16" s="166"/>
+      <c r="C16" s="166"/>
+      <c r="D16" s="166"/>
+      <c r="E16" s="166"/>
+      <c r="F16" s="166"/>
+      <c r="G16" s="166"/>
+      <c r="H16" s="166"/>
+      <c r="I16" s="166"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="127" t="s">
-        <v>738</v>
-      </c>
-      <c r="B17" s="123" t="s">
-        <v>727</v>
-      </c>
-      <c r="C17" s="171" t="n">
+      <c r="A17" s="124" t="s">
+        <v>731</v>
+      </c>
+      <c r="B17" s="120" t="s">
+        <v>720</v>
+      </c>
+      <c r="C17" s="168" t="n">
         <v>5211</v>
       </c>
-      <c r="D17" s="174" t="n">
+      <c r="D17" s="171" t="n">
         <f aca="false">IF(C17=0,0,E17/C17)</f>
         <v>5</v>
       </c>
-      <c r="E17" s="177" t="n">
+      <c r="E17" s="174" t="n">
         <v>26055</v>
       </c>
-      <c r="F17" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="174" t="n">
+      <c r="F17" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="171" t="n">
         <f aca="false">D17+F17</f>
         <v>5</v>
       </c>
-      <c r="H17" s="177" t="n">
+      <c r="H17" s="174" t="n">
         <f aca="false">E17+I17</f>
         <v>26055</v>
       </c>
-      <c r="I17" s="178" t="n">
+      <c r="I17" s="175" t="n">
         <f aca="false">C17*F17</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="127" t="s">
-        <v>739</v>
-      </c>
-      <c r="B18" s="123" t="s">
-        <v>406</v>
-      </c>
-      <c r="C18" s="171" t="n">
+      <c r="A18" s="124" t="s">
+        <v>732</v>
+      </c>
+      <c r="B18" s="120" t="s">
+        <v>399</v>
+      </c>
+      <c r="C18" s="168" t="n">
         <v>1198</v>
       </c>
-      <c r="D18" s="174" t="n">
+      <c r="D18" s="171" t="n">
         <f aca="false">IF(C18=0,0,E18/C18)</f>
         <v>11.5</v>
       </c>
-      <c r="E18" s="177" t="n">
+      <c r="E18" s="174" t="n">
         <v>13777</v>
       </c>
-      <c r="F18" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="174" t="n">
+      <c r="F18" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="171" t="n">
         <f aca="false">D18+F18</f>
         <v>11.5</v>
       </c>
-      <c r="H18" s="177" t="n">
+      <c r="H18" s="174" t="n">
         <f aca="false">E18+I18</f>
         <v>13777</v>
       </c>
-      <c r="I18" s="178" t="n">
+      <c r="I18" s="175" t="n">
         <f aca="false">C18*F18</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="127" t="s">
-        <v>740</v>
-      </c>
-      <c r="B19" s="123" t="s">
-        <v>406</v>
-      </c>
-      <c r="C19" s="171" t="n">
+      <c r="A19" s="124" t="s">
+        <v>733</v>
+      </c>
+      <c r="B19" s="120" t="s">
+        <v>399</v>
+      </c>
+      <c r="C19" s="168" t="n">
         <v>4396</v>
       </c>
-      <c r="D19" s="174" t="n">
+      <c r="D19" s="171" t="n">
         <f aca="false">IF(C19=0,0,E19/C19)</f>
         <v>4.31</v>
       </c>
-      <c r="E19" s="177" t="n">
+      <c r="E19" s="174" t="n">
         <v>18946.76</v>
       </c>
-      <c r="F19" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="174" t="n">
+      <c r="F19" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="171" t="n">
         <f aca="false">D19+F19</f>
         <v>4.31</v>
       </c>
-      <c r="H19" s="177" t="n">
+      <c r="H19" s="174" t="n">
         <f aca="false">E19+I19</f>
         <v>18946.76</v>
       </c>
-      <c r="I19" s="178" t="n">
+      <c r="I19" s="175" t="n">
         <f aca="false">C19*F19</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="127" t="s">
-        <v>579</v>
-      </c>
-      <c r="B20" s="123" t="s">
-        <v>406</v>
-      </c>
-      <c r="C20" s="171" t="n">
+      <c r="A20" s="124" t="s">
+        <v>572</v>
+      </c>
+      <c r="B20" s="120" t="s">
+        <v>399</v>
+      </c>
+      <c r="C20" s="168" t="n">
         <v>1757</v>
       </c>
-      <c r="D20" s="174" t="n">
+      <c r="D20" s="171" t="n">
         <f aca="false">IF(C20=0,0,E20/C20)</f>
         <v>5.96</v>
       </c>
-      <c r="E20" s="177" t="n">
+      <c r="E20" s="174" t="n">
         <v>10471.72</v>
       </c>
-      <c r="F20" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="174" t="n">
+      <c r="F20" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="171" t="n">
         <f aca="false">D20+F20</f>
         <v>5.96</v>
       </c>
-      <c r="H20" s="177" t="n">
+      <c r="H20" s="174" t="n">
         <f aca="false">E20+I20</f>
         <v>10471.72</v>
       </c>
-      <c r="I20" s="178" t="n">
+      <c r="I20" s="175" t="n">
         <f aca="false">C20*F20</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="127" t="s">
-        <v>575</v>
-      </c>
-      <c r="B21" s="123" t="s">
-        <v>406</v>
-      </c>
-      <c r="C21" s="176" t="n">
+      <c r="A21" s="124" t="s">
+        <v>568</v>
+      </c>
+      <c r="B21" s="120" t="s">
+        <v>399</v>
+      </c>
+      <c r="C21" s="173" t="n">
         <v>2519</v>
       </c>
-      <c r="D21" s="174" t="n">
+      <c r="D21" s="171" t="n">
         <f aca="false">IF(C21=0,0,E21/C21)</f>
         <v>4.43</v>
       </c>
-      <c r="E21" s="177" t="n">
+      <c r="E21" s="174" t="n">
         <v>11159.17</v>
       </c>
-      <c r="F21" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="174" t="n">
+      <c r="F21" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="171" t="n">
         <f aca="false">D21+F21</f>
         <v>4.43</v>
       </c>
-      <c r="H21" s="177" t="n">
+      <c r="H21" s="174" t="n">
         <f aca="false">E21+I21</f>
         <v>11159.17</v>
       </c>
-      <c r="I21" s="178" t="n">
+      <c r="I21" s="175" t="n">
         <f aca="false">C21*F21</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="127" t="s">
-        <v>741</v>
-      </c>
-      <c r="B22" s="123" t="s">
-        <v>727</v>
-      </c>
-      <c r="C22" s="176" t="n">
+      <c r="A22" s="124" t="s">
+        <v>734</v>
+      </c>
+      <c r="B22" s="120" t="s">
+        <v>720</v>
+      </c>
+      <c r="C22" s="173" t="n">
         <v>4935</v>
       </c>
-      <c r="D22" s="174" t="n">
+      <c r="D22" s="171" t="n">
         <f aca="false">IF(C22=0,0,E22/C22)</f>
         <v>4.69</v>
       </c>
-      <c r="E22" s="177" t="n">
+      <c r="E22" s="174" t="n">
         <v>23145.15</v>
       </c>
-      <c r="F22" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="174" t="n">
+      <c r="F22" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="171" t="n">
         <f aca="false">D22+F22</f>
         <v>4.69</v>
       </c>
-      <c r="H22" s="177" t="n">
+      <c r="H22" s="174" t="n">
         <f aca="false">E22+I22</f>
         <v>23145.15</v>
       </c>
-      <c r="I22" s="178" t="n">
+      <c r="I22" s="175" t="n">
         <f aca="false">C22*F22</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="127" t="s">
-        <v>742</v>
-      </c>
-      <c r="B23" s="123" t="s">
-        <v>743</v>
-      </c>
-      <c r="C23" s="171" t="n">
+      <c r="A23" s="124" t="s">
+        <v>735</v>
+      </c>
+      <c r="B23" s="120" t="s">
+        <v>736</v>
+      </c>
+      <c r="C23" s="168" t="n">
         <v>1309</v>
       </c>
-      <c r="D23" s="174" t="n">
+      <c r="D23" s="171" t="n">
         <f aca="false">IF(C23=0,0,E23/C23)</f>
         <v>13.1</v>
       </c>
-      <c r="E23" s="177" t="n">
+      <c r="E23" s="174" t="n">
         <v>17147.9</v>
       </c>
-      <c r="F23" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="174" t="n">
+      <c r="F23" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="171" t="n">
         <f aca="false">D23+F23</f>
         <v>13.1</v>
       </c>
-      <c r="H23" s="177" t="n">
+      <c r="H23" s="174" t="n">
         <f aca="false">E23+I23</f>
         <v>17147.9</v>
       </c>
-      <c r="I23" s="178" t="n">
+      <c r="I23" s="175" t="n">
         <f aca="false">C23*F23</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="127" t="s">
-        <v>744</v>
-      </c>
-      <c r="B24" s="123" t="s">
-        <v>406</v>
-      </c>
-      <c r="C24" s="171" t="n">
+      <c r="A24" s="124" t="s">
+        <v>737</v>
+      </c>
+      <c r="B24" s="120" t="s">
+        <v>399</v>
+      </c>
+      <c r="C24" s="168" t="n">
         <v>845</v>
       </c>
-      <c r="D24" s="174" t="n">
+      <c r="D24" s="171" t="n">
         <f aca="false">IF(C24=0,0,E24/C24)</f>
         <v>6.05</v>
       </c>
-      <c r="E24" s="177" t="n">
+      <c r="E24" s="174" t="n">
         <v>5112.25</v>
       </c>
-      <c r="F24" s="175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="174" t="n">
+      <c r="F24" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="171" t="n">
         <f aca="false">D24+F24</f>
         <v>6.05</v>
       </c>
-      <c r="H24" s="177" t="n">
+      <c r="H24" s="174" t="n">
         <f aca="false">E24+I24</f>
         <v>5112.25</v>
       </c>
-      <c r="I24" s="178" t="n">
+      <c r="I24" s="175" t="n">
         <f aca="false">C24*F24</f>
         <v>0</v>
       </c>
@@ -35916,7 +35882,7 @@
       <c r="I27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="179"/>
+      <c r="A28" s="176"/>
       <c r="B28" s="19"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
@@ -35927,33 +35893,33 @@
       <c r="I28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="95" t="s">
-        <v>745</v>
-      </c>
-      <c r="B29" s="169"/>
-      <c r="C29" s="180" t="n">
+      <c r="A29" s="92" t="s">
+        <v>738</v>
+      </c>
+      <c r="B29" s="166"/>
+      <c r="C29" s="177" t="n">
         <f aca="false">SUM(C6:C28)</f>
         <v>40509</v>
       </c>
-      <c r="D29" s="170"/>
+      <c r="D29" s="167"/>
       <c r="E29" s="45" t="n">
         <f aca="false">SUM(E6:E28)</f>
         <v>220193.95</v>
       </c>
-      <c r="F29" s="169"/>
-      <c r="G29" s="169"/>
-      <c r="H29" s="181" t="n">
+      <c r="F29" s="166"/>
+      <c r="G29" s="166"/>
+      <c r="H29" s="178" t="n">
         <f aca="false">SUM(H6:H28)</f>
         <v>230372.75</v>
       </c>
-      <c r="I29" s="181" t="n">
+      <c r="I29" s="178" t="n">
         <f aca="false">SUM(I6:I28)</f>
         <v>10178.8</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="123" t="s">
-        <v>746</v>
+      <c r="A30" s="120" t="s">
+        <v>739</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="23"/>
@@ -35976,24 +35942,24 @@
       <c r="I31" s="19"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="137" t="s">
-        <v>747</v>
-      </c>
-      <c r="B32" s="137"/>
-      <c r="C32" s="137"/>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="137"/>
-      <c r="G32" s="137"/>
-      <c r="H32" s="137"/>
-      <c r="I32" s="137"/>
+      <c r="A32" s="134" t="s">
+        <v>740</v>
+      </c>
+      <c r="B32" s="134"/>
+      <c r="C32" s="134"/>
+      <c r="D32" s="134"/>
+      <c r="E32" s="134"/>
+      <c r="F32" s="134"/>
+      <c r="G32" s="134"/>
+      <c r="H32" s="134"/>
+      <c r="I32" s="134"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="67" t="s">
-        <v>748</v>
+      <c r="A33" s="66" t="s">
+        <v>741</v>
       </c>
       <c r="B33" s="19"/>
-      <c r="C33" s="88" t="n">
+      <c r="C33" s="85" t="n">
         <f aca="false">SUMIF($B$6:$B$28,"NA",$I$6:$I$28)</f>
         <v>7571.8</v>
       </c>
@@ -36005,11 +35971,11 @@
       <c r="I33" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="67" t="s">
-        <v>749</v>
+      <c r="A34" s="66" t="s">
+        <v>742</v>
       </c>
       <c r="B34" s="19"/>
-      <c r="C34" s="88" t="n">
+      <c r="C34" s="85" t="n">
         <f aca="false">SUMIF($B$6:$B$28,"Food",$I$6:$I$28)</f>
         <v>2607</v>
       </c>
@@ -36021,11 +35987,11 @@
       <c r="I34" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="67" t="s">
-        <v>750</v>
+      <c r="A35" s="66" t="s">
+        <v>743</v>
       </c>
       <c r="B35" s="19"/>
-      <c r="C35" s="88" t="n">
+      <c r="C35" s="85" t="n">
         <f aca="false">I29</f>
         <v>10178.8</v>
       </c>
@@ -36037,11 +36003,11 @@
       <c r="I35" s="19"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="123" t="s">
-        <v>751</v>
+      <c r="A36" s="120" t="s">
+        <v>744</v>
       </c>
       <c r="B36" s="19"/>
-      <c r="C36" s="182" t="n">
+      <c r="C36" s="179" t="n">
         <f aca="false">I29/258287</f>
         <v>0.0394088746239648</v>
       </c>
@@ -36064,8 +36030,8 @@
       <c r="I37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="67" t="s">
-        <v>752</v>
+      <c r="A38" s="66" t="s">
+        <v>745</v>
       </c>
       <c r="B38" s="19"/>
       <c r="C38" s="23"/>
@@ -36077,11 +36043,11 @@
       <c r="I38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="127" t="s">
-        <v>753</v>
+      <c r="A39" s="124" t="s">
+        <v>746</v>
       </c>
       <c r="B39" s="19"/>
-      <c r="C39" s="177" t="n">
+      <c r="C39" s="174" t="n">
         <f aca="false">I29*1</f>
         <v>10178.8</v>
       </c>
@@ -36093,11 +36059,11 @@
       <c r="I39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="127" t="s">
-        <v>754</v>
+      <c r="A40" s="124" t="s">
+        <v>747</v>
       </c>
       <c r="B40" s="19"/>
-      <c r="C40" s="177" t="n">
+      <c r="C40" s="174" t="n">
         <f aca="false">I29*0.9</f>
         <v>9160.92</v>
       </c>
@@ -36109,11 +36075,11 @@
       <c r="I40" s="19"/>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="183" t="s">
-        <v>755</v>
+      <c r="A41" s="180" t="s">
+        <v>748</v>
       </c>
       <c r="B41" s="19"/>
-      <c r="C41" s="177" t="n">
+      <c r="C41" s="174" t="n">
         <f aca="false">I29*0.8</f>
         <v>8143.04</v>
       </c>
@@ -36125,7 +36091,7 @@
       <c r="I41" s="19"/>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="184"/>
+      <c r="A42" s="181"/>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
       <c r="D42" s="19"/>
@@ -36136,82 +36102,82 @@
       <c r="I42" s="19"/>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="185" t="s">
-        <v>756</v>
-      </c>
-      <c r="B43" s="185"/>
-      <c r="C43" s="185"/>
-      <c r="D43" s="185"/>
-      <c r="E43" s="185"/>
-      <c r="F43" s="185"/>
-      <c r="G43" s="185"/>
-      <c r="H43" s="185"/>
-      <c r="I43" s="185"/>
+      <c r="A43" s="182" t="s">
+        <v>749</v>
+      </c>
+      <c r="B43" s="182"/>
+      <c r="C43" s="182"/>
+      <c r="D43" s="182"/>
+      <c r="E43" s="182"/>
+      <c r="F43" s="182"/>
+      <c r="G43" s="182"/>
+      <c r="H43" s="182"/>
+      <c r="I43" s="182"/>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="186" t="s">
-        <v>757</v>
-      </c>
-      <c r="B44" s="186"/>
-      <c r="C44" s="186"/>
-      <c r="D44" s="186"/>
-      <c r="E44" s="186"/>
-      <c r="F44" s="186"/>
-      <c r="G44" s="186"/>
-      <c r="H44" s="186"/>
-      <c r="I44" s="186"/>
+      <c r="A44" s="183" t="s">
+        <v>750</v>
+      </c>
+      <c r="B44" s="183"/>
+      <c r="C44" s="183"/>
+      <c r="D44" s="183"/>
+      <c r="E44" s="183"/>
+      <c r="F44" s="183"/>
+      <c r="G44" s="183"/>
+      <c r="H44" s="183"/>
+      <c r="I44" s="183"/>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="186" t="s">
-        <v>758</v>
-      </c>
-      <c r="B45" s="186"/>
-      <c r="C45" s="186"/>
-      <c r="D45" s="186"/>
-      <c r="E45" s="186"/>
-      <c r="F45" s="186"/>
-      <c r="G45" s="186"/>
-      <c r="H45" s="186"/>
-      <c r="I45" s="186"/>
+      <c r="A45" s="183" t="s">
+        <v>751</v>
+      </c>
+      <c r="B45" s="183"/>
+      <c r="C45" s="183"/>
+      <c r="D45" s="183"/>
+      <c r="E45" s="183"/>
+      <c r="F45" s="183"/>
+      <c r="G45" s="183"/>
+      <c r="H45" s="183"/>
+      <c r="I45" s="183"/>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="186" t="s">
-        <v>759</v>
-      </c>
-      <c r="B46" s="186"/>
-      <c r="C46" s="186"/>
-      <c r="D46" s="186"/>
-      <c r="E46" s="186"/>
-      <c r="F46" s="186"/>
-      <c r="G46" s="186"/>
-      <c r="H46" s="186"/>
-      <c r="I46" s="186"/>
+      <c r="A46" s="183" t="s">
+        <v>752</v>
+      </c>
+      <c r="B46" s="183"/>
+      <c r="C46" s="183"/>
+      <c r="D46" s="183"/>
+      <c r="E46" s="183"/>
+      <c r="F46" s="183"/>
+      <c r="G46" s="183"/>
+      <c r="H46" s="183"/>
+      <c r="I46" s="183"/>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="186" t="s">
-        <v>760</v>
-      </c>
-      <c r="B47" s="186"/>
-      <c r="C47" s="186"/>
-      <c r="D47" s="186"/>
-      <c r="E47" s="186"/>
-      <c r="F47" s="186"/>
-      <c r="G47" s="186"/>
-      <c r="H47" s="186"/>
-      <c r="I47" s="186"/>
+      <c r="A47" s="183" t="s">
+        <v>753</v>
+      </c>
+      <c r="B47" s="183"/>
+      <c r="C47" s="183"/>
+      <c r="D47" s="183"/>
+      <c r="E47" s="183"/>
+      <c r="F47" s="183"/>
+      <c r="G47" s="183"/>
+      <c r="H47" s="183"/>
+      <c r="I47" s="183"/>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="186" t="s">
-        <v>761</v>
-      </c>
-      <c r="B48" s="186"/>
-      <c r="C48" s="186"/>
-      <c r="D48" s="186"/>
-      <c r="E48" s="186"/>
-      <c r="F48" s="186"/>
-      <c r="G48" s="186"/>
-      <c r="H48" s="186"/>
-      <c r="I48" s="186"/>
+      <c r="A48" s="183" t="s">
+        <v>754</v>
+      </c>
+      <c r="B48" s="183"/>
+      <c r="C48" s="183"/>
+      <c r="D48" s="183"/>
+      <c r="E48" s="183"/>
+      <c r="F48" s="183"/>
+      <c r="G48" s="183"/>
+      <c r="H48" s="183"/>
+      <c r="I48" s="183"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="19"/>
@@ -36225,8 +36191,8 @@
       <c r="I49" s="19"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="67" t="s">
-        <v>762</v>
+      <c r="A50" s="66" t="s">
+        <v>755</v>
       </c>
       <c r="B50" s="19"/>
       <c r="C50" s="19"/>
@@ -36238,11 +36204,11 @@
       <c r="I50" s="19"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="127" t="s">
-        <v>763</v>
+      <c r="A51" s="124" t="s">
+        <v>756</v>
       </c>
       <c r="B51" s="19"/>
-      <c r="C51" s="177" t="n">
+      <c r="C51" s="174" t="n">
         <f aca="false">I29</f>
         <v>10178.8</v>
       </c>
@@ -36254,11 +36220,11 @@
       <c r="I51" s="19"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="127" t="s">
-        <v>764</v>
+      <c r="A52" s="124" t="s">
+        <v>757</v>
       </c>
       <c r="B52" s="19"/>
-      <c r="C52" s="94" t="n">
+      <c r="C52" s="91" t="n">
         <v>0.9</v>
       </c>
       <c r="D52" s="19"/>
@@ -36269,11 +36235,11 @@
       <c r="I52" s="19"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="67" t="s">
-        <v>765</v>
+      <c r="A53" s="66" t="s">
+        <v>758</v>
       </c>
       <c r="B53" s="19"/>
-      <c r="C53" s="178" t="n">
+      <c r="C53" s="175" t="n">
         <f aca="false">C51*C52</f>
         <v>9160.92</v>
       </c>
@@ -36342,45 +36308,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="B5" s="24" t="n">
         <v>35102</v>
       </c>
-      <c r="C5" s="187" t="n">
+      <c r="C5" s="184" t="n">
         <v>4000</v>
       </c>
-      <c r="D5" s="120" t="n">
+      <c r="D5" s="117" t="n">
         <v>0.42</v>
       </c>
       <c r="E5" s="24" t="n">
@@ -36394,15 +36360,15 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="B6" s="24" t="n">
         <v>18308</v>
       </c>
-      <c r="C6" s="187" t="n">
+      <c r="C6" s="184" t="n">
         <v>12000</v>
       </c>
-      <c r="D6" s="120" t="n">
+      <c r="D6" s="117" t="n">
         <v>0.42</v>
       </c>
       <c r="E6" s="24" t="n">
@@ -36416,15 +36382,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="B7" s="24" t="n">
         <v>13158</v>
       </c>
-      <c r="C7" s="187" t="n">
+      <c r="C7" s="184" t="n">
         <v>8000</v>
       </c>
-      <c r="D7" s="120" t="n">
+      <c r="D7" s="117" t="n">
         <v>0.42</v>
       </c>
       <c r="E7" s="24" t="n">
@@ -36438,15 +36404,15 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="B8" s="24" t="n">
         <v>1416</v>
       </c>
-      <c r="C8" s="187" t="n">
+      <c r="C8" s="184" t="n">
         <v>4000</v>
       </c>
-      <c r="D8" s="120" t="n">
+      <c r="D8" s="117" t="n">
         <v>0.42</v>
       </c>
       <c r="E8" s="24" t="n">
@@ -36460,15 +36426,15 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="B9" s="24" t="n">
         <v>857</v>
       </c>
-      <c r="C9" s="187" t="n">
+      <c r="C9" s="184" t="n">
         <v>4000</v>
       </c>
-      <c r="D9" s="120" t="n">
+      <c r="D9" s="117" t="n">
         <v>0.42</v>
       </c>
       <c r="E9" s="24" t="n">
@@ -36482,15 +36448,15 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="B10" s="24" t="n">
         <v>570</v>
       </c>
-      <c r="C10" s="187" t="n">
+      <c r="C10" s="184" t="n">
         <v>3000</v>
       </c>
-      <c r="D10" s="120" t="n">
+      <c r="D10" s="117" t="n">
         <v>0.42</v>
       </c>
       <c r="E10" s="24" t="n">
@@ -36504,15 +36470,15 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="B11" s="24" t="n">
         <v>387</v>
       </c>
-      <c r="C11" s="187" t="n">
+      <c r="C11" s="184" t="n">
         <v>6000</v>
       </c>
-      <c r="D11" s="120" t="n">
+      <c r="D11" s="117" t="n">
         <v>0.42</v>
       </c>
       <c r="E11" s="24" t="n">
@@ -36526,15 +36492,15 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="B12" s="24" t="n">
         <v>198</v>
       </c>
-      <c r="C12" s="187" t="n">
+      <c r="C12" s="184" t="n">
         <v>1500</v>
       </c>
-      <c r="D12" s="120" t="n">
+      <c r="D12" s="117" t="n">
         <v>0.42</v>
       </c>
       <c r="E12" s="24" t="n">
@@ -36548,15 +36514,15 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="B13" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="187" t="n">
+      <c r="C13" s="184" t="n">
         <v>1500</v>
       </c>
-      <c r="D13" s="120" t="n">
+      <c r="D13" s="117" t="n">
         <v>0.42</v>
       </c>
       <c r="E13" s="24" t="n">
@@ -36570,15 +36536,15 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="B14" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="187" t="n">
+      <c r="C14" s="184" t="n">
         <v>924</v>
       </c>
-      <c r="D14" s="120" t="n">
+      <c r="D14" s="117" t="n">
         <v>0.42</v>
       </c>
       <c r="E14" s="24" t="n">
@@ -36592,7 +36558,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="B15" s="27" t="n">
         <f aca="false">SUM(B5:B14)</f>
@@ -36602,7 +36568,7 @@
         <f aca="false">SUM(C5:C14)</f>
         <v>44924</v>
       </c>
-      <c r="D15" s="188" t="n">
+      <c r="D15" s="185" t="n">
         <f aca="false">SUMPRODUCT(C5:C14,D5:D14)/C15</f>
         <v>0.42</v>
       </c>
@@ -36617,17 +36583,17 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="C18" s="24" t="n">
         <f aca="false">'LW Assumptions'!C47</f>
@@ -36636,7 +36602,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="C19" s="7" t="n">
         <f aca="false">C15-C18</f>
@@ -36645,16 +36611,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>787</v>
-      </c>
-      <c r="C20" s="189" t="n">
+        <v>780</v>
+      </c>
+      <c r="C20" s="186" t="n">
         <f aca="false">D15</f>
         <v>0.42</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
     </row>
   </sheetData>
@@ -44509,27 +44475,27 @@
       <c r="D2" s="40"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="61" t="s">
         <v>277</v>
       </c>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="C6" s="63" t="n">
+      <c r="C6" s="62" t="n">
         <v>3720</v>
       </c>
-      <c r="D6" s="64" t="s">
+      <c r="D6" s="63" t="s">
         <v>279</v>
       </c>
     </row>
@@ -44537,10 +44503,10 @@
       <c r="B7" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="C7" s="65" t="n">
+      <c r="C7" s="64" t="n">
         <v>0.713</v>
       </c>
-      <c r="D7" s="64" t="s">
+      <c r="D7" s="63" t="s">
         <v>281</v>
       </c>
     </row>
@@ -44548,11 +44514,11 @@
       <c r="B8" s="47" t="s">
         <v>282</v>
       </c>
-      <c r="C8" s="65" t="n">
+      <c r="C8" s="64" t="n">
         <f aca="false">2880/3720</f>
         <v>0.774193548387097</v>
       </c>
-      <c r="D8" s="64" t="s">
+      <c r="D8" s="63" t="s">
         <v>283</v>
       </c>
     </row>
@@ -44560,29 +44526,29 @@
       <c r="B9" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C9" s="65" t="n">
+      <c r="C9" s="64" t="n">
         <v>0.2</v>
       </c>
-      <c r="D9" s="64" t="s">
+      <c r="D9" s="63" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="62" t="s">
+      <c r="B11" s="61" t="s">
         <v>286</v>
       </c>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="47" t="s">
         <v>287</v>
       </c>
-      <c r="C12" s="65" t="n">
+      <c r="C12" s="64" t="n">
         <f aca="false">1600/2880</f>
         <v>0.555555555555556</v>
       </c>
-      <c r="D12" s="64" t="s">
+      <c r="D12" s="63" t="s">
         <v>288</v>
       </c>
     </row>
@@ -44590,26 +44556,26 @@
       <c r="B13" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="C13" s="65" t="n">
+      <c r="C13" s="64" t="n">
         <v>0.25</v>
       </c>
-      <c r="D13" s="64" t="str">
+      <c r="D13" s="63" t="str">
         <f aca="false">TEXT(1-$C$13,"0%")&amp;" margin"</f>
         <v>75% margin</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="62" t="s">
+      <c r="B15" s="61" t="s">
         <v>290</v>
       </c>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="47" t="s">
         <v>291</v>
       </c>
-      <c r="C16" s="66" t="n">
+      <c r="C16" s="65" t="n">
         <v>1</v>
       </c>
     </row>
@@ -44617,7 +44583,7 @@
       <c r="B17" s="47" t="s">
         <v>292</v>
       </c>
-      <c r="C17" s="66" t="n">
+      <c r="C17" s="65" t="n">
         <v>2</v>
       </c>
     </row>
@@ -44625,7 +44591,7 @@
       <c r="B18" s="47" t="s">
         <v>293</v>
       </c>
-      <c r="C18" s="63" t="n">
+      <c r="C18" s="62" t="n">
         <v>35</v>
       </c>
     </row>
@@ -44633,15 +44599,15 @@
       <c r="B19" s="47" t="s">
         <v>294</v>
       </c>
-      <c r="C19" s="66" t="n">
+      <c r="C19" s="65" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="66" t="s">
         <v>295</v>
       </c>
-      <c r="C20" s="68" t="n">
+      <c r="C20" s="67" t="n">
         <f aca="false">(C16+C17)*C18*C19</f>
         <v>525</v>
       </c>
@@ -44650,11 +44616,11 @@
       <c r="B21" s="47" t="s">
         <v>296</v>
       </c>
-      <c r="C21" s="68" t="n">
+      <c r="C21" s="67" t="n">
         <f aca="false">'Vessel GL Basis'!D8</f>
         <v>1435.83333333333</v>
       </c>
-      <c r="D21" s="64" t="s">
+      <c r="D21" s="63" t="s">
         <v>297</v>
       </c>
     </row>
@@ -44662,30 +44628,30 @@
       <c r="B22" s="47" t="s">
         <v>298</v>
       </c>
-      <c r="C22" s="65" t="n">
+      <c r="C22" s="64" t="n">
         <f aca="false">114/692</f>
         <v>0.164739884393064</v>
       </c>
-      <c r="D22" s="64" t="s">
+      <c r="D22" s="63" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="62" t="s">
+      <c r="B24" s="61" t="s">
         <v>300</v>
       </c>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="47" t="s">
         <v>301</v>
       </c>
-      <c r="C25" s="68" t="n">
+      <c r="C25" s="67" t="n">
         <f aca="false">'Vessel GL Basis'!D18</f>
         <v>6718.66666666667</v>
       </c>
-      <c r="D25" s="64" t="s">
+      <c r="D25" s="63" t="s">
         <v>297</v>
       </c>
     </row>
@@ -44693,11 +44659,11 @@
       <c r="B26" s="47" t="s">
         <v>302</v>
       </c>
-      <c r="C26" s="68" t="n">
+      <c r="C26" s="67" t="n">
         <f aca="false">'Vessel GL Basis'!D24</f>
         <v>1045.41666666667</v>
       </c>
-      <c r="D26" s="64" t="s">
+      <c r="D26" s="63" t="s">
         <v>297</v>
       </c>
     </row>
@@ -44705,36 +44671,36 @@
       <c r="B27" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="C27" s="65" t="n">
+      <c r="C27" s="64" t="n">
         <v>0.025</v>
       </c>
-      <c r="D27" s="64" t="s">
+      <c r="D27" s="63" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="62" t="s">
+      <c r="B29" s="61" t="s">
         <v>305</v>
       </c>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="C30" s="69" t="n">
+      <c r="C30" s="68" t="n">
         <v>0.04</v>
       </c>
-      <c r="D30" s="64" t="s">
+      <c r="D30" s="63" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="67" t="s">
+      <c r="B31" s="66" t="s">
         <v>308</v>
       </c>
-      <c r="C31" s="70" t="n">
+      <c r="C31" s="69" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -44745,7 +44711,7 @@
       <c r="B32" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C32" s="71" t="n">
+      <c r="C32" s="70" t="n">
         <v>0.05</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -44756,10 +44722,10 @@
       <c r="B34" s="47" t="s">
         <v>312</v>
       </c>
-      <c r="C34" s="69" t="n">
+      <c r="C34" s="68" t="n">
         <v>0.03</v>
       </c>
-      <c r="D34" s="64" t="s">
+      <c r="D34" s="63" t="s">
         <v>313</v>
       </c>
     </row>
@@ -44767,10 +44733,10 @@
       <c r="B35" s="47" t="s">
         <v>314</v>
       </c>
-      <c r="C35" s="69" t="n">
+      <c r="C35" s="68" t="n">
         <v>0.04</v>
       </c>
-      <c r="D35" s="64" t="s">
+      <c r="D35" s="63" t="s">
         <v>315</v>
       </c>
     </row>
@@ -44778,10 +44744,10 @@
       <c r="B36" s="47" t="s">
         <v>316</v>
       </c>
-      <c r="C36" s="72" t="n">
+      <c r="C36" s="71" t="n">
         <v>55</v>
       </c>
-      <c r="D36" s="64" t="s">
+      <c r="D36" s="63" t="s">
         <v>317</v>
       </c>
     </row>
@@ -44789,10 +44755,10 @@
       <c r="B37" s="47" t="s">
         <v>318</v>
       </c>
-      <c r="C37" s="72" t="n">
+      <c r="C37" s="71" t="n">
         <v>112</v>
       </c>
-      <c r="D37" s="64" t="s">
+      <c r="D37" s="63" t="s">
         <v>317</v>
       </c>
     </row>
@@ -44800,11 +44766,11 @@
       <c r="B38" s="47" t="s">
         <v>319</v>
       </c>
-      <c r="C38" s="73" t="n">
+      <c r="C38" s="72" t="n">
         <f aca="false">575/4650</f>
         <v>0.123655913978495</v>
       </c>
-      <c r="D38" s="64" t="s">
+      <c r="D38" s="63" t="s">
         <v>320</v>
       </c>
     </row>
@@ -44812,11 +44778,11 @@
       <c r="B39" s="47" t="s">
         <v>321</v>
       </c>
-      <c r="C39" s="73" t="n">
+      <c r="C39" s="72" t="n">
         <f aca="false">116/4650</f>
         <v>0.0249462365591398</v>
       </c>
-      <c r="D39" s="64" t="s">
+      <c r="D39" s="63" t="s">
         <v>322</v>
       </c>
     </row>
@@ -45087,46 +45053,46 @@
       <c r="A8" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="C8" s="74" t="n">
+      <c r="C8" s="73" t="n">
         <v>13</v>
       </c>
-      <c r="E8" s="74" t="n">
+      <c r="E8" s="73" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="74" t="n">
+      <c r="G8" s="73" t="n">
         <v>13</v>
       </c>
-      <c r="I8" s="74" t="n">
+      <c r="I8" s="73" t="n">
         <v>4</v>
       </c>
-      <c r="K8" s="74" t="n">
+      <c r="K8" s="73" t="n">
         <v>10</v>
       </c>
-      <c r="M8" s="75" t="n">
+      <c r="M8" s="74" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
-      <c r="O8" s="75" t="n">
+      <c r="O8" s="74" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
-      <c r="Q8" s="75" t="n">
+      <c r="Q8" s="74" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
-      <c r="S8" s="75" t="n">
+      <c r="S8" s="74" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
-      <c r="U8" s="75" t="n">
+      <c r="U8" s="74" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
-      <c r="W8" s="75" t="n">
+      <c r="W8" s="74" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
-      <c r="Y8" s="75" t="n">
+      <c r="Y8" s="74" t="n">
         <f aca="false">AVERAGE($C$8,$E$8,$G$8,$I$8,$K$8)</f>
         <v>8.8</v>
       </c>
@@ -45139,55 +45105,55 @@
       <c r="A9" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="C9" s="75" t="n">
+      <c r="C9" s="74" t="n">
         <f aca="false">C8*'Vessel Assumptions'!$C$7</f>
         <v>9.269</v>
       </c>
-      <c r="E9" s="75" t="n">
+      <c r="E9" s="74" t="n">
         <f aca="false">E8*'Vessel Assumptions'!$C$7</f>
         <v>2.852</v>
       </c>
-      <c r="G9" s="75" t="n">
+      <c r="G9" s="74" t="n">
         <f aca="false">G8*'Vessel Assumptions'!$C$7</f>
         <v>9.269</v>
       </c>
-      <c r="I9" s="75" t="n">
+      <c r="I9" s="74" t="n">
         <f aca="false">I8*'Vessel Assumptions'!$C$7</f>
         <v>2.852</v>
       </c>
-      <c r="K9" s="75" t="n">
+      <c r="K9" s="74" t="n">
         <f aca="false">K8*'Vessel Assumptions'!$C$7</f>
         <v>7.13</v>
       </c>
-      <c r="M9" s="75" t="n">
+      <c r="M9" s="74" t="n">
         <f aca="false">M8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="O9" s="75" t="n">
+      <c r="O9" s="74" t="n">
         <f aca="false">O8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="Q9" s="75" t="n">
+      <c r="Q9" s="74" t="n">
         <f aca="false">Q8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="S9" s="75" t="n">
+      <c r="S9" s="74" t="n">
         <f aca="false">S8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="U9" s="75" t="n">
+      <c r="U9" s="74" t="n">
         <f aca="false">U8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="W9" s="75" t="n">
+      <c r="W9" s="74" t="n">
         <f aca="false">W8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="Y9" s="75" t="n">
+      <c r="Y9" s="74" t="n">
         <f aca="false">Y8*'Vessel Assumptions'!$C$7</f>
         <v>6.2744</v>
       </c>
-      <c r="AB9" s="75" t="n">
+      <c r="AB9" s="74" t="n">
         <f aca="false">SUM(C9,E9,G9,I9,K9,M9,O9,Q9,S9,U9,W9,Y9)</f>
         <v>75.2928</v>
       </c>
@@ -50115,7 +50081,7 @@
       <c r="A5" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B5" s="76" t="n">
+      <c r="B5" s="75" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -50126,7 +50092,7 @@
       <c r="A6" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="B6" s="77" t="n">
+      <c r="B6" s="76" t="n">
         <v>0.06</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -50144,19 +50110,13 @@
       <c r="D8" s="31" t="s">
         <v>342</v>
       </c>
-      <c r="E8" s="31" t="s">
-        <v>343</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>344</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>345</v>
-      </c>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B9" s="78" t="n">
         <f aca="false">'Vessel Budget'!$AB$9</f>
@@ -50170,134 +50130,93 @@
         <f aca="false">C9+$B$5</f>
         <v>95.2928</v>
       </c>
-      <c r="E9" s="78" t="n">
-        <f aca="false">D9+$B$5</f>
-        <v>105.2928</v>
-      </c>
-      <c r="F9" s="78" t="n">
-        <f aca="false">E9+$B$5</f>
-        <v>115.2928</v>
-      </c>
-      <c r="G9" s="79" t="s">
-        <v>347</v>
-      </c>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="B10" s="80" t="n">
+        <v>344</v>
+      </c>
+      <c r="B10" s="79" t="n">
         <f aca="false">'Vessel Budget'!$AB$20/'Vessel Budget'!$AB$9</f>
         <v>4650</v>
       </c>
-      <c r="C10" s="80" t="n">
+      <c r="C10" s="79" t="n">
         <f aca="false">B10*(1+$B$6)</f>
         <v>4929</v>
       </c>
-      <c r="D10" s="80" t="n">
+      <c r="D10" s="79" t="n">
         <f aca="false">C10*(1+$B$6)</f>
         <v>5224.74</v>
       </c>
-      <c r="E10" s="80" t="n">
-        <f aca="false">D10*(1+$B$6)</f>
-        <v>5538.2244</v>
-      </c>
-      <c r="F10" s="80" t="n">
-        <f aca="false">E10*(1+$B$6)</f>
-        <v>5870.517864</v>
-      </c>
-      <c r="G10" s="79" t="s">
-        <v>349</v>
-      </c>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="B11" s="81" t="n">
+        <v>345</v>
+      </c>
+      <c r="B11" s="80" t="n">
         <f aca="false">B9*B10</f>
         <v>350111.52</v>
       </c>
-      <c r="C11" s="81" t="n">
+      <c r="C11" s="80" t="n">
         <f aca="false">C9*C10</f>
         <v>420408.2112</v>
       </c>
-      <c r="D11" s="81" t="n">
+      <c r="D11" s="80" t="n">
         <f aca="false">D9*D10</f>
         <v>497880.103872</v>
       </c>
-      <c r="E11" s="81" t="n">
-        <f aca="false">E9*E10</f>
-        <v>583135.15410432</v>
-      </c>
-      <c r="F11" s="81" t="n">
-        <f aca="false">F9*F10</f>
-        <v>676828.441990579</v>
-      </c>
-      <c r="G11" s="82" t="s">
-        <v>351</v>
-      </c>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="B12" s="83" t="n">
+        <v>346</v>
+      </c>
+      <c r="B12" s="81" t="n">
         <f aca="false">'Vessel Budget'!$AB$62/'Vessel Budget'!$AB$20</f>
         <v>0.248817204301075</v>
       </c>
-      <c r="C12" s="83" t="n">
+      <c r="C12" s="81" t="n">
         <f aca="false">$B$12</f>
         <v>0.248817204301075</v>
       </c>
-      <c r="D12" s="83" t="n">
+      <c r="D12" s="81" t="n">
         <f aca="false">$B$12</f>
         <v>0.248817204301075</v>
       </c>
-      <c r="E12" s="83" t="n">
-        <f aca="false">$B$12</f>
-        <v>0.248817204301075</v>
-      </c>
-      <c r="F12" s="83" t="n">
-        <f aca="false">$B$12</f>
-        <v>0.248817204301075</v>
-      </c>
-      <c r="G12" s="83" t="n">
-        <f aca="false">$B$12</f>
-        <v>0.248817204301075</v>
-      </c>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="B13" s="84" t="n">
+        <v>347</v>
+      </c>
+      <c r="B13" s="82" t="n">
         <f aca="false">B11*B12</f>
         <v>87113.7696</v>
       </c>
-      <c r="C13" s="84" t="n">
+      <c r="C13" s="82" t="n">
         <f aca="false">C11*C12</f>
         <v>104604.795776</v>
       </c>
-      <c r="D13" s="84" t="n">
+      <c r="D13" s="82" t="n">
         <f aca="false">D11*D12</f>
         <v>123881.13552256</v>
       </c>
-      <c r="E13" s="84" t="n">
-        <f aca="false">E11*E12</f>
-        <v>145094.058773914</v>
-      </c>
-      <c r="F13" s="84" t="n">
-        <f aca="false">F11*F12</f>
-        <v>168406.560727548</v>
-      </c>
-      <c r="G13" s="85" t="s">
-        <v>354</v>
-      </c>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
